--- a/lit_search_output/10_final_set.xlsx
+++ b/lit_search_output/10_final_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\01 DE\5. postdoc\SocEnRep Project\WP1 &amp; 2\litsearch\lit_search_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974E1A97-12A0-45F2-86DF-CB7D4EA3286C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC608AC8-3384-4D14-8AEE-43C54CF9B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Literature" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Literature!$A$1:$K$146</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="SWmQMlEmdeGT9ySd3u4M8qaq9Vn3ofc37xaN/KhwRaw="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="841">
   <si>
     <t>No.</t>
   </si>
@@ -2304,22 +2299,22 @@
     <t>Source: forward snowballing (Step 4); Cited by: Tools and recommendations for reproducible teaching</t>
   </si>
   <si>
-    <t>Perceived problems, causes, and solutions of finance research reproducibility and replicability: a pre-registered study</t>
-  </si>
-  <si>
-    <t>10.2139/ssrn.5610822</t>
-  </si>
-  <si>
-    <t>https://www.ssrn.com/abstract=5610822</t>
-  </si>
-  <si>
-    <t>Forward snowball ← Perceived problems, causes, and solutions of finance research reproducibility and replicability: a pre-registered report</t>
-  </si>
-  <si>
-    <t>https://openalex.org/W4415199669</t>
-  </si>
-  <si>
-    <t>Source: forward snowballing (Step 4); Cited by: Perceived problems, causes, and solutions of finance research reproducibility and replicability: a pre-registered report</t>
+    <t>Advancing Computational Reproducibility in Economics (ACRE)</t>
+  </si>
+  <si>
+    <t>Guide for Accelerating Computational Reproducibility in the Social Sciences</t>
+  </si>
+  <si>
+    <t>BITSS</t>
+  </si>
+  <si>
+    <t>https://bitss.github.io/ACRE/</t>
+  </si>
+  <si>
+    <t>Recommended by Amelia</t>
+  </si>
+  <si>
+    <t>Source: recommended by Amelia</t>
   </si>
   <si>
     <t>Rose, Julian; Neubauer, Florian; Ankel-Peters, Jörg</t>
@@ -2539,9 +2534,6 @@
   </si>
   <si>
     <t>https://www.nature.com/articles/s41586-026-10203-5</t>
-  </si>
-  <si>
-    <t>Source: recommended by Amelia</t>
   </si>
   <si>
     <t>Nosek, Brian; Errington, Timothy M., Haber, Noah et al.</t>
@@ -2560,7 +2552,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2612,6 +2604,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2654,7 +2652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2709,6 +2707,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2925,7 +2925,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2933,14 +2933,14 @@
     <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="10" width="28" customWidth="1"/>
     <col min="11" max="11" width="45" customWidth="1"/>
-    <col min="12" max="26" width="8.7109375" customWidth="1"/>
+    <col min="12" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -5778,7 +5778,7 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -5840,7 +5840,7 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -6499,7 +6499,7 @@
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
     </row>
-    <row r="104" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -7327,7 +7327,7 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
     </row>
-    <row r="128" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -7358,7 +7358,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
     </row>
-    <row r="129" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -7389,7 +7389,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
     </row>
-    <row r="130" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -7420,7 +7420,7 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
     </row>
-    <row r="131" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -7455,42 +7455,36 @@
         <v>757</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+    <row r="132" spans="1:11" s="20" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="20">
         <v>131</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="D132" s="3" t="s">
+      <c r="B132" s="20" t="s">
         <v>758</v>
       </c>
-      <c r="E132" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="F132" s="3" t="s">
+      <c r="C132" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D132" s="20" t="s">
         <v>759</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="E132" s="20" t="s">
         <v>760</v>
       </c>
-      <c r="H132" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I132" s="3" t="s">
+      <c r="G132" s="20" t="s">
         <v>761</v>
       </c>
-      <c r="J132" s="3" t="s">
+      <c r="H132" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I132" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="K132" s="3" t="s">
+      <c r="K132" s="20" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -7525,7 +7519,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -7560,7 +7554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -7595,7 +7589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -7630,7 +7624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -7663,7 +7657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -7698,7 +7692,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -7733,7 +7727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -7768,7 +7762,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -7801,7 +7795,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -7836,7 +7830,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -7869,7 +7863,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -7902,7 +7896,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -7932,30 +7926,30 @@
       </c>
       <c r="J145" s="9"/>
       <c r="K145" s="3" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>771</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>424</v>
       </c>
       <c r="F146" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="G146" s="12" t="s">
         <v>840</v>
-      </c>
-      <c r="G146" s="12" t="s">
-        <v>841</v>
       </c>
       <c r="H146" s="9" t="s">
         <v>115</v>
@@ -7965,10 +7959,10 @@
       </c>
       <c r="J146" s="9"/>
       <c r="K146" s="3" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -7981,20 +7975,15 @@
       <c r="J147" s="13"/>
       <c r="K147" s="13"/>
     </row>
-    <row r="148" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="13"/>
-      <c r="B148" s="14"/>
-      <c r="C148" s="14"/>
-      <c r="D148" s="14"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="16"/>
-      <c r="G148" s="14"/>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
-      <c r="J148" s="13"/>
-      <c r="K148" s="13"/>
-    </row>
-    <row r="149" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B148" s="17"/>
+      <c r="C148" s="17"/>
+      <c r="D148" s="17"/>
+      <c r="E148" s="18"/>
+      <c r="F148" s="19"/>
+      <c r="G148" s="17"/>
+    </row>
+    <row r="149" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="17"/>
       <c r="C149" s="17"/>
       <c r="D149" s="17"/>
@@ -8002,7 +7991,7 @@
       <c r="F149" s="19"/>
       <c r="G149" s="17"/>
     </row>
-    <row r="150" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
       <c r="D150" s="17"/>
@@ -8010,7 +7999,7 @@
       <c r="F150" s="19"/>
       <c r="G150" s="17"/>
     </row>
-    <row r="151" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="17"/>
       <c r="C151" s="17"/>
       <c r="D151" s="17"/>
@@ -8018,7 +8007,7 @@
       <c r="F151" s="19"/>
       <c r="G151" s="17"/>
     </row>
-    <row r="152" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
       <c r="D152" s="17"/>
@@ -8026,7 +8015,7 @@
       <c r="F152" s="19"/>
       <c r="G152" s="17"/>
     </row>
-    <row r="153" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="17"/>
       <c r="C153" s="17"/>
       <c r="D153" s="17"/>
@@ -8034,7 +8023,7 @@
       <c r="F153" s="19"/>
       <c r="G153" s="17"/>
     </row>
-    <row r="154" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
       <c r="D154" s="17"/>
@@ -8042,7 +8031,7 @@
       <c r="F154" s="19"/>
       <c r="G154" s="17"/>
     </row>
-    <row r="155" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="17"/>
       <c r="C155" s="17"/>
       <c r="D155" s="17"/>
@@ -8050,7 +8039,7 @@
       <c r="F155" s="19"/>
       <c r="G155" s="17"/>
     </row>
-    <row r="156" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
       <c r="D156" s="17"/>
@@ -8058,7 +8047,7 @@
       <c r="F156" s="19"/>
       <c r="G156" s="17"/>
     </row>
-    <row r="157" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="17"/>
       <c r="C157" s="17"/>
       <c r="D157" s="17"/>
@@ -8066,7 +8055,7 @@
       <c r="F157" s="19"/>
       <c r="G157" s="17"/>
     </row>
-    <row r="158" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
       <c r="D158" s="17"/>
@@ -8074,7 +8063,7 @@
       <c r="F158" s="19"/>
       <c r="G158" s="17"/>
     </row>
-    <row r="159" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="17"/>
       <c r="C159" s="17"/>
       <c r="D159" s="17"/>
@@ -8082,7 +8071,7 @@
       <c r="F159" s="19"/>
       <c r="G159" s="17"/>
     </row>
-    <row r="160" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
       <c r="D160" s="17"/>
@@ -8090,7 +8079,7 @@
       <c r="F160" s="19"/>
       <c r="G160" s="17"/>
     </row>
-    <row r="161" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="17"/>
       <c r="C161" s="17"/>
       <c r="D161" s="17"/>
@@ -8098,7 +8087,7 @@
       <c r="F161" s="19"/>
       <c r="G161" s="17"/>
     </row>
-    <row r="162" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
       <c r="D162" s="17"/>
@@ -8106,7 +8095,7 @@
       <c r="F162" s="19"/>
       <c r="G162" s="17"/>
     </row>
-    <row r="163" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="17"/>
       <c r="C163" s="17"/>
       <c r="D163" s="17"/>
@@ -8114,7 +8103,7 @@
       <c r="F163" s="19"/>
       <c r="G163" s="17"/>
     </row>
-    <row r="164" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
       <c r="D164" s="17"/>
@@ -8122,7 +8111,7 @@
       <c r="F164" s="19"/>
       <c r="G164" s="17"/>
     </row>
-    <row r="165" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="17"/>
       <c r="C165" s="17"/>
       <c r="D165" s="17"/>
@@ -8130,7 +8119,7 @@
       <c r="F165" s="19"/>
       <c r="G165" s="17"/>
     </row>
-    <row r="166" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
       <c r="D166" s="17"/>
@@ -8138,7 +8127,7 @@
       <c r="F166" s="19"/>
       <c r="G166" s="17"/>
     </row>
-    <row r="167" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="17"/>
       <c r="C167" s="17"/>
       <c r="D167" s="17"/>
@@ -8146,7 +8135,7 @@
       <c r="F167" s="19"/>
       <c r="G167" s="17"/>
     </row>
-    <row r="168" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
       <c r="D168" s="17"/>
@@ -8154,7 +8143,7 @@
       <c r="F168" s="19"/>
       <c r="G168" s="17"/>
     </row>
-    <row r="169" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="17"/>
       <c r="C169" s="17"/>
       <c r="D169" s="17"/>
@@ -8162,7 +8151,7 @@
       <c r="F169" s="19"/>
       <c r="G169" s="17"/>
     </row>
-    <row r="170" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
       <c r="D170" s="17"/>
@@ -8170,7 +8159,7 @@
       <c r="F170" s="19"/>
       <c r="G170" s="17"/>
     </row>
-    <row r="171" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B171" s="17"/>
       <c r="C171" s="17"/>
       <c r="D171" s="17"/>
@@ -8178,7 +8167,7 @@
       <c r="F171" s="19"/>
       <c r="G171" s="17"/>
     </row>
-    <row r="172" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
       <c r="D172" s="17"/>
@@ -8186,7 +8175,7 @@
       <c r="F172" s="19"/>
       <c r="G172" s="17"/>
     </row>
-    <row r="173" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B173" s="17"/>
       <c r="C173" s="17"/>
       <c r="D173" s="17"/>
@@ -8194,7 +8183,7 @@
       <c r="F173" s="19"/>
       <c r="G173" s="17"/>
     </row>
-    <row r="174" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
       <c r="D174" s="17"/>
@@ -8202,7 +8191,7 @@
       <c r="F174" s="19"/>
       <c r="G174" s="17"/>
     </row>
-    <row r="175" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B175" s="17"/>
       <c r="C175" s="17"/>
       <c r="D175" s="17"/>
@@ -8210,7 +8199,7 @@
       <c r="F175" s="19"/>
       <c r="G175" s="17"/>
     </row>
-    <row r="176" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
       <c r="D176" s="17"/>
@@ -8218,7 +8207,7 @@
       <c r="F176" s="19"/>
       <c r="G176" s="17"/>
     </row>
-    <row r="177" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B177" s="17"/>
       <c r="C177" s="17"/>
       <c r="D177" s="17"/>
@@ -8226,7 +8215,7 @@
       <c r="F177" s="19"/>
       <c r="G177" s="17"/>
     </row>
-    <row r="178" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
       <c r="D178" s="17"/>
@@ -8234,7 +8223,7 @@
       <c r="F178" s="19"/>
       <c r="G178" s="17"/>
     </row>
-    <row r="179" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B179" s="17"/>
       <c r="C179" s="17"/>
       <c r="D179" s="17"/>
@@ -8242,7 +8231,7 @@
       <c r="F179" s="19"/>
       <c r="G179" s="17"/>
     </row>
-    <row r="180" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
       <c r="D180" s="17"/>
@@ -8250,7 +8239,7 @@
       <c r="F180" s="19"/>
       <c r="G180" s="17"/>
     </row>
-    <row r="181" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
       <c r="D181" s="17"/>
@@ -8258,7 +8247,7 @@
       <c r="F181" s="19"/>
       <c r="G181" s="17"/>
     </row>
-    <row r="182" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
       <c r="D182" s="17"/>
@@ -8266,7 +8255,7 @@
       <c r="F182" s="19"/>
       <c r="G182" s="17"/>
     </row>
-    <row r="183" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
       <c r="D183" s="17"/>
@@ -8274,7 +8263,7 @@
       <c r="F183" s="19"/>
       <c r="G183" s="17"/>
     </row>
-    <row r="184" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
       <c r="D184" s="17"/>
@@ -8282,7 +8271,7 @@
       <c r="F184" s="19"/>
       <c r="G184" s="17"/>
     </row>
-    <row r="185" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
       <c r="D185" s="17"/>
@@ -8290,7 +8279,7 @@
       <c r="F185" s="19"/>
       <c r="G185" s="17"/>
     </row>
-    <row r="186" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
       <c r="D186" s="17"/>
@@ -8298,7 +8287,7 @@
       <c r="F186" s="19"/>
       <c r="G186" s="17"/>
     </row>
-    <row r="187" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
       <c r="D187" s="17"/>
@@ -8306,7 +8295,7 @@
       <c r="F187" s="19"/>
       <c r="G187" s="17"/>
     </row>
-    <row r="188" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
       <c r="D188" s="17"/>
@@ -8314,7 +8303,7 @@
       <c r="F188" s="19"/>
       <c r="G188" s="17"/>
     </row>
-    <row r="189" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="17"/>
       <c r="C189" s="17"/>
       <c r="D189" s="17"/>
@@ -8322,7 +8311,7 @@
       <c r="F189" s="19"/>
       <c r="G189" s="17"/>
     </row>
-    <row r="190" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
       <c r="D190" s="17"/>
@@ -8330,7 +8319,7 @@
       <c r="F190" s="19"/>
       <c r="G190" s="17"/>
     </row>
-    <row r="191" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
       <c r="D191" s="17"/>
@@ -8338,7 +8327,7 @@
       <c r="F191" s="19"/>
       <c r="G191" s="17"/>
     </row>
-    <row r="192" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
       <c r="D192" s="17"/>
@@ -8346,7 +8335,7 @@
       <c r="F192" s="19"/>
       <c r="G192" s="17"/>
     </row>
-    <row r="193" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B193" s="17"/>
       <c r="C193" s="17"/>
       <c r="D193" s="17"/>
@@ -8354,7 +8343,7 @@
       <c r="F193" s="19"/>
       <c r="G193" s="17"/>
     </row>
-    <row r="194" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
       <c r="D194" s="17"/>
@@ -8362,7 +8351,7 @@
       <c r="F194" s="19"/>
       <c r="G194" s="17"/>
     </row>
-    <row r="195" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B195" s="17"/>
       <c r="C195" s="17"/>
       <c r="D195" s="17"/>
@@ -8370,7 +8359,7 @@
       <c r="F195" s="19"/>
       <c r="G195" s="17"/>
     </row>
-    <row r="196" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
       <c r="D196" s="17"/>
@@ -8378,7 +8367,7 @@
       <c r="F196" s="19"/>
       <c r="G196" s="17"/>
     </row>
-    <row r="197" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
       <c r="D197" s="17"/>
@@ -8386,7 +8375,7 @@
       <c r="F197" s="19"/>
       <c r="G197" s="17"/>
     </row>
-    <row r="198" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
       <c r="D198" s="17"/>
@@ -8394,7 +8383,7 @@
       <c r="F198" s="19"/>
       <c r="G198" s="17"/>
     </row>
-    <row r="199" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B199" s="17"/>
       <c r="C199" s="17"/>
       <c r="D199" s="17"/>
@@ -8402,7 +8391,7 @@
       <c r="F199" s="19"/>
       <c r="G199" s="17"/>
     </row>
-    <row r="200" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
       <c r="D200" s="17"/>
@@ -8410,7 +8399,7 @@
       <c r="F200" s="19"/>
       <c r="G200" s="17"/>
     </row>
-    <row r="201" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B201" s="17"/>
       <c r="C201" s="17"/>
       <c r="D201" s="17"/>
@@ -8418,7 +8407,7 @@
       <c r="F201" s="19"/>
       <c r="G201" s="17"/>
     </row>
-    <row r="202" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
       <c r="D202" s="17"/>
@@ -8426,7 +8415,7 @@
       <c r="F202" s="19"/>
       <c r="G202" s="17"/>
     </row>
-    <row r="203" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B203" s="17"/>
       <c r="C203" s="17"/>
       <c r="D203" s="17"/>
@@ -8434,7 +8423,7 @@
       <c r="F203" s="19"/>
       <c r="G203" s="17"/>
     </row>
-    <row r="204" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B204" s="17"/>
       <c r="C204" s="17"/>
       <c r="D204" s="17"/>
@@ -8442,7 +8431,7 @@
       <c r="F204" s="19"/>
       <c r="G204" s="17"/>
     </row>
-    <row r="205" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B205" s="17"/>
       <c r="C205" s="17"/>
       <c r="D205" s="17"/>
@@ -8450,7 +8439,7 @@
       <c r="F205" s="19"/>
       <c r="G205" s="17"/>
     </row>
-    <row r="206" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B206" s="17"/>
       <c r="C206" s="17"/>
       <c r="D206" s="17"/>
@@ -8458,7 +8447,7 @@
       <c r="F206" s="19"/>
       <c r="G206" s="17"/>
     </row>
-    <row r="207" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B207" s="17"/>
       <c r="C207" s="17"/>
       <c r="D207" s="17"/>
@@ -8466,7 +8455,7 @@
       <c r="F207" s="19"/>
       <c r="G207" s="17"/>
     </row>
-    <row r="208" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B208" s="17"/>
       <c r="C208" s="17"/>
       <c r="D208" s="17"/>
@@ -8474,7 +8463,7 @@
       <c r="F208" s="19"/>
       <c r="G208" s="17"/>
     </row>
-    <row r="209" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
       <c r="D209" s="17"/>
@@ -8482,7 +8471,7 @@
       <c r="F209" s="19"/>
       <c r="G209" s="17"/>
     </row>
-    <row r="210" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B210" s="17"/>
       <c r="C210" s="17"/>
       <c r="D210" s="17"/>
@@ -8490,7 +8479,7 @@
       <c r="F210" s="19"/>
       <c r="G210" s="17"/>
     </row>
-    <row r="211" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B211" s="17"/>
       <c r="C211" s="17"/>
       <c r="D211" s="17"/>
@@ -8498,7 +8487,7 @@
       <c r="F211" s="19"/>
       <c r="G211" s="17"/>
     </row>
-    <row r="212" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B212" s="17"/>
       <c r="C212" s="17"/>
       <c r="D212" s="17"/>
@@ -8506,7 +8495,7 @@
       <c r="F212" s="19"/>
       <c r="G212" s="17"/>
     </row>
-    <row r="213" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B213" s="17"/>
       <c r="C213" s="17"/>
       <c r="D213" s="17"/>
@@ -8514,7 +8503,7 @@
       <c r="F213" s="19"/>
       <c r="G213" s="17"/>
     </row>
-    <row r="214" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B214" s="17"/>
       <c r="C214" s="17"/>
       <c r="D214" s="17"/>
@@ -8522,7 +8511,7 @@
       <c r="F214" s="19"/>
       <c r="G214" s="17"/>
     </row>
-    <row r="215" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B215" s="17"/>
       <c r="C215" s="17"/>
       <c r="D215" s="17"/>
@@ -8530,7 +8519,7 @@
       <c r="F215" s="19"/>
       <c r="G215" s="17"/>
     </row>
-    <row r="216" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B216" s="17"/>
       <c r="C216" s="17"/>
       <c r="D216" s="17"/>
@@ -8538,7 +8527,7 @@
       <c r="F216" s="19"/>
       <c r="G216" s="17"/>
     </row>
-    <row r="217" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B217" s="17"/>
       <c r="C217" s="17"/>
       <c r="D217" s="17"/>
@@ -8546,7 +8535,7 @@
       <c r="F217" s="19"/>
       <c r="G217" s="17"/>
     </row>
-    <row r="218" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B218" s="17"/>
       <c r="C218" s="17"/>
       <c r="D218" s="17"/>
@@ -8554,7 +8543,7 @@
       <c r="F218" s="19"/>
       <c r="G218" s="17"/>
     </row>
-    <row r="219" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B219" s="17"/>
       <c r="C219" s="17"/>
       <c r="D219" s="17"/>
@@ -8562,7 +8551,7 @@
       <c r="F219" s="19"/>
       <c r="G219" s="17"/>
     </row>
-    <row r="220" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B220" s="17"/>
       <c r="C220" s="17"/>
       <c r="D220" s="17"/>
@@ -8570,7 +8559,7 @@
       <c r="F220" s="19"/>
       <c r="G220" s="17"/>
     </row>
-    <row r="221" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B221" s="17"/>
       <c r="C221" s="17"/>
       <c r="D221" s="17"/>
@@ -8578,7 +8567,7 @@
       <c r="F221" s="19"/>
       <c r="G221" s="17"/>
     </row>
-    <row r="222" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B222" s="17"/>
       <c r="C222" s="17"/>
       <c r="D222" s="17"/>
@@ -8586,7 +8575,7 @@
       <c r="F222" s="19"/>
       <c r="G222" s="17"/>
     </row>
-    <row r="223" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B223" s="17"/>
       <c r="C223" s="17"/>
       <c r="D223" s="17"/>
@@ -8594,7 +8583,7 @@
       <c r="F223" s="19"/>
       <c r="G223" s="17"/>
     </row>
-    <row r="224" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B224" s="17"/>
       <c r="C224" s="17"/>
       <c r="D224" s="17"/>
@@ -8602,7 +8591,7 @@
       <c r="F224" s="19"/>
       <c r="G224" s="17"/>
     </row>
-    <row r="225" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B225" s="17"/>
       <c r="C225" s="17"/>
       <c r="D225" s="17"/>
@@ -8610,7 +8599,7 @@
       <c r="F225" s="19"/>
       <c r="G225" s="17"/>
     </row>
-    <row r="226" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B226" s="17"/>
       <c r="C226" s="17"/>
       <c r="D226" s="17"/>
@@ -8618,7 +8607,7 @@
       <c r="F226" s="19"/>
       <c r="G226" s="17"/>
     </row>
-    <row r="227" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B227" s="17"/>
       <c r="C227" s="17"/>
       <c r="D227" s="17"/>
@@ -8626,7 +8615,7 @@
       <c r="F227" s="19"/>
       <c r="G227" s="17"/>
     </row>
-    <row r="228" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B228" s="17"/>
       <c r="C228" s="17"/>
       <c r="D228" s="17"/>
@@ -8634,7 +8623,7 @@
       <c r="F228" s="19"/>
       <c r="G228" s="17"/>
     </row>
-    <row r="229" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B229" s="17"/>
       <c r="C229" s="17"/>
       <c r="D229" s="17"/>
@@ -8642,7 +8631,7 @@
       <c r="F229" s="19"/>
       <c r="G229" s="17"/>
     </row>
-    <row r="230" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B230" s="17"/>
       <c r="C230" s="17"/>
       <c r="D230" s="17"/>
@@ -8650,7 +8639,7 @@
       <c r="F230" s="19"/>
       <c r="G230" s="17"/>
     </row>
-    <row r="231" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B231" s="17"/>
       <c r="C231" s="17"/>
       <c r="D231" s="17"/>
@@ -8658,7 +8647,7 @@
       <c r="F231" s="19"/>
       <c r="G231" s="17"/>
     </row>
-    <row r="232" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B232" s="17"/>
       <c r="C232" s="17"/>
       <c r="D232" s="17"/>
@@ -8666,7 +8655,7 @@
       <c r="F232" s="19"/>
       <c r="G232" s="17"/>
     </row>
-    <row r="233" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B233" s="17"/>
       <c r="C233" s="17"/>
       <c r="D233" s="17"/>
@@ -8674,7 +8663,7 @@
       <c r="F233" s="19"/>
       <c r="G233" s="17"/>
     </row>
-    <row r="234" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B234" s="17"/>
       <c r="C234" s="17"/>
       <c r="D234" s="17"/>
@@ -8682,7 +8671,7 @@
       <c r="F234" s="19"/>
       <c r="G234" s="17"/>
     </row>
-    <row r="235" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B235" s="17"/>
       <c r="C235" s="17"/>
       <c r="D235" s="17"/>
@@ -8690,7 +8679,7 @@
       <c r="F235" s="19"/>
       <c r="G235" s="17"/>
     </row>
-    <row r="236" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B236" s="17"/>
       <c r="C236" s="17"/>
       <c r="D236" s="17"/>
@@ -8698,7 +8687,7 @@
       <c r="F236" s="19"/>
       <c r="G236" s="17"/>
     </row>
-    <row r="237" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B237" s="17"/>
       <c r="C237" s="17"/>
       <c r="D237" s="17"/>
@@ -8706,7 +8695,7 @@
       <c r="F237" s="19"/>
       <c r="G237" s="17"/>
     </row>
-    <row r="238" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B238" s="17"/>
       <c r="C238" s="17"/>
       <c r="D238" s="17"/>
@@ -8714,7 +8703,7 @@
       <c r="F238" s="19"/>
       <c r="G238" s="17"/>
     </row>
-    <row r="239" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B239" s="17"/>
       <c r="C239" s="17"/>
       <c r="D239" s="17"/>
@@ -8722,7 +8711,7 @@
       <c r="F239" s="19"/>
       <c r="G239" s="17"/>
     </row>
-    <row r="240" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B240" s="17"/>
       <c r="C240" s="17"/>
       <c r="D240" s="17"/>
@@ -8730,7 +8719,7 @@
       <c r="F240" s="19"/>
       <c r="G240" s="17"/>
     </row>
-    <row r="241" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
       <c r="D241" s="17"/>
@@ -8738,7 +8727,7 @@
       <c r="F241" s="19"/>
       <c r="G241" s="17"/>
     </row>
-    <row r="242" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B242" s="17"/>
       <c r="C242" s="17"/>
       <c r="D242" s="17"/>
@@ -8746,7 +8735,7 @@
       <c r="F242" s="19"/>
       <c r="G242" s="17"/>
     </row>
-    <row r="243" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B243" s="17"/>
       <c r="C243" s="17"/>
       <c r="D243" s="17"/>
@@ -8754,7 +8743,7 @@
       <c r="F243" s="19"/>
       <c r="G243" s="17"/>
     </row>
-    <row r="244" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
       <c r="D244" s="17"/>
@@ -8762,7 +8751,7 @@
       <c r="F244" s="19"/>
       <c r="G244" s="17"/>
     </row>
-    <row r="245" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B245" s="17"/>
       <c r="C245" s="17"/>
       <c r="D245" s="17"/>
@@ -8770,7 +8759,7 @@
       <c r="F245" s="19"/>
       <c r="G245" s="17"/>
     </row>
-    <row r="246" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B246" s="17"/>
       <c r="C246" s="17"/>
       <c r="D246" s="17"/>
@@ -8778,7 +8767,7 @@
       <c r="F246" s="19"/>
       <c r="G246" s="17"/>
     </row>
-    <row r="247" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B247" s="17"/>
       <c r="C247" s="17"/>
       <c r="D247" s="17"/>
@@ -8786,7 +8775,7 @@
       <c r="F247" s="19"/>
       <c r="G247" s="17"/>
     </row>
-    <row r="248" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
       <c r="D248" s="17"/>
@@ -8794,7 +8783,7 @@
       <c r="F248" s="19"/>
       <c r="G248" s="17"/>
     </row>
-    <row r="249" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B249" s="17"/>
       <c r="C249" s="17"/>
       <c r="D249" s="17"/>
@@ -8802,7 +8791,7 @@
       <c r="F249" s="19"/>
       <c r="G249" s="17"/>
     </row>
-    <row r="250" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B250" s="17"/>
       <c r="C250" s="17"/>
       <c r="D250" s="17"/>
@@ -8810,7 +8799,7 @@
       <c r="F250" s="19"/>
       <c r="G250" s="17"/>
     </row>
-    <row r="251" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B251" s="17"/>
       <c r="C251" s="17"/>
       <c r="D251" s="17"/>
@@ -8818,7 +8807,7 @@
       <c r="F251" s="19"/>
       <c r="G251" s="17"/>
     </row>
-    <row r="252" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B252" s="17"/>
       <c r="C252" s="17"/>
       <c r="D252" s="17"/>
@@ -8826,7 +8815,7 @@
       <c r="F252" s="19"/>
       <c r="G252" s="17"/>
     </row>
-    <row r="253" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B253" s="17"/>
       <c r="C253" s="17"/>
       <c r="D253" s="17"/>
@@ -8834,7 +8823,7 @@
       <c r="F253" s="19"/>
       <c r="G253" s="17"/>
     </row>
-    <row r="254" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B254" s="17"/>
       <c r="C254" s="17"/>
       <c r="D254" s="17"/>
@@ -8842,7 +8831,7 @@
       <c r="F254" s="19"/>
       <c r="G254" s="17"/>
     </row>
-    <row r="255" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B255" s="17"/>
       <c r="C255" s="17"/>
       <c r="D255" s="17"/>
@@ -8850,7 +8839,7 @@
       <c r="F255" s="19"/>
       <c r="G255" s="17"/>
     </row>
-    <row r="256" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B256" s="17"/>
       <c r="C256" s="17"/>
       <c r="D256" s="17"/>
@@ -8858,7 +8847,7 @@
       <c r="F256" s="19"/>
       <c r="G256" s="17"/>
     </row>
-    <row r="257" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B257" s="17"/>
       <c r="C257" s="17"/>
       <c r="D257" s="17"/>
@@ -8866,7 +8855,7 @@
       <c r="F257" s="19"/>
       <c r="G257" s="17"/>
     </row>
-    <row r="258" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B258" s="17"/>
       <c r="C258" s="17"/>
       <c r="D258" s="17"/>
@@ -8874,7 +8863,7 @@
       <c r="F258" s="19"/>
       <c r="G258" s="17"/>
     </row>
-    <row r="259" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B259" s="17"/>
       <c r="C259" s="17"/>
       <c r="D259" s="17"/>
@@ -8882,7 +8871,7 @@
       <c r="F259" s="19"/>
       <c r="G259" s="17"/>
     </row>
-    <row r="260" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B260" s="17"/>
       <c r="C260" s="17"/>
       <c r="D260" s="17"/>
@@ -8890,7 +8879,7 @@
       <c r="F260" s="19"/>
       <c r="G260" s="17"/>
     </row>
-    <row r="261" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B261" s="17"/>
       <c r="C261" s="17"/>
       <c r="D261" s="17"/>
@@ -8898,7 +8887,7 @@
       <c r="F261" s="19"/>
       <c r="G261" s="17"/>
     </row>
-    <row r="262" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B262" s="17"/>
       <c r="C262" s="17"/>
       <c r="D262" s="17"/>
@@ -8906,7 +8895,7 @@
       <c r="F262" s="19"/>
       <c r="G262" s="17"/>
     </row>
-    <row r="263" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B263" s="17"/>
       <c r="C263" s="17"/>
       <c r="D263" s="17"/>
@@ -8914,7 +8903,7 @@
       <c r="F263" s="19"/>
       <c r="G263" s="17"/>
     </row>
-    <row r="264" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B264" s="17"/>
       <c r="C264" s="17"/>
       <c r="D264" s="17"/>
@@ -8922,7 +8911,7 @@
       <c r="F264" s="19"/>
       <c r="G264" s="17"/>
     </row>
-    <row r="265" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B265" s="17"/>
       <c r="C265" s="17"/>
       <c r="D265" s="17"/>
@@ -8930,7 +8919,7 @@
       <c r="F265" s="19"/>
       <c r="G265" s="17"/>
     </row>
-    <row r="266" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B266" s="17"/>
       <c r="C266" s="17"/>
       <c r="D266" s="17"/>
@@ -8938,7 +8927,7 @@
       <c r="F266" s="19"/>
       <c r="G266" s="17"/>
     </row>
-    <row r="267" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B267" s="17"/>
       <c r="C267" s="17"/>
       <c r="D267" s="17"/>
@@ -8946,7 +8935,7 @@
       <c r="F267" s="19"/>
       <c r="G267" s="17"/>
     </row>
-    <row r="268" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B268" s="17"/>
       <c r="C268" s="17"/>
       <c r="D268" s="17"/>
@@ -8954,7 +8943,7 @@
       <c r="F268" s="19"/>
       <c r="G268" s="17"/>
     </row>
-    <row r="269" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
       <c r="D269" s="17"/>
@@ -8962,7 +8951,7 @@
       <c r="F269" s="19"/>
       <c r="G269" s="17"/>
     </row>
-    <row r="270" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B270" s="17"/>
       <c r="C270" s="17"/>
       <c r="D270" s="17"/>
@@ -8970,7 +8959,7 @@
       <c r="F270" s="19"/>
       <c r="G270" s="17"/>
     </row>
-    <row r="271" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B271" s="17"/>
       <c r="C271" s="17"/>
       <c r="D271" s="17"/>
@@ -8978,7 +8967,7 @@
       <c r="F271" s="19"/>
       <c r="G271" s="17"/>
     </row>
-    <row r="272" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
       <c r="D272" s="17"/>
@@ -8986,7 +8975,7 @@
       <c r="F272" s="19"/>
       <c r="G272" s="17"/>
     </row>
-    <row r="273" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B273" s="17"/>
       <c r="C273" s="17"/>
       <c r="D273" s="17"/>
@@ -8994,7 +8983,7 @@
       <c r="F273" s="19"/>
       <c r="G273" s="17"/>
     </row>
-    <row r="274" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B274" s="17"/>
       <c r="C274" s="17"/>
       <c r="D274" s="17"/>
@@ -9002,7 +8991,7 @@
       <c r="F274" s="19"/>
       <c r="G274" s="17"/>
     </row>
-    <row r="275" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
       <c r="D275" s="17"/>
@@ -9010,7 +8999,7 @@
       <c r="F275" s="19"/>
       <c r="G275" s="17"/>
     </row>
-    <row r="276" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
       <c r="D276" s="17"/>
@@ -9018,7 +9007,7 @@
       <c r="F276" s="19"/>
       <c r="G276" s="17"/>
     </row>
-    <row r="277" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B277" s="17"/>
       <c r="C277" s="17"/>
       <c r="D277" s="17"/>
@@ -9026,7 +9015,7 @@
       <c r="F277" s="19"/>
       <c r="G277" s="17"/>
     </row>
-    <row r="278" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B278" s="17"/>
       <c r="C278" s="17"/>
       <c r="D278" s="17"/>
@@ -9034,7 +9023,7 @@
       <c r="F278" s="19"/>
       <c r="G278" s="17"/>
     </row>
-    <row r="279" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B279" s="17"/>
       <c r="C279" s="17"/>
       <c r="D279" s="17"/>
@@ -9042,7 +9031,7 @@
       <c r="F279" s="19"/>
       <c r="G279" s="17"/>
     </row>
-    <row r="280" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B280" s="17"/>
       <c r="C280" s="17"/>
       <c r="D280" s="17"/>
@@ -9050,7 +9039,7 @@
       <c r="F280" s="19"/>
       <c r="G280" s="17"/>
     </row>
-    <row r="281" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B281" s="17"/>
       <c r="C281" s="17"/>
       <c r="D281" s="17"/>
@@ -9058,7 +9047,7 @@
       <c r="F281" s="19"/>
       <c r="G281" s="17"/>
     </row>
-    <row r="282" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B282" s="17"/>
       <c r="C282" s="17"/>
       <c r="D282" s="17"/>
@@ -9066,7 +9055,7 @@
       <c r="F282" s="19"/>
       <c r="G282" s="17"/>
     </row>
-    <row r="283" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B283" s="17"/>
       <c r="C283" s="17"/>
       <c r="D283" s="17"/>
@@ -9074,7 +9063,7 @@
       <c r="F283" s="19"/>
       <c r="G283" s="17"/>
     </row>
-    <row r="284" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B284" s="17"/>
       <c r="C284" s="17"/>
       <c r="D284" s="17"/>
@@ -9082,7 +9071,7 @@
       <c r="F284" s="19"/>
       <c r="G284" s="17"/>
     </row>
-    <row r="285" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B285" s="17"/>
       <c r="C285" s="17"/>
       <c r="D285" s="17"/>
@@ -9090,7 +9079,7 @@
       <c r="F285" s="19"/>
       <c r="G285" s="17"/>
     </row>
-    <row r="286" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B286" s="17"/>
       <c r="C286" s="17"/>
       <c r="D286" s="17"/>
@@ -9098,7 +9087,7 @@
       <c r="F286" s="19"/>
       <c r="G286" s="17"/>
     </row>
-    <row r="287" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B287" s="17"/>
       <c r="C287" s="17"/>
       <c r="D287" s="17"/>
@@ -9106,7 +9095,7 @@
       <c r="F287" s="19"/>
       <c r="G287" s="17"/>
     </row>
-    <row r="288" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B288" s="17"/>
       <c r="C288" s="17"/>
       <c r="D288" s="17"/>
@@ -9114,7 +9103,7 @@
       <c r="F288" s="19"/>
       <c r="G288" s="17"/>
     </row>
-    <row r="289" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B289" s="17"/>
       <c r="C289" s="17"/>
       <c r="D289" s="17"/>
@@ -9122,7 +9111,7 @@
       <c r="F289" s="19"/>
       <c r="G289" s="17"/>
     </row>
-    <row r="290" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B290" s="17"/>
       <c r="C290" s="17"/>
       <c r="D290" s="17"/>
@@ -9130,7 +9119,7 @@
       <c r="F290" s="19"/>
       <c r="G290" s="17"/>
     </row>
-    <row r="291" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B291" s="17"/>
       <c r="C291" s="17"/>
       <c r="D291" s="17"/>
@@ -9138,7 +9127,7 @@
       <c r="F291" s="19"/>
       <c r="G291" s="17"/>
     </row>
-    <row r="292" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B292" s="17"/>
       <c r="C292" s="17"/>
       <c r="D292" s="17"/>
@@ -9146,7 +9135,7 @@
       <c r="F292" s="19"/>
       <c r="G292" s="17"/>
     </row>
-    <row r="293" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B293" s="17"/>
       <c r="C293" s="17"/>
       <c r="D293" s="17"/>
@@ -9154,7 +9143,7 @@
       <c r="F293" s="19"/>
       <c r="G293" s="17"/>
     </row>
-    <row r="294" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B294" s="17"/>
       <c r="C294" s="17"/>
       <c r="D294" s="17"/>
@@ -9162,7 +9151,7 @@
       <c r="F294" s="19"/>
       <c r="G294" s="17"/>
     </row>
-    <row r="295" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B295" s="17"/>
       <c r="C295" s="17"/>
       <c r="D295" s="17"/>
@@ -9170,7 +9159,7 @@
       <c r="F295" s="19"/>
       <c r="G295" s="17"/>
     </row>
-    <row r="296" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B296" s="17"/>
       <c r="C296" s="17"/>
       <c r="D296" s="17"/>
@@ -9178,7 +9167,7 @@
       <c r="F296" s="19"/>
       <c r="G296" s="17"/>
     </row>
-    <row r="297" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B297" s="17"/>
       <c r="C297" s="17"/>
       <c r="D297" s="17"/>
@@ -9186,7 +9175,7 @@
       <c r="F297" s="19"/>
       <c r="G297" s="17"/>
     </row>
-    <row r="298" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B298" s="17"/>
       <c r="C298" s="17"/>
       <c r="D298" s="17"/>
@@ -9194,7 +9183,7 @@
       <c r="F298" s="19"/>
       <c r="G298" s="17"/>
     </row>
-    <row r="299" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B299" s="17"/>
       <c r="C299" s="17"/>
       <c r="D299" s="17"/>
@@ -9202,7 +9191,7 @@
       <c r="F299" s="19"/>
       <c r="G299" s="17"/>
     </row>
-    <row r="300" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B300" s="17"/>
       <c r="C300" s="17"/>
       <c r="D300" s="17"/>
@@ -9210,7 +9199,7 @@
       <c r="F300" s="19"/>
       <c r="G300" s="17"/>
     </row>
-    <row r="301" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B301" s="17"/>
       <c r="C301" s="17"/>
       <c r="D301" s="17"/>
@@ -9218,7 +9207,7 @@
       <c r="F301" s="19"/>
       <c r="G301" s="17"/>
     </row>
-    <row r="302" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B302" s="17"/>
       <c r="C302" s="17"/>
       <c r="D302" s="17"/>
@@ -9226,7 +9215,7 @@
       <c r="F302" s="19"/>
       <c r="G302" s="17"/>
     </row>
-    <row r="303" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B303" s="17"/>
       <c r="C303" s="17"/>
       <c r="D303" s="17"/>
@@ -9234,7 +9223,7 @@
       <c r="F303" s="19"/>
       <c r="G303" s="17"/>
     </row>
-    <row r="304" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B304" s="17"/>
       <c r="C304" s="17"/>
       <c r="D304" s="17"/>
@@ -9242,7 +9231,7 @@
       <c r="F304" s="19"/>
       <c r="G304" s="17"/>
     </row>
-    <row r="305" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B305" s="17"/>
       <c r="C305" s="17"/>
       <c r="D305" s="17"/>
@@ -9250,7 +9239,7 @@
       <c r="F305" s="19"/>
       <c r="G305" s="17"/>
     </row>
-    <row r="306" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B306" s="17"/>
       <c r="C306" s="17"/>
       <c r="D306" s="17"/>
@@ -9258,7 +9247,7 @@
       <c r="F306" s="19"/>
       <c r="G306" s="17"/>
     </row>
-    <row r="307" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B307" s="17"/>
       <c r="C307" s="17"/>
       <c r="D307" s="17"/>
@@ -9266,7 +9255,7 @@
       <c r="F307" s="19"/>
       <c r="G307" s="17"/>
     </row>
-    <row r="308" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B308" s="17"/>
       <c r="C308" s="17"/>
       <c r="D308" s="17"/>
@@ -9274,7 +9263,7 @@
       <c r="F308" s="19"/>
       <c r="G308" s="17"/>
     </row>
-    <row r="309" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B309" s="17"/>
       <c r="C309" s="17"/>
       <c r="D309" s="17"/>
@@ -9282,7 +9271,7 @@
       <c r="F309" s="19"/>
       <c r="G309" s="17"/>
     </row>
-    <row r="310" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B310" s="17"/>
       <c r="C310" s="17"/>
       <c r="D310" s="17"/>
@@ -9290,7 +9279,7 @@
       <c r="F310" s="19"/>
       <c r="G310" s="17"/>
     </row>
-    <row r="311" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B311" s="17"/>
       <c r="C311" s="17"/>
       <c r="D311" s="17"/>
@@ -9298,7 +9287,7 @@
       <c r="F311" s="19"/>
       <c r="G311" s="17"/>
     </row>
-    <row r="312" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B312" s="17"/>
       <c r="C312" s="17"/>
       <c r="D312" s="17"/>
@@ -9306,7 +9295,7 @@
       <c r="F312" s="19"/>
       <c r="G312" s="17"/>
     </row>
-    <row r="313" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B313" s="17"/>
       <c r="C313" s="17"/>
       <c r="D313" s="17"/>
@@ -9314,7 +9303,7 @@
       <c r="F313" s="19"/>
       <c r="G313" s="17"/>
     </row>
-    <row r="314" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B314" s="17"/>
       <c r="C314" s="17"/>
       <c r="D314" s="17"/>
@@ -9322,7 +9311,7 @@
       <c r="F314" s="19"/>
       <c r="G314" s="17"/>
     </row>
-    <row r="315" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B315" s="17"/>
       <c r="C315" s="17"/>
       <c r="D315" s="17"/>
@@ -9330,7 +9319,7 @@
       <c r="F315" s="19"/>
       <c r="G315" s="17"/>
     </row>
-    <row r="316" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B316" s="17"/>
       <c r="C316" s="17"/>
       <c r="D316" s="17"/>
@@ -9338,7 +9327,7 @@
       <c r="F316" s="19"/>
       <c r="G316" s="17"/>
     </row>
-    <row r="317" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B317" s="17"/>
       <c r="C317" s="17"/>
       <c r="D317" s="17"/>
@@ -9346,7 +9335,7 @@
       <c r="F317" s="19"/>
       <c r="G317" s="17"/>
     </row>
-    <row r="318" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B318" s="17"/>
       <c r="C318" s="17"/>
       <c r="D318" s="17"/>
@@ -9354,7 +9343,7 @@
       <c r="F318" s="19"/>
       <c r="G318" s="17"/>
     </row>
-    <row r="319" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B319" s="17"/>
       <c r="C319" s="17"/>
       <c r="D319" s="17"/>
@@ -9362,7 +9351,7 @@
       <c r="F319" s="19"/>
       <c r="G319" s="17"/>
     </row>
-    <row r="320" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B320" s="17"/>
       <c r="C320" s="17"/>
       <c r="D320" s="17"/>
@@ -9370,7 +9359,7 @@
       <c r="F320" s="19"/>
       <c r="G320" s="17"/>
     </row>
-    <row r="321" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B321" s="17"/>
       <c r="C321" s="17"/>
       <c r="D321" s="17"/>
@@ -9378,7 +9367,7 @@
       <c r="F321" s="19"/>
       <c r="G321" s="17"/>
     </row>
-    <row r="322" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B322" s="17"/>
       <c r="C322" s="17"/>
       <c r="D322" s="17"/>
@@ -9386,7 +9375,7 @@
       <c r="F322" s="19"/>
       <c r="G322" s="17"/>
     </row>
-    <row r="323" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B323" s="17"/>
       <c r="C323" s="17"/>
       <c r="D323" s="17"/>
@@ -9394,7 +9383,7 @@
       <c r="F323" s="19"/>
       <c r="G323" s="17"/>
     </row>
-    <row r="324" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B324" s="17"/>
       <c r="C324" s="17"/>
       <c r="D324" s="17"/>
@@ -9402,7 +9391,7 @@
       <c r="F324" s="19"/>
       <c r="G324" s="17"/>
     </row>
-    <row r="325" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B325" s="17"/>
       <c r="C325" s="17"/>
       <c r="D325" s="17"/>
@@ -9410,7 +9399,7 @@
       <c r="F325" s="19"/>
       <c r="G325" s="17"/>
     </row>
-    <row r="326" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B326" s="17"/>
       <c r="C326" s="17"/>
       <c r="D326" s="17"/>
@@ -9418,7 +9407,7 @@
       <c r="F326" s="19"/>
       <c r="G326" s="17"/>
     </row>
-    <row r="327" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B327" s="17"/>
       <c r="C327" s="17"/>
       <c r="D327" s="17"/>
@@ -9426,7 +9415,7 @@
       <c r="F327" s="19"/>
       <c r="G327" s="17"/>
     </row>
-    <row r="328" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B328" s="17"/>
       <c r="C328" s="17"/>
       <c r="D328" s="17"/>
@@ -9434,7 +9423,7 @@
       <c r="F328" s="19"/>
       <c r="G328" s="17"/>
     </row>
-    <row r="329" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B329" s="17"/>
       <c r="C329" s="17"/>
       <c r="D329" s="17"/>
@@ -9442,7 +9431,7 @@
       <c r="F329" s="19"/>
       <c r="G329" s="17"/>
     </row>
-    <row r="330" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B330" s="17"/>
       <c r="C330" s="17"/>
       <c r="D330" s="17"/>
@@ -9450,7 +9439,7 @@
       <c r="F330" s="19"/>
       <c r="G330" s="17"/>
     </row>
-    <row r="331" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B331" s="17"/>
       <c r="C331" s="17"/>
       <c r="D331" s="17"/>
@@ -9458,7 +9447,7 @@
       <c r="F331" s="19"/>
       <c r="G331" s="17"/>
     </row>
-    <row r="332" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B332" s="17"/>
       <c r="C332" s="17"/>
       <c r="D332" s="17"/>
@@ -9466,7 +9455,7 @@
       <c r="F332" s="19"/>
       <c r="G332" s="17"/>
     </row>
-    <row r="333" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B333" s="17"/>
       <c r="C333" s="17"/>
       <c r="D333" s="17"/>
@@ -9474,7 +9463,7 @@
       <c r="F333" s="19"/>
       <c r="G333" s="17"/>
     </row>
-    <row r="334" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B334" s="17"/>
       <c r="C334" s="17"/>
       <c r="D334" s="17"/>
@@ -9482,7 +9471,7 @@
       <c r="F334" s="19"/>
       <c r="G334" s="17"/>
     </row>
-    <row r="335" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B335" s="17"/>
       <c r="C335" s="17"/>
       <c r="D335" s="17"/>
@@ -9490,7 +9479,7 @@
       <c r="F335" s="19"/>
       <c r="G335" s="17"/>
     </row>
-    <row r="336" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B336" s="17"/>
       <c r="C336" s="17"/>
       <c r="D336" s="17"/>
@@ -9498,7 +9487,7 @@
       <c r="F336" s="19"/>
       <c r="G336" s="17"/>
     </row>
-    <row r="337" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B337" s="17"/>
       <c r="C337" s="17"/>
       <c r="D337" s="17"/>
@@ -9506,7 +9495,7 @@
       <c r="F337" s="19"/>
       <c r="G337" s="17"/>
     </row>
-    <row r="338" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B338" s="17"/>
       <c r="C338" s="17"/>
       <c r="D338" s="17"/>
@@ -9514,7 +9503,7 @@
       <c r="F338" s="19"/>
       <c r="G338" s="17"/>
     </row>
-    <row r="339" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B339" s="17"/>
       <c r="C339" s="17"/>
       <c r="D339" s="17"/>
@@ -9522,7 +9511,7 @@
       <c r="F339" s="19"/>
       <c r="G339" s="17"/>
     </row>
-    <row r="340" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B340" s="17"/>
       <c r="C340" s="17"/>
       <c r="D340" s="17"/>
@@ -9530,7 +9519,7 @@
       <c r="F340" s="19"/>
       <c r="G340" s="17"/>
     </row>
-    <row r="341" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B341" s="17"/>
       <c r="C341" s="17"/>
       <c r="D341" s="17"/>
@@ -9538,7 +9527,7 @@
       <c r="F341" s="19"/>
       <c r="G341" s="17"/>
     </row>
-    <row r="342" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B342" s="17"/>
       <c r="C342" s="17"/>
       <c r="D342" s="17"/>
@@ -9546,7 +9535,7 @@
       <c r="F342" s="19"/>
       <c r="G342" s="17"/>
     </row>
-    <row r="343" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B343" s="17"/>
       <c r="C343" s="17"/>
       <c r="D343" s="17"/>
@@ -9554,7 +9543,7 @@
       <c r="F343" s="19"/>
       <c r="G343" s="17"/>
     </row>
-    <row r="344" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B344" s="17"/>
       <c r="C344" s="17"/>
       <c r="D344" s="17"/>
@@ -9562,7 +9551,7 @@
       <c r="F344" s="19"/>
       <c r="G344" s="17"/>
     </row>
-    <row r="345" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B345" s="17"/>
       <c r="C345" s="17"/>
       <c r="D345" s="17"/>
@@ -9570,7 +9559,7 @@
       <c r="F345" s="19"/>
       <c r="G345" s="17"/>
     </row>
-    <row r="346" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B346" s="17"/>
       <c r="C346" s="17"/>
       <c r="D346" s="17"/>
@@ -9578,7 +9567,7 @@
       <c r="F346" s="19"/>
       <c r="G346" s="17"/>
     </row>
-    <row r="347" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B347" s="17"/>
       <c r="C347" s="17"/>
       <c r="D347" s="17"/>
@@ -9586,7 +9575,7 @@
       <c r="F347" s="19"/>
       <c r="G347" s="17"/>
     </row>
-    <row r="348" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B348" s="17"/>
       <c r="C348" s="17"/>
       <c r="D348" s="17"/>
@@ -9594,7 +9583,7 @@
       <c r="F348" s="19"/>
       <c r="G348" s="17"/>
     </row>
-    <row r="349" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B349" s="17"/>
       <c r="C349" s="17"/>
       <c r="D349" s="17"/>
@@ -9602,7 +9591,7 @@
       <c r="F349" s="19"/>
       <c r="G349" s="17"/>
     </row>
-    <row r="350" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B350" s="17"/>
       <c r="C350" s="17"/>
       <c r="D350" s="17"/>
@@ -9610,7 +9599,7 @@
       <c r="F350" s="19"/>
       <c r="G350" s="17"/>
     </row>
-    <row r="351" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B351" s="17"/>
       <c r="C351" s="17"/>
       <c r="D351" s="17"/>
@@ -9618,7 +9607,7 @@
       <c r="F351" s="19"/>
       <c r="G351" s="17"/>
     </row>
-    <row r="352" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B352" s="17"/>
       <c r="C352" s="17"/>
       <c r="D352" s="17"/>
@@ -9626,7 +9615,7 @@
       <c r="F352" s="19"/>
       <c r="G352" s="17"/>
     </row>
-    <row r="353" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="17"/>
       <c r="C353" s="17"/>
       <c r="D353" s="17"/>
@@ -9634,7 +9623,7 @@
       <c r="F353" s="19"/>
       <c r="G353" s="17"/>
     </row>
-    <row r="354" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B354" s="17"/>
       <c r="C354" s="17"/>
       <c r="D354" s="17"/>
@@ -9642,7 +9631,7 @@
       <c r="F354" s="19"/>
       <c r="G354" s="17"/>
     </row>
-    <row r="355" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B355" s="17"/>
       <c r="C355" s="17"/>
       <c r="D355" s="17"/>
@@ -9650,7 +9639,7 @@
       <c r="F355" s="19"/>
       <c r="G355" s="17"/>
     </row>
-    <row r="356" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="17"/>
       <c r="C356" s="17"/>
       <c r="D356" s="17"/>
@@ -9658,7 +9647,7 @@
       <c r="F356" s="19"/>
       <c r="G356" s="17"/>
     </row>
-    <row r="357" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="17"/>
       <c r="C357" s="17"/>
       <c r="D357" s="17"/>
@@ -9666,7 +9655,7 @@
       <c r="F357" s="19"/>
       <c r="G357" s="17"/>
     </row>
-    <row r="358" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="17"/>
       <c r="C358" s="17"/>
       <c r="D358" s="17"/>
@@ -9674,7 +9663,7 @@
       <c r="F358" s="19"/>
       <c r="G358" s="17"/>
     </row>
-    <row r="359" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="17"/>
       <c r="C359" s="17"/>
       <c r="D359" s="17"/>
@@ -9682,7 +9671,7 @@
       <c r="F359" s="19"/>
       <c r="G359" s="17"/>
     </row>
-    <row r="360" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="17"/>
       <c r="C360" s="17"/>
       <c r="D360" s="17"/>
@@ -9690,7 +9679,7 @@
       <c r="F360" s="19"/>
       <c r="G360" s="17"/>
     </row>
-    <row r="361" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="17"/>
       <c r="C361" s="17"/>
       <c r="D361" s="17"/>
@@ -9698,7 +9687,7 @@
       <c r="F361" s="19"/>
       <c r="G361" s="17"/>
     </row>
-    <row r="362" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="17"/>
       <c r="C362" s="17"/>
       <c r="D362" s="17"/>
@@ -9706,7 +9695,7 @@
       <c r="F362" s="19"/>
       <c r="G362" s="17"/>
     </row>
-    <row r="363" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="17"/>
       <c r="C363" s="17"/>
       <c r="D363" s="17"/>
@@ -9714,7 +9703,7 @@
       <c r="F363" s="19"/>
       <c r="G363" s="17"/>
     </row>
-    <row r="364" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="17"/>
       <c r="C364" s="17"/>
       <c r="D364" s="17"/>
@@ -9722,7 +9711,7 @@
       <c r="F364" s="19"/>
       <c r="G364" s="17"/>
     </row>
-    <row r="365" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="17"/>
       <c r="C365" s="17"/>
       <c r="D365" s="17"/>
@@ -9730,7 +9719,7 @@
       <c r="F365" s="19"/>
       <c r="G365" s="17"/>
     </row>
-    <row r="366" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="17"/>
       <c r="C366" s="17"/>
       <c r="D366" s="17"/>
@@ -9738,7 +9727,7 @@
       <c r="F366" s="19"/>
       <c r="G366" s="17"/>
     </row>
-    <row r="367" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="17"/>
       <c r="C367" s="17"/>
       <c r="D367" s="17"/>
@@ -9746,7 +9735,7 @@
       <c r="F367" s="19"/>
       <c r="G367" s="17"/>
     </row>
-    <row r="368" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="17"/>
       <c r="C368" s="17"/>
       <c r="D368" s="17"/>
@@ -9754,7 +9743,7 @@
       <c r="F368" s="19"/>
       <c r="G368" s="17"/>
     </row>
-    <row r="369" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="17"/>
       <c r="C369" s="17"/>
       <c r="D369" s="17"/>
@@ -9762,7 +9751,7 @@
       <c r="F369" s="19"/>
       <c r="G369" s="17"/>
     </row>
-    <row r="370" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="17"/>
       <c r="C370" s="17"/>
       <c r="D370" s="17"/>
@@ -9770,7 +9759,7 @@
       <c r="F370" s="19"/>
       <c r="G370" s="17"/>
     </row>
-    <row r="371" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="17"/>
       <c r="C371" s="17"/>
       <c r="D371" s="17"/>
@@ -9778,7 +9767,7 @@
       <c r="F371" s="19"/>
       <c r="G371" s="17"/>
     </row>
-    <row r="372" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="17"/>
       <c r="C372" s="17"/>
       <c r="D372" s="17"/>
@@ -9786,7 +9775,7 @@
       <c r="F372" s="19"/>
       <c r="G372" s="17"/>
     </row>
-    <row r="373" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="17"/>
       <c r="C373" s="17"/>
       <c r="D373" s="17"/>
@@ -9794,7 +9783,7 @@
       <c r="F373" s="19"/>
       <c r="G373" s="17"/>
     </row>
-    <row r="374" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="17"/>
       <c r="C374" s="17"/>
       <c r="D374" s="17"/>
@@ -9802,7 +9791,7 @@
       <c r="F374" s="19"/>
       <c r="G374" s="17"/>
     </row>
-    <row r="375" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="17"/>
       <c r="C375" s="17"/>
       <c r="D375" s="17"/>
@@ -9810,7 +9799,7 @@
       <c r="F375" s="19"/>
       <c r="G375" s="17"/>
     </row>
-    <row r="376" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B376" s="17"/>
       <c r="C376" s="17"/>
       <c r="D376" s="17"/>
@@ -9818,7 +9807,7 @@
       <c r="F376" s="19"/>
       <c r="G376" s="17"/>
     </row>
-    <row r="377" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B377" s="17"/>
       <c r="C377" s="17"/>
       <c r="D377" s="17"/>
@@ -9826,7 +9815,7 @@
       <c r="F377" s="19"/>
       <c r="G377" s="17"/>
     </row>
-    <row r="378" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B378" s="17"/>
       <c r="C378" s="17"/>
       <c r="D378" s="17"/>
@@ -9834,7 +9823,7 @@
       <c r="F378" s="19"/>
       <c r="G378" s="17"/>
     </row>
-    <row r="379" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B379" s="17"/>
       <c r="C379" s="17"/>
       <c r="D379" s="17"/>
@@ -9842,7 +9831,7 @@
       <c r="F379" s="19"/>
       <c r="G379" s="17"/>
     </row>
-    <row r="380" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="17"/>
       <c r="C380" s="17"/>
       <c r="D380" s="17"/>
@@ -9850,7 +9839,7 @@
       <c r="F380" s="19"/>
       <c r="G380" s="17"/>
     </row>
-    <row r="381" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B381" s="17"/>
       <c r="C381" s="17"/>
       <c r="D381" s="17"/>
@@ -9858,7 +9847,7 @@
       <c r="F381" s="19"/>
       <c r="G381" s="17"/>
     </row>
-    <row r="382" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B382" s="17"/>
       <c r="C382" s="17"/>
       <c r="D382" s="17"/>
@@ -9866,7 +9855,7 @@
       <c r="F382" s="19"/>
       <c r="G382" s="17"/>
     </row>
-    <row r="383" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="17"/>
       <c r="C383" s="17"/>
       <c r="D383" s="17"/>
@@ -9874,7 +9863,7 @@
       <c r="F383" s="19"/>
       <c r="G383" s="17"/>
     </row>
-    <row r="384" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="17"/>
       <c r="C384" s="17"/>
       <c r="D384" s="17"/>
@@ -9882,7 +9871,7 @@
       <c r="F384" s="19"/>
       <c r="G384" s="17"/>
     </row>
-    <row r="385" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="17"/>
       <c r="C385" s="17"/>
       <c r="D385" s="17"/>
@@ -9890,7 +9879,7 @@
       <c r="F385" s="19"/>
       <c r="G385" s="17"/>
     </row>
-    <row r="386" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="17"/>
       <c r="C386" s="17"/>
       <c r="D386" s="17"/>
@@ -9898,7 +9887,7 @@
       <c r="F386" s="19"/>
       <c r="G386" s="17"/>
     </row>
-    <row r="387" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="17"/>
       <c r="C387" s="17"/>
       <c r="D387" s="17"/>
@@ -9906,7 +9895,7 @@
       <c r="F387" s="19"/>
       <c r="G387" s="17"/>
     </row>
-    <row r="388" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="17"/>
       <c r="C388" s="17"/>
       <c r="D388" s="17"/>
@@ -9914,7 +9903,7 @@
       <c r="F388" s="19"/>
       <c r="G388" s="17"/>
     </row>
-    <row r="389" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="17"/>
       <c r="C389" s="17"/>
       <c r="D389" s="17"/>
@@ -9922,7 +9911,7 @@
       <c r="F389" s="19"/>
       <c r="G389" s="17"/>
     </row>
-    <row r="390" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="17"/>
       <c r="C390" s="17"/>
       <c r="D390" s="17"/>
@@ -9930,7 +9919,7 @@
       <c r="F390" s="19"/>
       <c r="G390" s="17"/>
     </row>
-    <row r="391" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="17"/>
       <c r="C391" s="17"/>
       <c r="D391" s="17"/>
@@ -9938,7 +9927,7 @@
       <c r="F391" s="19"/>
       <c r="G391" s="17"/>
     </row>
-    <row r="392" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="17"/>
       <c r="C392" s="17"/>
       <c r="D392" s="17"/>
@@ -9946,7 +9935,7 @@
       <c r="F392" s="19"/>
       <c r="G392" s="17"/>
     </row>
-    <row r="393" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="17"/>
       <c r="C393" s="17"/>
       <c r="D393" s="17"/>
@@ -9954,7 +9943,7 @@
       <c r="F393" s="19"/>
       <c r="G393" s="17"/>
     </row>
-    <row r="394" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="17"/>
       <c r="C394" s="17"/>
       <c r="D394" s="17"/>
@@ -9962,7 +9951,7 @@
       <c r="F394" s="19"/>
       <c r="G394" s="17"/>
     </row>
-    <row r="395" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="17"/>
       <c r="C395" s="17"/>
       <c r="D395" s="17"/>
@@ -9970,7 +9959,7 @@
       <c r="F395" s="19"/>
       <c r="G395" s="17"/>
     </row>
-    <row r="396" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="17"/>
       <c r="C396" s="17"/>
       <c r="D396" s="17"/>
@@ -9978,7 +9967,7 @@
       <c r="F396" s="19"/>
       <c r="G396" s="17"/>
     </row>
-    <row r="397" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="17"/>
       <c r="C397" s="17"/>
       <c r="D397" s="17"/>
@@ -9986,7 +9975,7 @@
       <c r="F397" s="19"/>
       <c r="G397" s="17"/>
     </row>
-    <row r="398" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="17"/>
       <c r="C398" s="17"/>
       <c r="D398" s="17"/>
@@ -9994,7 +9983,7 @@
       <c r="F398" s="19"/>
       <c r="G398" s="17"/>
     </row>
-    <row r="399" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="17"/>
       <c r="C399" s="17"/>
       <c r="D399" s="17"/>
@@ -10002,7 +9991,7 @@
       <c r="F399" s="19"/>
       <c r="G399" s="17"/>
     </row>
-    <row r="400" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B400" s="17"/>
       <c r="C400" s="17"/>
       <c r="D400" s="17"/>
@@ -10010,7 +9999,7 @@
       <c r="F400" s="19"/>
       <c r="G400" s="17"/>
     </row>
-    <row r="401" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B401" s="17"/>
       <c r="C401" s="17"/>
       <c r="D401" s="17"/>
@@ -10018,7 +10007,7 @@
       <c r="F401" s="19"/>
       <c r="G401" s="17"/>
     </row>
-    <row r="402" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B402" s="17"/>
       <c r="C402" s="17"/>
       <c r="D402" s="17"/>
@@ -10026,7 +10015,7 @@
       <c r="F402" s="19"/>
       <c r="G402" s="17"/>
     </row>
-    <row r="403" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B403" s="17"/>
       <c r="C403" s="17"/>
       <c r="D403" s="17"/>
@@ -10034,7 +10023,7 @@
       <c r="F403" s="19"/>
       <c r="G403" s="17"/>
     </row>
-    <row r="404" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B404" s="17"/>
       <c r="C404" s="17"/>
       <c r="D404" s="17"/>
@@ -10042,7 +10031,7 @@
       <c r="F404" s="19"/>
       <c r="G404" s="17"/>
     </row>
-    <row r="405" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B405" s="17"/>
       <c r="C405" s="17"/>
       <c r="D405" s="17"/>
@@ -10050,7 +10039,7 @@
       <c r="F405" s="19"/>
       <c r="G405" s="17"/>
     </row>
-    <row r="406" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B406" s="17"/>
       <c r="C406" s="17"/>
       <c r="D406" s="17"/>
@@ -10058,7 +10047,7 @@
       <c r="F406" s="19"/>
       <c r="G406" s="17"/>
     </row>
-    <row r="407" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B407" s="17"/>
       <c r="C407" s="17"/>
       <c r="D407" s="17"/>
@@ -10066,7 +10055,7 @@
       <c r="F407" s="19"/>
       <c r="G407" s="17"/>
     </row>
-    <row r="408" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B408" s="17"/>
       <c r="C408" s="17"/>
       <c r="D408" s="17"/>
@@ -10074,7 +10063,7 @@
       <c r="F408" s="19"/>
       <c r="G408" s="17"/>
     </row>
-    <row r="409" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B409" s="17"/>
       <c r="C409" s="17"/>
       <c r="D409" s="17"/>
@@ -10082,7 +10071,7 @@
       <c r="F409" s="19"/>
       <c r="G409" s="17"/>
     </row>
-    <row r="410" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B410" s="17"/>
       <c r="C410" s="17"/>
       <c r="D410" s="17"/>
@@ -10090,7 +10079,7 @@
       <c r="F410" s="19"/>
       <c r="G410" s="17"/>
     </row>
-    <row r="411" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B411" s="17"/>
       <c r="C411" s="17"/>
       <c r="D411" s="17"/>
@@ -10098,7 +10087,7 @@
       <c r="F411" s="19"/>
       <c r="G411" s="17"/>
     </row>
-    <row r="412" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B412" s="17"/>
       <c r="C412" s="17"/>
       <c r="D412" s="17"/>
@@ -10106,7 +10095,7 @@
       <c r="F412" s="19"/>
       <c r="G412" s="17"/>
     </row>
-    <row r="413" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B413" s="17"/>
       <c r="C413" s="17"/>
       <c r="D413" s="17"/>
@@ -10114,7 +10103,7 @@
       <c r="F413" s="19"/>
       <c r="G413" s="17"/>
     </row>
-    <row r="414" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B414" s="17"/>
       <c r="C414" s="17"/>
       <c r="D414" s="17"/>
@@ -10122,7 +10111,7 @@
       <c r="F414" s="19"/>
       <c r="G414" s="17"/>
     </row>
-    <row r="415" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B415" s="17"/>
       <c r="C415" s="17"/>
       <c r="D415" s="17"/>
@@ -10130,7 +10119,7 @@
       <c r="F415" s="19"/>
       <c r="G415" s="17"/>
     </row>
-    <row r="416" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B416" s="17"/>
       <c r="C416" s="17"/>
       <c r="D416" s="17"/>
@@ -10138,7 +10127,7 @@
       <c r="F416" s="19"/>
       <c r="G416" s="17"/>
     </row>
-    <row r="417" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B417" s="17"/>
       <c r="C417" s="17"/>
       <c r="D417" s="17"/>
@@ -10146,7 +10135,7 @@
       <c r="F417" s="19"/>
       <c r="G417" s="17"/>
     </row>
-    <row r="418" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B418" s="17"/>
       <c r="C418" s="17"/>
       <c r="D418" s="17"/>
@@ -10154,7 +10143,7 @@
       <c r="F418" s="19"/>
       <c r="G418" s="17"/>
     </row>
-    <row r="419" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B419" s="17"/>
       <c r="C419" s="17"/>
       <c r="D419" s="17"/>
@@ -10162,7 +10151,7 @@
       <c r="F419" s="19"/>
       <c r="G419" s="17"/>
     </row>
-    <row r="420" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B420" s="17"/>
       <c r="C420" s="17"/>
       <c r="D420" s="17"/>
@@ -10170,7 +10159,7 @@
       <c r="F420" s="19"/>
       <c r="G420" s="17"/>
     </row>
-    <row r="421" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B421" s="17"/>
       <c r="C421" s="17"/>
       <c r="D421" s="17"/>
@@ -10178,7 +10167,7 @@
       <c r="F421" s="19"/>
       <c r="G421" s="17"/>
     </row>
-    <row r="422" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B422" s="17"/>
       <c r="C422" s="17"/>
       <c r="D422" s="17"/>
@@ -10186,7 +10175,7 @@
       <c r="F422" s="19"/>
       <c r="G422" s="17"/>
     </row>
-    <row r="423" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B423" s="17"/>
       <c r="C423" s="17"/>
       <c r="D423" s="17"/>
@@ -10194,7 +10183,7 @@
       <c r="F423" s="19"/>
       <c r="G423" s="17"/>
     </row>
-    <row r="424" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B424" s="17"/>
       <c r="C424" s="17"/>
       <c r="D424" s="17"/>
@@ -10202,7 +10191,7 @@
       <c r="F424" s="19"/>
       <c r="G424" s="17"/>
     </row>
-    <row r="425" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B425" s="17"/>
       <c r="C425" s="17"/>
       <c r="D425" s="17"/>
@@ -10210,7 +10199,7 @@
       <c r="F425" s="19"/>
       <c r="G425" s="17"/>
     </row>
-    <row r="426" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B426" s="17"/>
       <c r="C426" s="17"/>
       <c r="D426" s="17"/>
@@ -10218,7 +10207,7 @@
       <c r="F426" s="19"/>
       <c r="G426" s="17"/>
     </row>
-    <row r="427" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B427" s="17"/>
       <c r="C427" s="17"/>
       <c r="D427" s="17"/>
@@ -10226,7 +10215,7 @@
       <c r="F427" s="19"/>
       <c r="G427" s="17"/>
     </row>
-    <row r="428" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B428" s="17"/>
       <c r="C428" s="17"/>
       <c r="D428" s="17"/>
@@ -10234,7 +10223,7 @@
       <c r="F428" s="19"/>
       <c r="G428" s="17"/>
     </row>
-    <row r="429" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B429" s="17"/>
       <c r="C429" s="17"/>
       <c r="D429" s="17"/>
@@ -10242,7 +10231,7 @@
       <c r="F429" s="19"/>
       <c r="G429" s="17"/>
     </row>
-    <row r="430" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B430" s="17"/>
       <c r="C430" s="17"/>
       <c r="D430" s="17"/>
@@ -10250,7 +10239,7 @@
       <c r="F430" s="19"/>
       <c r="G430" s="17"/>
     </row>
-    <row r="431" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B431" s="17"/>
       <c r="C431" s="17"/>
       <c r="D431" s="17"/>
@@ -10258,7 +10247,7 @@
       <c r="F431" s="19"/>
       <c r="G431" s="17"/>
     </row>
-    <row r="432" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B432" s="17"/>
       <c r="C432" s="17"/>
       <c r="D432" s="17"/>
@@ -10266,7 +10255,7 @@
       <c r="F432" s="19"/>
       <c r="G432" s="17"/>
     </row>
-    <row r="433" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B433" s="17"/>
       <c r="C433" s="17"/>
       <c r="D433" s="17"/>
@@ -10274,7 +10263,7 @@
       <c r="F433" s="19"/>
       <c r="G433" s="17"/>
     </row>
-    <row r="434" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B434" s="17"/>
       <c r="C434" s="17"/>
       <c r="D434" s="17"/>
@@ -10282,7 +10271,7 @@
       <c r="F434" s="19"/>
       <c r="G434" s="17"/>
     </row>
-    <row r="435" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B435" s="17"/>
       <c r="C435" s="17"/>
       <c r="D435" s="17"/>
@@ -10290,7 +10279,7 @@
       <c r="F435" s="19"/>
       <c r="G435" s="17"/>
     </row>
-    <row r="436" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B436" s="17"/>
       <c r="C436" s="17"/>
       <c r="D436" s="17"/>
@@ -10298,7 +10287,7 @@
       <c r="F436" s="19"/>
       <c r="G436" s="17"/>
     </row>
-    <row r="437" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B437" s="17"/>
       <c r="C437" s="17"/>
       <c r="D437" s="17"/>
@@ -10306,7 +10295,7 @@
       <c r="F437" s="19"/>
       <c r="G437" s="17"/>
     </row>
-    <row r="438" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B438" s="17"/>
       <c r="C438" s="17"/>
       <c r="D438" s="17"/>
@@ -10314,7 +10303,7 @@
       <c r="F438" s="19"/>
       <c r="G438" s="17"/>
     </row>
-    <row r="439" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B439" s="17"/>
       <c r="C439" s="17"/>
       <c r="D439" s="17"/>
@@ -10322,7 +10311,7 @@
       <c r="F439" s="19"/>
       <c r="G439" s="17"/>
     </row>
-    <row r="440" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B440" s="17"/>
       <c r="C440" s="17"/>
       <c r="D440" s="17"/>
@@ -10330,7 +10319,7 @@
       <c r="F440" s="19"/>
       <c r="G440" s="17"/>
     </row>
-    <row r="441" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B441" s="17"/>
       <c r="C441" s="17"/>
       <c r="D441" s="17"/>
@@ -10338,7 +10327,7 @@
       <c r="F441" s="19"/>
       <c r="G441" s="17"/>
     </row>
-    <row r="442" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B442" s="17"/>
       <c r="C442" s="17"/>
       <c r="D442" s="17"/>
@@ -10346,7 +10335,7 @@
       <c r="F442" s="19"/>
       <c r="G442" s="17"/>
     </row>
-    <row r="443" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B443" s="17"/>
       <c r="C443" s="17"/>
       <c r="D443" s="17"/>
@@ -10354,7 +10343,7 @@
       <c r="F443" s="19"/>
       <c r="G443" s="17"/>
     </row>
-    <row r="444" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B444" s="17"/>
       <c r="C444" s="17"/>
       <c r="D444" s="17"/>
@@ -10362,7 +10351,7 @@
       <c r="F444" s="19"/>
       <c r="G444" s="17"/>
     </row>
-    <row r="445" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B445" s="17"/>
       <c r="C445" s="17"/>
       <c r="D445" s="17"/>
@@ -10370,7 +10359,7 @@
       <c r="F445" s="19"/>
       <c r="G445" s="17"/>
     </row>
-    <row r="446" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B446" s="17"/>
       <c r="C446" s="17"/>
       <c r="D446" s="17"/>
@@ -10378,7 +10367,7 @@
       <c r="F446" s="19"/>
       <c r="G446" s="17"/>
     </row>
-    <row r="447" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B447" s="17"/>
       <c r="C447" s="17"/>
       <c r="D447" s="17"/>
@@ -10386,7 +10375,7 @@
       <c r="F447" s="19"/>
       <c r="G447" s="17"/>
     </row>
-    <row r="448" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B448" s="17"/>
       <c r="C448" s="17"/>
       <c r="D448" s="17"/>
@@ -10394,7 +10383,7 @@
       <c r="F448" s="19"/>
       <c r="G448" s="17"/>
     </row>
-    <row r="449" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B449" s="17"/>
       <c r="C449" s="17"/>
       <c r="D449" s="17"/>
@@ -10402,7 +10391,7 @@
       <c r="F449" s="19"/>
       <c r="G449" s="17"/>
     </row>
-    <row r="450" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B450" s="17"/>
       <c r="C450" s="17"/>
       <c r="D450" s="17"/>
@@ -10410,7 +10399,7 @@
       <c r="F450" s="19"/>
       <c r="G450" s="17"/>
     </row>
-    <row r="451" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B451" s="17"/>
       <c r="C451" s="17"/>
       <c r="D451" s="17"/>
@@ -10418,7 +10407,7 @@
       <c r="F451" s="19"/>
       <c r="G451" s="17"/>
     </row>
-    <row r="452" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B452" s="17"/>
       <c r="C452" s="17"/>
       <c r="D452" s="17"/>
@@ -10426,7 +10415,7 @@
       <c r="F452" s="19"/>
       <c r="G452" s="17"/>
     </row>
-    <row r="453" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B453" s="17"/>
       <c r="C453" s="17"/>
       <c r="D453" s="17"/>
@@ -10434,7 +10423,7 @@
       <c r="F453" s="19"/>
       <c r="G453" s="17"/>
     </row>
-    <row r="454" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B454" s="17"/>
       <c r="C454" s="17"/>
       <c r="D454" s="17"/>
@@ -10442,7 +10431,7 @@
       <c r="F454" s="19"/>
       <c r="G454" s="17"/>
     </row>
-    <row r="455" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B455" s="17"/>
       <c r="C455" s="17"/>
       <c r="D455" s="17"/>
@@ -10450,7 +10439,7 @@
       <c r="F455" s="19"/>
       <c r="G455" s="17"/>
     </row>
-    <row r="456" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B456" s="17"/>
       <c r="C456" s="17"/>
       <c r="D456" s="17"/>
@@ -10458,7 +10447,7 @@
       <c r="F456" s="19"/>
       <c r="G456" s="17"/>
     </row>
-    <row r="457" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B457" s="17"/>
       <c r="C457" s="17"/>
       <c r="D457" s="17"/>
@@ -10466,7 +10455,7 @@
       <c r="F457" s="19"/>
       <c r="G457" s="17"/>
     </row>
-    <row r="458" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B458" s="17"/>
       <c r="C458" s="17"/>
       <c r="D458" s="17"/>
@@ -10474,7 +10463,7 @@
       <c r="F458" s="19"/>
       <c r="G458" s="17"/>
     </row>
-    <row r="459" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B459" s="17"/>
       <c r="C459" s="17"/>
       <c r="D459" s="17"/>
@@ -10482,7 +10471,7 @@
       <c r="F459" s="19"/>
       <c r="G459" s="17"/>
     </row>
-    <row r="460" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B460" s="17"/>
       <c r="C460" s="17"/>
       <c r="D460" s="17"/>
@@ -10490,7 +10479,7 @@
       <c r="F460" s="19"/>
       <c r="G460" s="17"/>
     </row>
-    <row r="461" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B461" s="17"/>
       <c r="C461" s="17"/>
       <c r="D461" s="17"/>
@@ -10498,7 +10487,7 @@
       <c r="F461" s="19"/>
       <c r="G461" s="17"/>
     </row>
-    <row r="462" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B462" s="17"/>
       <c r="C462" s="17"/>
       <c r="D462" s="17"/>
@@ -10506,7 +10495,7 @@
       <c r="F462" s="19"/>
       <c r="G462" s="17"/>
     </row>
-    <row r="463" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B463" s="17"/>
       <c r="C463" s="17"/>
       <c r="D463" s="17"/>
@@ -10514,7 +10503,7 @@
       <c r="F463" s="19"/>
       <c r="G463" s="17"/>
     </row>
-    <row r="464" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B464" s="17"/>
       <c r="C464" s="17"/>
       <c r="D464" s="17"/>
@@ -10522,7 +10511,7 @@
       <c r="F464" s="19"/>
       <c r="G464" s="17"/>
     </row>
-    <row r="465" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B465" s="17"/>
       <c r="C465" s="17"/>
       <c r="D465" s="17"/>
@@ -10530,7 +10519,7 @@
       <c r="F465" s="19"/>
       <c r="G465" s="17"/>
     </row>
-    <row r="466" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B466" s="17"/>
       <c r="C466" s="17"/>
       <c r="D466" s="17"/>
@@ -10538,7 +10527,7 @@
       <c r="F466" s="19"/>
       <c r="G466" s="17"/>
     </row>
-    <row r="467" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B467" s="17"/>
       <c r="C467" s="17"/>
       <c r="D467" s="17"/>
@@ -10546,7 +10535,7 @@
       <c r="F467" s="19"/>
       <c r="G467" s="17"/>
     </row>
-    <row r="468" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B468" s="17"/>
       <c r="C468" s="17"/>
       <c r="D468" s="17"/>
@@ -10554,7 +10543,7 @@
       <c r="F468" s="19"/>
       <c r="G468" s="17"/>
     </row>
-    <row r="469" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B469" s="17"/>
       <c r="C469" s="17"/>
       <c r="D469" s="17"/>
@@ -10562,7 +10551,7 @@
       <c r="F469" s="19"/>
       <c r="G469" s="17"/>
     </row>
-    <row r="470" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B470" s="17"/>
       <c r="C470" s="17"/>
       <c r="D470" s="17"/>
@@ -10570,7 +10559,7 @@
       <c r="F470" s="19"/>
       <c r="G470" s="17"/>
     </row>
-    <row r="471" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B471" s="17"/>
       <c r="C471" s="17"/>
       <c r="D471" s="17"/>
@@ -10578,7 +10567,7 @@
       <c r="F471" s="19"/>
       <c r="G471" s="17"/>
     </row>
-    <row r="472" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B472" s="17"/>
       <c r="C472" s="17"/>
       <c r="D472" s="17"/>
@@ -10586,7 +10575,7 @@
       <c r="F472" s="19"/>
       <c r="G472" s="17"/>
     </row>
-    <row r="473" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B473" s="17"/>
       <c r="C473" s="17"/>
       <c r="D473" s="17"/>
@@ -10594,7 +10583,7 @@
       <c r="F473" s="19"/>
       <c r="G473" s="17"/>
     </row>
-    <row r="474" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B474" s="17"/>
       <c r="C474" s="17"/>
       <c r="D474" s="17"/>
@@ -10602,7 +10591,7 @@
       <c r="F474" s="19"/>
       <c r="G474" s="17"/>
     </row>
-    <row r="475" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B475" s="17"/>
       <c r="C475" s="17"/>
       <c r="D475" s="17"/>
@@ -10610,7 +10599,7 @@
       <c r="F475" s="19"/>
       <c r="G475" s="17"/>
     </row>
-    <row r="476" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B476" s="17"/>
       <c r="C476" s="17"/>
       <c r="D476" s="17"/>
@@ -10618,7 +10607,7 @@
       <c r="F476" s="19"/>
       <c r="G476" s="17"/>
     </row>
-    <row r="477" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B477" s="17"/>
       <c r="C477" s="17"/>
       <c r="D477" s="17"/>
@@ -10626,7 +10615,7 @@
       <c r="F477" s="19"/>
       <c r="G477" s="17"/>
     </row>
-    <row r="478" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B478" s="17"/>
       <c r="C478" s="17"/>
       <c r="D478" s="17"/>
@@ -10634,7 +10623,7 @@
       <c r="F478" s="19"/>
       <c r="G478" s="17"/>
     </row>
-    <row r="479" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B479" s="17"/>
       <c r="C479" s="17"/>
       <c r="D479" s="17"/>
@@ -10642,7 +10631,7 @@
       <c r="F479" s="19"/>
       <c r="G479" s="17"/>
     </row>
-    <row r="480" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B480" s="17"/>
       <c r="C480" s="17"/>
       <c r="D480" s="17"/>
@@ -10650,7 +10639,7 @@
       <c r="F480" s="19"/>
       <c r="G480" s="17"/>
     </row>
-    <row r="481" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B481" s="17"/>
       <c r="C481" s="17"/>
       <c r="D481" s="17"/>
@@ -10658,7 +10647,7 @@
       <c r="F481" s="19"/>
       <c r="G481" s="17"/>
     </row>
-    <row r="482" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B482" s="17"/>
       <c r="C482" s="17"/>
       <c r="D482" s="17"/>
@@ -10666,7 +10655,7 @@
       <c r="F482" s="19"/>
       <c r="G482" s="17"/>
     </row>
-    <row r="483" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B483" s="17"/>
       <c r="C483" s="17"/>
       <c r="D483" s="17"/>
@@ -10674,7 +10663,7 @@
       <c r="F483" s="19"/>
       <c r="G483" s="17"/>
     </row>
-    <row r="484" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B484" s="17"/>
       <c r="C484" s="17"/>
       <c r="D484" s="17"/>
@@ -10682,7 +10671,7 @@
       <c r="F484" s="19"/>
       <c r="G484" s="17"/>
     </row>
-    <row r="485" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B485" s="17"/>
       <c r="C485" s="17"/>
       <c r="D485" s="17"/>
@@ -10690,7 +10679,7 @@
       <c r="F485" s="19"/>
       <c r="G485" s="17"/>
     </row>
-    <row r="486" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B486" s="17"/>
       <c r="C486" s="17"/>
       <c r="D486" s="17"/>
@@ -10698,7 +10687,7 @@
       <c r="F486" s="19"/>
       <c r="G486" s="17"/>
     </row>
-    <row r="487" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B487" s="17"/>
       <c r="C487" s="17"/>
       <c r="D487" s="17"/>
@@ -10706,7 +10695,7 @@
       <c r="F487" s="19"/>
       <c r="G487" s="17"/>
     </row>
-    <row r="488" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B488" s="17"/>
       <c r="C488" s="17"/>
       <c r="D488" s="17"/>
@@ -10714,7 +10703,7 @@
       <c r="F488" s="19"/>
       <c r="G488" s="17"/>
     </row>
-    <row r="489" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B489" s="17"/>
       <c r="C489" s="17"/>
       <c r="D489" s="17"/>
@@ -10722,7 +10711,7 @@
       <c r="F489" s="19"/>
       <c r="G489" s="17"/>
     </row>
-    <row r="490" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B490" s="17"/>
       <c r="C490" s="17"/>
       <c r="D490" s="17"/>
@@ -10730,7 +10719,7 @@
       <c r="F490" s="19"/>
       <c r="G490" s="17"/>
     </row>
-    <row r="491" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B491" s="17"/>
       <c r="C491" s="17"/>
       <c r="D491" s="17"/>
@@ -10738,7 +10727,7 @@
       <c r="F491" s="19"/>
       <c r="G491" s="17"/>
     </row>
-    <row r="492" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B492" s="17"/>
       <c r="C492" s="17"/>
       <c r="D492" s="17"/>
@@ -10746,7 +10735,7 @@
       <c r="F492" s="19"/>
       <c r="G492" s="17"/>
     </row>
-    <row r="493" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B493" s="17"/>
       <c r="C493" s="17"/>
       <c r="D493" s="17"/>
@@ -10754,7 +10743,7 @@
       <c r="F493" s="19"/>
       <c r="G493" s="17"/>
     </row>
-    <row r="494" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B494" s="17"/>
       <c r="C494" s="17"/>
       <c r="D494" s="17"/>
@@ -10762,7 +10751,7 @@
       <c r="F494" s="19"/>
       <c r="G494" s="17"/>
     </row>
-    <row r="495" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B495" s="17"/>
       <c r="C495" s="17"/>
       <c r="D495" s="17"/>
@@ -10770,7 +10759,7 @@
       <c r="F495" s="19"/>
       <c r="G495" s="17"/>
     </row>
-    <row r="496" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B496" s="17"/>
       <c r="C496" s="17"/>
       <c r="D496" s="17"/>
@@ -10778,7 +10767,7 @@
       <c r="F496" s="19"/>
       <c r="G496" s="17"/>
     </row>
-    <row r="497" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B497" s="17"/>
       <c r="C497" s="17"/>
       <c r="D497" s="17"/>
@@ -10786,7 +10775,7 @@
       <c r="F497" s="19"/>
       <c r="G497" s="17"/>
     </row>
-    <row r="498" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B498" s="17"/>
       <c r="C498" s="17"/>
       <c r="D498" s="17"/>
@@ -10794,7 +10783,7 @@
       <c r="F498" s="19"/>
       <c r="G498" s="17"/>
     </row>
-    <row r="499" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B499" s="17"/>
       <c r="C499" s="17"/>
       <c r="D499" s="17"/>
@@ -10802,7 +10791,7 @@
       <c r="F499" s="19"/>
       <c r="G499" s="17"/>
     </row>
-    <row r="500" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B500" s="17"/>
       <c r="C500" s="17"/>
       <c r="D500" s="17"/>
@@ -10810,7 +10799,7 @@
       <c r="F500" s="19"/>
       <c r="G500" s="17"/>
     </row>
-    <row r="501" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B501" s="17"/>
       <c r="C501" s="17"/>
       <c r="D501" s="17"/>
@@ -10818,7 +10807,7 @@
       <c r="F501" s="19"/>
       <c r="G501" s="17"/>
     </row>
-    <row r="502" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B502" s="17"/>
       <c r="C502" s="17"/>
       <c r="D502" s="17"/>
@@ -10826,7 +10815,7 @@
       <c r="F502" s="19"/>
       <c r="G502" s="17"/>
     </row>
-    <row r="503" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B503" s="17"/>
       <c r="C503" s="17"/>
       <c r="D503" s="17"/>
@@ -10834,7 +10823,7 @@
       <c r="F503" s="19"/>
       <c r="G503" s="17"/>
     </row>
-    <row r="504" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B504" s="17"/>
       <c r="C504" s="17"/>
       <c r="D504" s="17"/>
@@ -10842,7 +10831,7 @@
       <c r="F504" s="19"/>
       <c r="G504" s="17"/>
     </row>
-    <row r="505" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B505" s="17"/>
       <c r="C505" s="17"/>
       <c r="D505" s="17"/>
@@ -10850,7 +10839,7 @@
       <c r="F505" s="19"/>
       <c r="G505" s="17"/>
     </row>
-    <row r="506" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B506" s="17"/>
       <c r="C506" s="17"/>
       <c r="D506" s="17"/>
@@ -10858,7 +10847,7 @@
       <c r="F506" s="19"/>
       <c r="G506" s="17"/>
     </row>
-    <row r="507" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B507" s="17"/>
       <c r="C507" s="17"/>
       <c r="D507" s="17"/>
@@ -10866,7 +10855,7 @@
       <c r="F507" s="19"/>
       <c r="G507" s="17"/>
     </row>
-    <row r="508" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B508" s="17"/>
       <c r="C508" s="17"/>
       <c r="D508" s="17"/>
@@ -10874,7 +10863,7 @@
       <c r="F508" s="19"/>
       <c r="G508" s="17"/>
     </row>
-    <row r="509" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B509" s="17"/>
       <c r="C509" s="17"/>
       <c r="D509" s="17"/>
@@ -10882,7 +10871,7 @@
       <c r="F509" s="19"/>
       <c r="G509" s="17"/>
     </row>
-    <row r="510" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B510" s="17"/>
       <c r="C510" s="17"/>
       <c r="D510" s="17"/>
@@ -10890,7 +10879,7 @@
       <c r="F510" s="19"/>
       <c r="G510" s="17"/>
     </row>
-    <row r="511" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B511" s="17"/>
       <c r="C511" s="17"/>
       <c r="D511" s="17"/>
@@ -10898,7 +10887,7 @@
       <c r="F511" s="19"/>
       <c r="G511" s="17"/>
     </row>
-    <row r="512" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B512" s="17"/>
       <c r="C512" s="17"/>
       <c r="D512" s="17"/>
@@ -10906,7 +10895,7 @@
       <c r="F512" s="19"/>
       <c r="G512" s="17"/>
     </row>
-    <row r="513" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B513" s="17"/>
       <c r="C513" s="17"/>
       <c r="D513" s="17"/>
@@ -10914,7 +10903,7 @@
       <c r="F513" s="19"/>
       <c r="G513" s="17"/>
     </row>
-    <row r="514" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B514" s="17"/>
       <c r="C514" s="17"/>
       <c r="D514" s="17"/>
@@ -10922,7 +10911,7 @@
       <c r="F514" s="19"/>
       <c r="G514" s="17"/>
     </row>
-    <row r="515" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B515" s="17"/>
       <c r="C515" s="17"/>
       <c r="D515" s="17"/>
@@ -10930,7 +10919,7 @@
       <c r="F515" s="19"/>
       <c r="G515" s="17"/>
     </row>
-    <row r="516" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B516" s="17"/>
       <c r="C516" s="17"/>
       <c r="D516" s="17"/>
@@ -10938,7 +10927,7 @@
       <c r="F516" s="19"/>
       <c r="G516" s="17"/>
     </row>
-    <row r="517" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B517" s="17"/>
       <c r="C517" s="17"/>
       <c r="D517" s="17"/>
@@ -10946,7 +10935,7 @@
       <c r="F517" s="19"/>
       <c r="G517" s="17"/>
     </row>
-    <row r="518" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B518" s="17"/>
       <c r="C518" s="17"/>
       <c r="D518" s="17"/>
@@ -10954,7 +10943,7 @@
       <c r="F518" s="19"/>
       <c r="G518" s="17"/>
     </row>
-    <row r="519" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B519" s="17"/>
       <c r="C519" s="17"/>
       <c r="D519" s="17"/>
@@ -10962,7 +10951,7 @@
       <c r="F519" s="19"/>
       <c r="G519" s="17"/>
     </row>
-    <row r="520" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B520" s="17"/>
       <c r="C520" s="17"/>
       <c r="D520" s="17"/>
@@ -10970,7 +10959,7 @@
       <c r="F520" s="19"/>
       <c r="G520" s="17"/>
     </row>
-    <row r="521" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B521" s="17"/>
       <c r="C521" s="17"/>
       <c r="D521" s="17"/>
@@ -10978,7 +10967,7 @@
       <c r="F521" s="19"/>
       <c r="G521" s="17"/>
     </row>
-    <row r="522" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B522" s="17"/>
       <c r="C522" s="17"/>
       <c r="D522" s="17"/>
@@ -10986,7 +10975,7 @@
       <c r="F522" s="19"/>
       <c r="G522" s="17"/>
     </row>
-    <row r="523" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B523" s="17"/>
       <c r="C523" s="17"/>
       <c r="D523" s="17"/>
@@ -10994,7 +10983,7 @@
       <c r="F523" s="19"/>
       <c r="G523" s="17"/>
     </row>
-    <row r="524" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B524" s="17"/>
       <c r="C524" s="17"/>
       <c r="D524" s="17"/>
@@ -11002,7 +10991,7 @@
       <c r="F524" s="19"/>
       <c r="G524" s="17"/>
     </row>
-    <row r="525" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B525" s="17"/>
       <c r="C525" s="17"/>
       <c r="D525" s="17"/>
@@ -11010,7 +10999,7 @@
       <c r="F525" s="19"/>
       <c r="G525" s="17"/>
     </row>
-    <row r="526" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B526" s="17"/>
       <c r="C526" s="17"/>
       <c r="D526" s="17"/>
@@ -11018,7 +11007,7 @@
       <c r="F526" s="19"/>
       <c r="G526" s="17"/>
     </row>
-    <row r="527" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B527" s="17"/>
       <c r="C527" s="17"/>
       <c r="D527" s="17"/>
@@ -11026,7 +11015,7 @@
       <c r="F527" s="19"/>
       <c r="G527" s="17"/>
     </row>
-    <row r="528" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B528" s="17"/>
       <c r="C528" s="17"/>
       <c r="D528" s="17"/>
@@ -11034,7 +11023,7 @@
       <c r="F528" s="19"/>
       <c r="G528" s="17"/>
     </row>
-    <row r="529" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B529" s="17"/>
       <c r="C529" s="17"/>
       <c r="D529" s="17"/>
@@ -11042,7 +11031,7 @@
       <c r="F529" s="19"/>
       <c r="G529" s="17"/>
     </row>
-    <row r="530" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B530" s="17"/>
       <c r="C530" s="17"/>
       <c r="D530" s="17"/>
@@ -11050,7 +11039,7 @@
       <c r="F530" s="19"/>
       <c r="G530" s="17"/>
     </row>
-    <row r="531" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B531" s="17"/>
       <c r="C531" s="17"/>
       <c r="D531" s="17"/>
@@ -11058,7 +11047,7 @@
       <c r="F531" s="19"/>
       <c r="G531" s="17"/>
     </row>
-    <row r="532" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B532" s="17"/>
       <c r="C532" s="17"/>
       <c r="D532" s="17"/>
@@ -11066,7 +11055,7 @@
       <c r="F532" s="19"/>
       <c r="G532" s="17"/>
     </row>
-    <row r="533" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B533" s="17"/>
       <c r="C533" s="17"/>
       <c r="D533" s="17"/>
@@ -11074,7 +11063,7 @@
       <c r="F533" s="19"/>
       <c r="G533" s="17"/>
     </row>
-    <row r="534" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B534" s="17"/>
       <c r="C534" s="17"/>
       <c r="D534" s="17"/>
@@ -11082,7 +11071,7 @@
       <c r="F534" s="19"/>
       <c r="G534" s="17"/>
     </row>
-    <row r="535" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B535" s="17"/>
       <c r="C535" s="17"/>
       <c r="D535" s="17"/>
@@ -11090,7 +11079,7 @@
       <c r="F535" s="19"/>
       <c r="G535" s="17"/>
     </row>
-    <row r="536" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B536" s="17"/>
       <c r="C536" s="17"/>
       <c r="D536" s="17"/>
@@ -11098,7 +11087,7 @@
       <c r="F536" s="19"/>
       <c r="G536" s="17"/>
     </row>
-    <row r="537" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B537" s="17"/>
       <c r="C537" s="17"/>
       <c r="D537" s="17"/>
@@ -11106,7 +11095,7 @@
       <c r="F537" s="19"/>
       <c r="G537" s="17"/>
     </row>
-    <row r="538" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B538" s="17"/>
       <c r="C538" s="17"/>
       <c r="D538" s="17"/>
@@ -11114,7 +11103,7 @@
       <c r="F538" s="19"/>
       <c r="G538" s="17"/>
     </row>
-    <row r="539" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B539" s="17"/>
       <c r="C539" s="17"/>
       <c r="D539" s="17"/>
@@ -11122,7 +11111,7 @@
       <c r="F539" s="19"/>
       <c r="G539" s="17"/>
     </row>
-    <row r="540" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B540" s="17"/>
       <c r="C540" s="17"/>
       <c r="D540" s="17"/>
@@ -11130,7 +11119,7 @@
       <c r="F540" s="19"/>
       <c r="G540" s="17"/>
     </row>
-    <row r="541" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B541" s="17"/>
       <c r="C541" s="17"/>
       <c r="D541" s="17"/>
@@ -11138,7 +11127,7 @@
       <c r="F541" s="19"/>
       <c r="G541" s="17"/>
     </row>
-    <row r="542" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B542" s="17"/>
       <c r="C542" s="17"/>
       <c r="D542" s="17"/>
@@ -11146,7 +11135,7 @@
       <c r="F542" s="19"/>
       <c r="G542" s="17"/>
     </row>
-    <row r="543" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B543" s="17"/>
       <c r="C543" s="17"/>
       <c r="D543" s="17"/>
@@ -11154,7 +11143,7 @@
       <c r="F543" s="19"/>
       <c r="G543" s="17"/>
     </row>
-    <row r="544" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B544" s="17"/>
       <c r="C544" s="17"/>
       <c r="D544" s="17"/>
@@ -11162,7 +11151,7 @@
       <c r="F544" s="19"/>
       <c r="G544" s="17"/>
     </row>
-    <row r="545" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B545" s="17"/>
       <c r="C545" s="17"/>
       <c r="D545" s="17"/>
@@ -11170,7 +11159,7 @@
       <c r="F545" s="19"/>
       <c r="G545" s="17"/>
     </row>
-    <row r="546" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B546" s="17"/>
       <c r="C546" s="17"/>
       <c r="D546" s="17"/>
@@ -11178,7 +11167,7 @@
       <c r="F546" s="19"/>
       <c r="G546" s="17"/>
     </row>
-    <row r="547" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B547" s="17"/>
       <c r="C547" s="17"/>
       <c r="D547" s="17"/>
@@ -11186,7 +11175,7 @@
       <c r="F547" s="19"/>
       <c r="G547" s="17"/>
     </row>
-    <row r="548" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B548" s="17"/>
       <c r="C548" s="17"/>
       <c r="D548" s="17"/>
@@ -11194,7 +11183,7 @@
       <c r="F548" s="19"/>
       <c r="G548" s="17"/>
     </row>
-    <row r="549" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B549" s="17"/>
       <c r="C549" s="17"/>
       <c r="D549" s="17"/>
@@ -11202,7 +11191,7 @@
       <c r="F549" s="19"/>
       <c r="G549" s="17"/>
     </row>
-    <row r="550" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B550" s="17"/>
       <c r="C550" s="17"/>
       <c r="D550" s="17"/>
@@ -11210,7 +11199,7 @@
       <c r="F550" s="19"/>
       <c r="G550" s="17"/>
     </row>
-    <row r="551" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B551" s="17"/>
       <c r="C551" s="17"/>
       <c r="D551" s="17"/>
@@ -11218,7 +11207,7 @@
       <c r="F551" s="19"/>
       <c r="G551" s="17"/>
     </row>
-    <row r="552" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B552" s="17"/>
       <c r="C552" s="17"/>
       <c r="D552" s="17"/>
@@ -11226,7 +11215,7 @@
       <c r="F552" s="19"/>
       <c r="G552" s="17"/>
     </row>
-    <row r="553" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B553" s="17"/>
       <c r="C553" s="17"/>
       <c r="D553" s="17"/>
@@ -11234,7 +11223,7 @@
       <c r="F553" s="19"/>
       <c r="G553" s="17"/>
     </row>
-    <row r="554" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B554" s="17"/>
       <c r="C554" s="17"/>
       <c r="D554" s="17"/>
@@ -11242,7 +11231,7 @@
       <c r="F554" s="19"/>
       <c r="G554" s="17"/>
     </row>
-    <row r="555" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B555" s="17"/>
       <c r="C555" s="17"/>
       <c r="D555" s="17"/>
@@ -11250,7 +11239,7 @@
       <c r="F555" s="19"/>
       <c r="G555" s="17"/>
     </row>
-    <row r="556" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B556" s="17"/>
       <c r="C556" s="17"/>
       <c r="D556" s="17"/>
@@ -11258,7 +11247,7 @@
       <c r="F556" s="19"/>
       <c r="G556" s="17"/>
     </row>
-    <row r="557" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B557" s="17"/>
       <c r="C557" s="17"/>
       <c r="D557" s="17"/>
@@ -11266,7 +11255,7 @@
       <c r="F557" s="19"/>
       <c r="G557" s="17"/>
     </row>
-    <row r="558" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B558" s="17"/>
       <c r="C558" s="17"/>
       <c r="D558" s="17"/>
@@ -11274,7 +11263,7 @@
       <c r="F558" s="19"/>
       <c r="G558" s="17"/>
     </row>
-    <row r="559" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B559" s="17"/>
       <c r="C559" s="17"/>
       <c r="D559" s="17"/>
@@ -11282,7 +11271,7 @@
       <c r="F559" s="19"/>
       <c r="G559" s="17"/>
     </row>
-    <row r="560" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B560" s="17"/>
       <c r="C560" s="17"/>
       <c r="D560" s="17"/>
@@ -11290,7 +11279,7 @@
       <c r="F560" s="19"/>
       <c r="G560" s="17"/>
     </row>
-    <row r="561" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B561" s="17"/>
       <c r="C561" s="17"/>
       <c r="D561" s="17"/>
@@ -11298,7 +11287,7 @@
       <c r="F561" s="19"/>
       <c r="G561" s="17"/>
     </row>
-    <row r="562" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B562" s="17"/>
       <c r="C562" s="17"/>
       <c r="D562" s="17"/>
@@ -11306,7 +11295,7 @@
       <c r="F562" s="19"/>
       <c r="G562" s="17"/>
     </row>
-    <row r="563" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B563" s="17"/>
       <c r="C563" s="17"/>
       <c r="D563" s="17"/>
@@ -11314,7 +11303,7 @@
       <c r="F563" s="19"/>
       <c r="G563" s="17"/>
     </row>
-    <row r="564" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B564" s="17"/>
       <c r="C564" s="17"/>
       <c r="D564" s="17"/>
@@ -11322,7 +11311,7 @@
       <c r="F564" s="19"/>
       <c r="G564" s="17"/>
     </row>
-    <row r="565" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B565" s="17"/>
       <c r="C565" s="17"/>
       <c r="D565" s="17"/>
@@ -11330,7 +11319,7 @@
       <c r="F565" s="19"/>
       <c r="G565" s="17"/>
     </row>
-    <row r="566" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B566" s="17"/>
       <c r="C566" s="17"/>
       <c r="D566" s="17"/>
@@ -11338,7 +11327,7 @@
       <c r="F566" s="19"/>
       <c r="G566" s="17"/>
     </row>
-    <row r="567" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B567" s="17"/>
       <c r="C567" s="17"/>
       <c r="D567" s="17"/>
@@ -11346,7 +11335,7 @@
       <c r="F567" s="19"/>
       <c r="G567" s="17"/>
     </row>
-    <row r="568" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B568" s="17"/>
       <c r="C568" s="17"/>
       <c r="D568" s="17"/>
@@ -11354,7 +11343,7 @@
       <c r="F568" s="19"/>
       <c r="G568" s="17"/>
     </row>
-    <row r="569" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B569" s="17"/>
       <c r="C569" s="17"/>
       <c r="D569" s="17"/>
@@ -11362,7 +11351,7 @@
       <c r="F569" s="19"/>
       <c r="G569" s="17"/>
     </row>
-    <row r="570" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B570" s="17"/>
       <c r="C570" s="17"/>
       <c r="D570" s="17"/>
@@ -11370,7 +11359,7 @@
       <c r="F570" s="19"/>
       <c r="G570" s="17"/>
     </row>
-    <row r="571" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B571" s="17"/>
       <c r="C571" s="17"/>
       <c r="D571" s="17"/>
@@ -11378,7 +11367,7 @@
       <c r="F571" s="19"/>
       <c r="G571" s="17"/>
     </row>
-    <row r="572" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B572" s="17"/>
       <c r="C572" s="17"/>
       <c r="D572" s="17"/>
@@ -11386,7 +11375,7 @@
       <c r="F572" s="19"/>
       <c r="G572" s="17"/>
     </row>
-    <row r="573" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B573" s="17"/>
       <c r="C573" s="17"/>
       <c r="D573" s="17"/>
@@ -11394,7 +11383,7 @@
       <c r="F573" s="19"/>
       <c r="G573" s="17"/>
     </row>
-    <row r="574" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B574" s="17"/>
       <c r="C574" s="17"/>
       <c r="D574" s="17"/>
@@ -11402,7 +11391,7 @@
       <c r="F574" s="19"/>
       <c r="G574" s="17"/>
     </row>
-    <row r="575" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B575" s="17"/>
       <c r="C575" s="17"/>
       <c r="D575" s="17"/>
@@ -11410,7 +11399,7 @@
       <c r="F575" s="19"/>
       <c r="G575" s="17"/>
     </row>
-    <row r="576" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B576" s="17"/>
       <c r="C576" s="17"/>
       <c r="D576" s="17"/>
@@ -11418,7 +11407,7 @@
       <c r="F576" s="19"/>
       <c r="G576" s="17"/>
     </row>
-    <row r="577" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B577" s="17"/>
       <c r="C577" s="17"/>
       <c r="D577" s="17"/>
@@ -11426,7 +11415,7 @@
       <c r="F577" s="19"/>
       <c r="G577" s="17"/>
     </row>
-    <row r="578" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B578" s="17"/>
       <c r="C578" s="17"/>
       <c r="D578" s="17"/>
@@ -11434,7 +11423,7 @@
       <c r="F578" s="19"/>
       <c r="G578" s="17"/>
     </row>
-    <row r="579" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B579" s="17"/>
       <c r="C579" s="17"/>
       <c r="D579" s="17"/>
@@ -11442,7 +11431,7 @@
       <c r="F579" s="19"/>
       <c r="G579" s="17"/>
     </row>
-    <row r="580" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B580" s="17"/>
       <c r="C580" s="17"/>
       <c r="D580" s="17"/>
@@ -11450,7 +11439,7 @@
       <c r="F580" s="19"/>
       <c r="G580" s="17"/>
     </row>
-    <row r="581" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B581" s="17"/>
       <c r="C581" s="17"/>
       <c r="D581" s="17"/>
@@ -11458,7 +11447,7 @@
       <c r="F581" s="19"/>
       <c r="G581" s="17"/>
     </row>
-    <row r="582" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B582" s="17"/>
       <c r="C582" s="17"/>
       <c r="D582" s="17"/>
@@ -11466,7 +11455,7 @@
       <c r="F582" s="19"/>
       <c r="G582" s="17"/>
     </row>
-    <row r="583" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B583" s="17"/>
       <c r="C583" s="17"/>
       <c r="D583" s="17"/>
@@ -11474,7 +11463,7 @@
       <c r="F583" s="19"/>
       <c r="G583" s="17"/>
     </row>
-    <row r="584" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B584" s="17"/>
       <c r="C584" s="17"/>
       <c r="D584" s="17"/>
@@ -11482,7 +11471,7 @@
       <c r="F584" s="19"/>
       <c r="G584" s="17"/>
     </row>
-    <row r="585" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B585" s="17"/>
       <c r="C585" s="17"/>
       <c r="D585" s="17"/>
@@ -11490,7 +11479,7 @@
       <c r="F585" s="19"/>
       <c r="G585" s="17"/>
     </row>
-    <row r="586" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B586" s="17"/>
       <c r="C586" s="17"/>
       <c r="D586" s="17"/>
@@ -11498,7 +11487,7 @@
       <c r="F586" s="19"/>
       <c r="G586" s="17"/>
     </row>
-    <row r="587" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B587" s="17"/>
       <c r="C587" s="17"/>
       <c r="D587" s="17"/>
@@ -11506,7 +11495,7 @@
       <c r="F587" s="19"/>
       <c r="G587" s="17"/>
     </row>
-    <row r="588" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B588" s="17"/>
       <c r="C588" s="17"/>
       <c r="D588" s="17"/>
@@ -11514,7 +11503,7 @@
       <c r="F588" s="19"/>
       <c r="G588" s="17"/>
     </row>
-    <row r="589" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B589" s="17"/>
       <c r="C589" s="17"/>
       <c r="D589" s="17"/>
@@ -11522,7 +11511,7 @@
       <c r="F589" s="19"/>
       <c r="G589" s="17"/>
     </row>
-    <row r="590" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B590" s="17"/>
       <c r="C590" s="17"/>
       <c r="D590" s="17"/>
@@ -11530,7 +11519,7 @@
       <c r="F590" s="19"/>
       <c r="G590" s="17"/>
     </row>
-    <row r="591" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B591" s="17"/>
       <c r="C591" s="17"/>
       <c r="D591" s="17"/>
@@ -11538,7 +11527,7 @@
       <c r="F591" s="19"/>
       <c r="G591" s="17"/>
     </row>
-    <row r="592" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B592" s="17"/>
       <c r="C592" s="17"/>
       <c r="D592" s="17"/>
@@ -11546,7 +11535,7 @@
       <c r="F592" s="19"/>
       <c r="G592" s="17"/>
     </row>
-    <row r="593" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B593" s="17"/>
       <c r="C593" s="17"/>
       <c r="D593" s="17"/>
@@ -11554,7 +11543,7 @@
       <c r="F593" s="19"/>
       <c r="G593" s="17"/>
     </row>
-    <row r="594" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B594" s="17"/>
       <c r="C594" s="17"/>
       <c r="D594" s="17"/>
@@ -11562,7 +11551,7 @@
       <c r="F594" s="19"/>
       <c r="G594" s="17"/>
     </row>
-    <row r="595" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B595" s="17"/>
       <c r="C595" s="17"/>
       <c r="D595" s="17"/>
@@ -11570,7 +11559,7 @@
       <c r="F595" s="19"/>
       <c r="G595" s="17"/>
     </row>
-    <row r="596" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B596" s="17"/>
       <c r="C596" s="17"/>
       <c r="D596" s="17"/>
@@ -11578,7 +11567,7 @@
       <c r="F596" s="19"/>
       <c r="G596" s="17"/>
     </row>
-    <row r="597" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B597" s="17"/>
       <c r="C597" s="17"/>
       <c r="D597" s="17"/>
@@ -11586,7 +11575,7 @@
       <c r="F597" s="19"/>
       <c r="G597" s="17"/>
     </row>
-    <row r="598" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B598" s="17"/>
       <c r="C598" s="17"/>
       <c r="D598" s="17"/>
@@ -11594,7 +11583,7 @@
       <c r="F598" s="19"/>
       <c r="G598" s="17"/>
     </row>
-    <row r="599" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B599" s="17"/>
       <c r="C599" s="17"/>
       <c r="D599" s="17"/>
@@ -11602,7 +11591,7 @@
       <c r="F599" s="19"/>
       <c r="G599" s="17"/>
     </row>
-    <row r="600" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B600" s="17"/>
       <c r="C600" s="17"/>
       <c r="D600" s="17"/>
@@ -11610,7 +11599,7 @@
       <c r="F600" s="19"/>
       <c r="G600" s="17"/>
     </row>
-    <row r="601" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B601" s="17"/>
       <c r="C601" s="17"/>
       <c r="D601" s="17"/>
@@ -11618,7 +11607,7 @@
       <c r="F601" s="19"/>
       <c r="G601" s="17"/>
     </row>
-    <row r="602" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B602" s="17"/>
       <c r="C602" s="17"/>
       <c r="D602" s="17"/>
@@ -11626,7 +11615,7 @@
       <c r="F602" s="19"/>
       <c r="G602" s="17"/>
     </row>
-    <row r="603" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B603" s="17"/>
       <c r="C603" s="17"/>
       <c r="D603" s="17"/>
@@ -11634,7 +11623,7 @@
       <c r="F603" s="19"/>
       <c r="G603" s="17"/>
     </row>
-    <row r="604" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B604" s="17"/>
       <c r="C604" s="17"/>
       <c r="D604" s="17"/>
@@ -11642,7 +11631,7 @@
       <c r="F604" s="19"/>
       <c r="G604" s="17"/>
     </row>
-    <row r="605" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B605" s="17"/>
       <c r="C605" s="17"/>
       <c r="D605" s="17"/>
@@ -11650,7 +11639,7 @@
       <c r="F605" s="19"/>
       <c r="G605" s="17"/>
     </row>
-    <row r="606" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B606" s="17"/>
       <c r="C606" s="17"/>
       <c r="D606" s="17"/>
@@ -11658,7 +11647,7 @@
       <c r="F606" s="19"/>
       <c r="G606" s="17"/>
     </row>
-    <row r="607" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B607" s="17"/>
       <c r="C607" s="17"/>
       <c r="D607" s="17"/>
@@ -11666,7 +11655,7 @@
       <c r="F607" s="19"/>
       <c r="G607" s="17"/>
     </row>
-    <row r="608" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B608" s="17"/>
       <c r="C608" s="17"/>
       <c r="D608" s="17"/>
@@ -11674,7 +11663,7 @@
       <c r="F608" s="19"/>
       <c r="G608" s="17"/>
     </row>
-    <row r="609" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B609" s="17"/>
       <c r="C609" s="17"/>
       <c r="D609" s="17"/>
@@ -11682,7 +11671,7 @@
       <c r="F609" s="19"/>
       <c r="G609" s="17"/>
     </row>
-    <row r="610" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B610" s="17"/>
       <c r="C610" s="17"/>
       <c r="D610" s="17"/>
@@ -11690,7 +11679,7 @@
       <c r="F610" s="19"/>
       <c r="G610" s="17"/>
     </row>
-    <row r="611" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B611" s="17"/>
       <c r="C611" s="17"/>
       <c r="D611" s="17"/>
@@ -11698,7 +11687,7 @@
       <c r="F611" s="19"/>
       <c r="G611" s="17"/>
     </row>
-    <row r="612" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B612" s="17"/>
       <c r="C612" s="17"/>
       <c r="D612" s="17"/>
@@ -11706,7 +11695,7 @@
       <c r="F612" s="19"/>
       <c r="G612" s="17"/>
     </row>
-    <row r="613" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B613" s="17"/>
       <c r="C613" s="17"/>
       <c r="D613" s="17"/>
@@ -11714,7 +11703,7 @@
       <c r="F613" s="19"/>
       <c r="G613" s="17"/>
     </row>
-    <row r="614" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B614" s="17"/>
       <c r="C614" s="17"/>
       <c r="D614" s="17"/>
@@ -11722,7 +11711,7 @@
       <c r="F614" s="19"/>
       <c r="G614" s="17"/>
     </row>
-    <row r="615" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B615" s="17"/>
       <c r="C615" s="17"/>
       <c r="D615" s="17"/>
@@ -11730,7 +11719,7 @@
       <c r="F615" s="19"/>
       <c r="G615" s="17"/>
     </row>
-    <row r="616" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B616" s="17"/>
       <c r="C616" s="17"/>
       <c r="D616" s="17"/>
@@ -11738,7 +11727,7 @@
       <c r="F616" s="19"/>
       <c r="G616" s="17"/>
     </row>
-    <row r="617" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B617" s="17"/>
       <c r="C617" s="17"/>
       <c r="D617" s="17"/>
@@ -11746,7 +11735,7 @@
       <c r="F617" s="19"/>
       <c r="G617" s="17"/>
     </row>
-    <row r="618" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B618" s="17"/>
       <c r="C618" s="17"/>
       <c r="D618" s="17"/>
@@ -11754,7 +11743,7 @@
       <c r="F618" s="19"/>
       <c r="G618" s="17"/>
     </row>
-    <row r="619" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B619" s="17"/>
       <c r="C619" s="17"/>
       <c r="D619" s="17"/>
@@ -11762,7 +11751,7 @@
       <c r="F619" s="19"/>
       <c r="G619" s="17"/>
     </row>
-    <row r="620" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B620" s="17"/>
       <c r="C620" s="17"/>
       <c r="D620" s="17"/>
@@ -11770,7 +11759,7 @@
       <c r="F620" s="19"/>
       <c r="G620" s="17"/>
     </row>
-    <row r="621" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B621" s="17"/>
       <c r="C621" s="17"/>
       <c r="D621" s="17"/>
@@ -11778,7 +11767,7 @@
       <c r="F621" s="19"/>
       <c r="G621" s="17"/>
     </row>
-    <row r="622" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B622" s="17"/>
       <c r="C622" s="17"/>
       <c r="D622" s="17"/>
@@ -11786,7 +11775,7 @@
       <c r="F622" s="19"/>
       <c r="G622" s="17"/>
     </row>
-    <row r="623" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B623" s="17"/>
       <c r="C623" s="17"/>
       <c r="D623" s="17"/>
@@ -11794,7 +11783,7 @@
       <c r="F623" s="19"/>
       <c r="G623" s="17"/>
     </row>
-    <row r="624" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B624" s="17"/>
       <c r="C624" s="17"/>
       <c r="D624" s="17"/>
@@ -11802,7 +11791,7 @@
       <c r="F624" s="19"/>
       <c r="G624" s="17"/>
     </row>
-    <row r="625" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B625" s="17"/>
       <c r="C625" s="17"/>
       <c r="D625" s="17"/>
@@ -11810,7 +11799,7 @@
       <c r="F625" s="19"/>
       <c r="G625" s="17"/>
     </row>
-    <row r="626" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B626" s="17"/>
       <c r="C626" s="17"/>
       <c r="D626" s="17"/>
@@ -11818,7 +11807,7 @@
       <c r="F626" s="19"/>
       <c r="G626" s="17"/>
     </row>
-    <row r="627" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B627" s="17"/>
       <c r="C627" s="17"/>
       <c r="D627" s="17"/>
@@ -11826,7 +11815,7 @@
       <c r="F627" s="19"/>
       <c r="G627" s="17"/>
     </row>
-    <row r="628" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B628" s="17"/>
       <c r="C628" s="17"/>
       <c r="D628" s="17"/>
@@ -11834,7 +11823,7 @@
       <c r="F628" s="19"/>
       <c r="G628" s="17"/>
     </row>
-    <row r="629" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B629" s="17"/>
       <c r="C629" s="17"/>
       <c r="D629" s="17"/>
@@ -11842,7 +11831,7 @@
       <c r="F629" s="19"/>
       <c r="G629" s="17"/>
     </row>
-    <row r="630" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B630" s="17"/>
       <c r="C630" s="17"/>
       <c r="D630" s="17"/>
@@ -11850,7 +11839,7 @@
       <c r="F630" s="19"/>
       <c r="G630" s="17"/>
     </row>
-    <row r="631" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B631" s="17"/>
       <c r="C631" s="17"/>
       <c r="D631" s="17"/>
@@ -11858,7 +11847,7 @@
       <c r="F631" s="19"/>
       <c r="G631" s="17"/>
     </row>
-    <row r="632" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B632" s="17"/>
       <c r="C632" s="17"/>
       <c r="D632" s="17"/>
@@ -11866,7 +11855,7 @@
       <c r="F632" s="19"/>
       <c r="G632" s="17"/>
     </row>
-    <row r="633" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B633" s="17"/>
       <c r="C633" s="17"/>
       <c r="D633" s="17"/>
@@ -11874,7 +11863,7 @@
       <c r="F633" s="19"/>
       <c r="G633" s="17"/>
     </row>
-    <row r="634" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B634" s="17"/>
       <c r="C634" s="17"/>
       <c r="D634" s="17"/>
@@ -11882,7 +11871,7 @@
       <c r="F634" s="19"/>
       <c r="G634" s="17"/>
     </row>
-    <row r="635" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B635" s="17"/>
       <c r="C635" s="17"/>
       <c r="D635" s="17"/>
@@ -11890,7 +11879,7 @@
       <c r="F635" s="19"/>
       <c r="G635" s="17"/>
     </row>
-    <row r="636" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B636" s="17"/>
       <c r="C636" s="17"/>
       <c r="D636" s="17"/>
@@ -11898,7 +11887,7 @@
       <c r="F636" s="19"/>
       <c r="G636" s="17"/>
     </row>
-    <row r="637" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B637" s="17"/>
       <c r="C637" s="17"/>
       <c r="D637" s="17"/>
@@ -11906,7 +11895,7 @@
       <c r="F637" s="19"/>
       <c r="G637" s="17"/>
     </row>
-    <row r="638" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B638" s="17"/>
       <c r="C638" s="17"/>
       <c r="D638" s="17"/>
@@ -11914,7 +11903,7 @@
       <c r="F638" s="19"/>
       <c r="G638" s="17"/>
     </row>
-    <row r="639" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B639" s="17"/>
       <c r="C639" s="17"/>
       <c r="D639" s="17"/>
@@ -11922,7 +11911,7 @@
       <c r="F639" s="19"/>
       <c r="G639" s="17"/>
     </row>
-    <row r="640" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B640" s="17"/>
       <c r="C640" s="17"/>
       <c r="D640" s="17"/>
@@ -11930,7 +11919,7 @@
       <c r="F640" s="19"/>
       <c r="G640" s="17"/>
     </row>
-    <row r="641" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B641" s="17"/>
       <c r="C641" s="17"/>
       <c r="D641" s="17"/>
@@ -11938,7 +11927,7 @@
       <c r="F641" s="19"/>
       <c r="G641" s="17"/>
     </row>
-    <row r="642" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B642" s="17"/>
       <c r="C642" s="17"/>
       <c r="D642" s="17"/>
@@ -11946,7 +11935,7 @@
       <c r="F642" s="19"/>
       <c r="G642" s="17"/>
     </row>
-    <row r="643" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B643" s="17"/>
       <c r="C643" s="17"/>
       <c r="D643" s="17"/>
@@ -11954,7 +11943,7 @@
       <c r="F643" s="19"/>
       <c r="G643" s="17"/>
     </row>
-    <row r="644" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B644" s="17"/>
       <c r="C644" s="17"/>
       <c r="D644" s="17"/>
@@ -11962,7 +11951,7 @@
       <c r="F644" s="19"/>
       <c r="G644" s="17"/>
     </row>
-    <row r="645" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B645" s="17"/>
       <c r="C645" s="17"/>
       <c r="D645" s="17"/>
@@ -11970,7 +11959,7 @@
       <c r="F645" s="19"/>
       <c r="G645" s="17"/>
     </row>
-    <row r="646" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B646" s="17"/>
       <c r="C646" s="17"/>
       <c r="D646" s="17"/>
@@ -11978,7 +11967,7 @@
       <c r="F646" s="19"/>
       <c r="G646" s="17"/>
     </row>
-    <row r="647" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B647" s="17"/>
       <c r="C647" s="17"/>
       <c r="D647" s="17"/>
@@ -11986,7 +11975,7 @@
       <c r="F647" s="19"/>
       <c r="G647" s="17"/>
     </row>
-    <row r="648" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B648" s="17"/>
       <c r="C648" s="17"/>
       <c r="D648" s="17"/>
@@ -11994,7 +11983,7 @@
       <c r="F648" s="19"/>
       <c r="G648" s="17"/>
     </row>
-    <row r="649" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B649" s="17"/>
       <c r="C649" s="17"/>
       <c r="D649" s="17"/>
@@ -12002,7 +11991,7 @@
       <c r="F649" s="19"/>
       <c r="G649" s="17"/>
     </row>
-    <row r="650" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B650" s="17"/>
       <c r="C650" s="17"/>
       <c r="D650" s="17"/>
@@ -12010,7 +11999,7 @@
       <c r="F650" s="19"/>
       <c r="G650" s="17"/>
     </row>
-    <row r="651" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B651" s="17"/>
       <c r="C651" s="17"/>
       <c r="D651" s="17"/>
@@ -12018,7 +12007,7 @@
       <c r="F651" s="19"/>
       <c r="G651" s="17"/>
     </row>
-    <row r="652" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B652" s="17"/>
       <c r="C652" s="17"/>
       <c r="D652" s="17"/>
@@ -12026,7 +12015,7 @@
       <c r="F652" s="19"/>
       <c r="G652" s="17"/>
     </row>
-    <row r="653" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B653" s="17"/>
       <c r="C653" s="17"/>
       <c r="D653" s="17"/>
@@ -12034,7 +12023,7 @@
       <c r="F653" s="19"/>
       <c r="G653" s="17"/>
     </row>
-    <row r="654" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B654" s="17"/>
       <c r="C654" s="17"/>
       <c r="D654" s="17"/>
@@ -12042,7 +12031,7 @@
       <c r="F654" s="19"/>
       <c r="G654" s="17"/>
     </row>
-    <row r="655" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B655" s="17"/>
       <c r="C655" s="17"/>
       <c r="D655" s="17"/>
@@ -12050,7 +12039,7 @@
       <c r="F655" s="19"/>
       <c r="G655" s="17"/>
     </row>
-    <row r="656" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B656" s="17"/>
       <c r="C656" s="17"/>
       <c r="D656" s="17"/>
@@ -12058,7 +12047,7 @@
       <c r="F656" s="19"/>
       <c r="G656" s="17"/>
     </row>
-    <row r="657" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B657" s="17"/>
       <c r="C657" s="17"/>
       <c r="D657" s="17"/>
@@ -12066,7 +12055,7 @@
       <c r="F657" s="19"/>
       <c r="G657" s="17"/>
     </row>
-    <row r="658" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B658" s="17"/>
       <c r="C658" s="17"/>
       <c r="D658" s="17"/>
@@ -12074,7 +12063,7 @@
       <c r="F658" s="19"/>
       <c r="G658" s="17"/>
     </row>
-    <row r="659" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B659" s="17"/>
       <c r="C659" s="17"/>
       <c r="D659" s="17"/>
@@ -12082,7 +12071,7 @@
       <c r="F659" s="19"/>
       <c r="G659" s="17"/>
     </row>
-    <row r="660" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B660" s="17"/>
       <c r="C660" s="17"/>
       <c r="D660" s="17"/>
@@ -12090,7 +12079,7 @@
       <c r="F660" s="19"/>
       <c r="G660" s="17"/>
     </row>
-    <row r="661" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B661" s="17"/>
       <c r="C661" s="17"/>
       <c r="D661" s="17"/>
@@ -12098,7 +12087,7 @@
       <c r="F661" s="19"/>
       <c r="G661" s="17"/>
     </row>
-    <row r="662" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B662" s="17"/>
       <c r="C662" s="17"/>
       <c r="D662" s="17"/>
@@ -12106,7 +12095,7 @@
       <c r="F662" s="19"/>
       <c r="G662" s="17"/>
     </row>
-    <row r="663" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B663" s="17"/>
       <c r="C663" s="17"/>
       <c r="D663" s="17"/>
@@ -12114,7 +12103,7 @@
       <c r="F663" s="19"/>
       <c r="G663" s="17"/>
     </row>
-    <row r="664" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B664" s="17"/>
       <c r="C664" s="17"/>
       <c r="D664" s="17"/>
@@ -12122,7 +12111,7 @@
       <c r="F664" s="19"/>
       <c r="G664" s="17"/>
     </row>
-    <row r="665" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B665" s="17"/>
       <c r="C665" s="17"/>
       <c r="D665" s="17"/>
@@ -12130,7 +12119,7 @@
       <c r="F665" s="19"/>
       <c r="G665" s="17"/>
     </row>
-    <row r="666" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B666" s="17"/>
       <c r="C666" s="17"/>
       <c r="D666" s="17"/>
@@ -12138,7 +12127,7 @@
       <c r="F666" s="19"/>
       <c r="G666" s="17"/>
     </row>
-    <row r="667" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B667" s="17"/>
       <c r="C667" s="17"/>
       <c r="D667" s="17"/>
@@ -12146,7 +12135,7 @@
       <c r="F667" s="19"/>
       <c r="G667" s="17"/>
     </row>
-    <row r="668" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B668" s="17"/>
       <c r="C668" s="17"/>
       <c r="D668" s="17"/>
@@ -12154,7 +12143,7 @@
       <c r="F668" s="19"/>
       <c r="G668" s="17"/>
     </row>
-    <row r="669" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B669" s="17"/>
       <c r="C669" s="17"/>
       <c r="D669" s="17"/>
@@ -12162,7 +12151,7 @@
       <c r="F669" s="19"/>
       <c r="G669" s="17"/>
     </row>
-    <row r="670" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B670" s="17"/>
       <c r="C670" s="17"/>
       <c r="D670" s="17"/>
@@ -12170,7 +12159,7 @@
       <c r="F670" s="19"/>
       <c r="G670" s="17"/>
     </row>
-    <row r="671" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B671" s="17"/>
       <c r="C671" s="17"/>
       <c r="D671" s="17"/>
@@ -12178,7 +12167,7 @@
       <c r="F671" s="19"/>
       <c r="G671" s="17"/>
     </row>
-    <row r="672" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B672" s="17"/>
       <c r="C672" s="17"/>
       <c r="D672" s="17"/>
@@ -12186,7 +12175,7 @@
       <c r="F672" s="19"/>
       <c r="G672" s="17"/>
     </row>
-    <row r="673" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B673" s="17"/>
       <c r="C673" s="17"/>
       <c r="D673" s="17"/>
@@ -12194,7 +12183,7 @@
       <c r="F673" s="19"/>
       <c r="G673" s="17"/>
     </row>
-    <row r="674" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B674" s="17"/>
       <c r="C674" s="17"/>
       <c r="D674" s="17"/>
@@ -12202,7 +12191,7 @@
       <c r="F674" s="19"/>
       <c r="G674" s="17"/>
     </row>
-    <row r="675" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B675" s="17"/>
       <c r="C675" s="17"/>
       <c r="D675" s="17"/>
@@ -12210,7 +12199,7 @@
       <c r="F675" s="19"/>
       <c r="G675" s="17"/>
     </row>
-    <row r="676" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B676" s="17"/>
       <c r="C676" s="17"/>
       <c r="D676" s="17"/>
@@ -12218,7 +12207,7 @@
       <c r="F676" s="19"/>
       <c r="G676" s="17"/>
     </row>
-    <row r="677" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B677" s="17"/>
       <c r="C677" s="17"/>
       <c r="D677" s="17"/>
@@ -12226,7 +12215,7 @@
       <c r="F677" s="19"/>
       <c r="G677" s="17"/>
     </row>
-    <row r="678" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B678" s="17"/>
       <c r="C678" s="17"/>
       <c r="D678" s="17"/>
@@ -12234,7 +12223,7 @@
       <c r="F678" s="19"/>
       <c r="G678" s="17"/>
     </row>
-    <row r="679" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B679" s="17"/>
       <c r="C679" s="17"/>
       <c r="D679" s="17"/>
@@ -12242,7 +12231,7 @@
       <c r="F679" s="19"/>
       <c r="G679" s="17"/>
     </row>
-    <row r="680" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B680" s="17"/>
       <c r="C680" s="17"/>
       <c r="D680" s="17"/>
@@ -12250,7 +12239,7 @@
       <c r="F680" s="19"/>
       <c r="G680" s="17"/>
     </row>
-    <row r="681" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B681" s="17"/>
       <c r="C681" s="17"/>
       <c r="D681" s="17"/>
@@ -12258,7 +12247,7 @@
       <c r="F681" s="19"/>
       <c r="G681" s="17"/>
     </row>
-    <row r="682" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B682" s="17"/>
       <c r="C682" s="17"/>
       <c r="D682" s="17"/>
@@ -12266,7 +12255,7 @@
       <c r="F682" s="19"/>
       <c r="G682" s="17"/>
     </row>
-    <row r="683" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B683" s="17"/>
       <c r="C683" s="17"/>
       <c r="D683" s="17"/>
@@ -12274,7 +12263,7 @@
       <c r="F683" s="19"/>
       <c r="G683" s="17"/>
     </row>
-    <row r="684" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B684" s="17"/>
       <c r="C684" s="17"/>
       <c r="D684" s="17"/>
@@ -12282,7 +12271,7 @@
       <c r="F684" s="19"/>
       <c r="G684" s="17"/>
     </row>
-    <row r="685" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B685" s="17"/>
       <c r="C685" s="17"/>
       <c r="D685" s="17"/>
@@ -12290,7 +12279,7 @@
       <c r="F685" s="19"/>
       <c r="G685" s="17"/>
     </row>
-    <row r="686" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B686" s="17"/>
       <c r="C686" s="17"/>
       <c r="D686" s="17"/>
@@ -12298,7 +12287,7 @@
       <c r="F686" s="19"/>
       <c r="G686" s="17"/>
     </row>
-    <row r="687" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B687" s="17"/>
       <c r="C687" s="17"/>
       <c r="D687" s="17"/>
@@ -12306,7 +12295,7 @@
       <c r="F687" s="19"/>
       <c r="G687" s="17"/>
     </row>
-    <row r="688" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B688" s="17"/>
       <c r="C688" s="17"/>
       <c r="D688" s="17"/>
@@ -12314,7 +12303,7 @@
       <c r="F688" s="19"/>
       <c r="G688" s="17"/>
     </row>
-    <row r="689" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B689" s="17"/>
       <c r="C689" s="17"/>
       <c r="D689" s="17"/>
@@ -12322,7 +12311,7 @@
       <c r="F689" s="19"/>
       <c r="G689" s="17"/>
     </row>
-    <row r="690" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B690" s="17"/>
       <c r="C690" s="17"/>
       <c r="D690" s="17"/>
@@ -12330,7 +12319,7 @@
       <c r="F690" s="19"/>
       <c r="G690" s="17"/>
     </row>
-    <row r="691" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B691" s="17"/>
       <c r="C691" s="17"/>
       <c r="D691" s="17"/>
@@ -12338,7 +12327,7 @@
       <c r="F691" s="19"/>
       <c r="G691" s="17"/>
     </row>
-    <row r="692" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B692" s="17"/>
       <c r="C692" s="17"/>
       <c r="D692" s="17"/>
@@ -12346,7 +12335,7 @@
       <c r="F692" s="19"/>
       <c r="G692" s="17"/>
     </row>
-    <row r="693" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B693" s="17"/>
       <c r="C693" s="17"/>
       <c r="D693" s="17"/>
@@ -12354,7 +12343,7 @@
       <c r="F693" s="19"/>
       <c r="G693" s="17"/>
     </row>
-    <row r="694" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B694" s="17"/>
       <c r="C694" s="17"/>
       <c r="D694" s="17"/>
@@ -12362,7 +12351,7 @@
       <c r="F694" s="19"/>
       <c r="G694" s="17"/>
     </row>
-    <row r="695" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B695" s="17"/>
       <c r="C695" s="17"/>
       <c r="D695" s="17"/>
@@ -12370,7 +12359,7 @@
       <c r="F695" s="19"/>
       <c r="G695" s="17"/>
     </row>
-    <row r="696" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B696" s="17"/>
       <c r="C696" s="17"/>
       <c r="D696" s="17"/>
@@ -12378,7 +12367,7 @@
       <c r="F696" s="19"/>
       <c r="G696" s="17"/>
     </row>
-    <row r="697" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B697" s="17"/>
       <c r="C697" s="17"/>
       <c r="D697" s="17"/>
@@ -12386,7 +12375,7 @@
       <c r="F697" s="19"/>
       <c r="G697" s="17"/>
     </row>
-    <row r="698" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B698" s="17"/>
       <c r="C698" s="17"/>
       <c r="D698" s="17"/>
@@ -12394,7 +12383,7 @@
       <c r="F698" s="19"/>
       <c r="G698" s="17"/>
     </row>
-    <row r="699" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B699" s="17"/>
       <c r="C699" s="17"/>
       <c r="D699" s="17"/>
@@ -12402,7 +12391,7 @@
       <c r="F699" s="19"/>
       <c r="G699" s="17"/>
     </row>
-    <row r="700" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B700" s="17"/>
       <c r="C700" s="17"/>
       <c r="D700" s="17"/>
@@ -12410,7 +12399,7 @@
       <c r="F700" s="19"/>
       <c r="G700" s="17"/>
     </row>
-    <row r="701" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B701" s="17"/>
       <c r="C701" s="17"/>
       <c r="D701" s="17"/>
@@ -12418,7 +12407,7 @@
       <c r="F701" s="19"/>
       <c r="G701" s="17"/>
     </row>
-    <row r="702" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B702" s="17"/>
       <c r="C702" s="17"/>
       <c r="D702" s="17"/>
@@ -12426,7 +12415,7 @@
       <c r="F702" s="19"/>
       <c r="G702" s="17"/>
     </row>
-    <row r="703" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B703" s="17"/>
       <c r="C703" s="17"/>
       <c r="D703" s="17"/>
@@ -12434,7 +12423,7 @@
       <c r="F703" s="19"/>
       <c r="G703" s="17"/>
     </row>
-    <row r="704" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B704" s="17"/>
       <c r="C704" s="17"/>
       <c r="D704" s="17"/>
@@ -12442,7 +12431,7 @@
       <c r="F704" s="19"/>
       <c r="G704" s="17"/>
     </row>
-    <row r="705" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B705" s="17"/>
       <c r="C705" s="17"/>
       <c r="D705" s="17"/>
@@ -12450,7 +12439,7 @@
       <c r="F705" s="19"/>
       <c r="G705" s="17"/>
     </row>
-    <row r="706" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B706" s="17"/>
       <c r="C706" s="17"/>
       <c r="D706" s="17"/>
@@ -12458,7 +12447,7 @@
       <c r="F706" s="19"/>
       <c r="G706" s="17"/>
     </row>
-    <row r="707" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B707" s="17"/>
       <c r="C707" s="17"/>
       <c r="D707" s="17"/>
@@ -12466,7 +12455,7 @@
       <c r="F707" s="19"/>
       <c r="G707" s="17"/>
     </row>
-    <row r="708" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B708" s="17"/>
       <c r="C708" s="17"/>
       <c r="D708" s="17"/>
@@ -12474,7 +12463,7 @@
       <c r="F708" s="19"/>
       <c r="G708" s="17"/>
     </row>
-    <row r="709" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B709" s="17"/>
       <c r="C709" s="17"/>
       <c r="D709" s="17"/>
@@ -12482,7 +12471,7 @@
       <c r="F709" s="19"/>
       <c r="G709" s="17"/>
     </row>
-    <row r="710" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B710" s="17"/>
       <c r="C710" s="17"/>
       <c r="D710" s="17"/>
@@ -12490,7 +12479,7 @@
       <c r="F710" s="19"/>
       <c r="G710" s="17"/>
     </row>
-    <row r="711" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B711" s="17"/>
       <c r="C711" s="17"/>
       <c r="D711" s="17"/>
@@ -12498,7 +12487,7 @@
       <c r="F711" s="19"/>
       <c r="G711" s="17"/>
     </row>
-    <row r="712" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B712" s="17"/>
       <c r="C712" s="17"/>
       <c r="D712" s="17"/>
@@ -12506,7 +12495,7 @@
       <c r="F712" s="19"/>
       <c r="G712" s="17"/>
     </row>
-    <row r="713" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B713" s="17"/>
       <c r="C713" s="17"/>
       <c r="D713" s="17"/>
@@ -12514,7 +12503,7 @@
       <c r="F713" s="19"/>
       <c r="G713" s="17"/>
     </row>
-    <row r="714" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B714" s="17"/>
       <c r="C714" s="17"/>
       <c r="D714" s="17"/>
@@ -12522,7 +12511,7 @@
       <c r="F714" s="19"/>
       <c r="G714" s="17"/>
     </row>
-    <row r="715" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B715" s="17"/>
       <c r="C715" s="17"/>
       <c r="D715" s="17"/>
@@ -12530,7 +12519,7 @@
       <c r="F715" s="19"/>
       <c r="G715" s="17"/>
     </row>
-    <row r="716" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B716" s="17"/>
       <c r="C716" s="17"/>
       <c r="D716" s="17"/>
@@ -12538,7 +12527,7 @@
       <c r="F716" s="19"/>
       <c r="G716" s="17"/>
     </row>
-    <row r="717" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B717" s="17"/>
       <c r="C717" s="17"/>
       <c r="D717" s="17"/>
@@ -12546,7 +12535,7 @@
       <c r="F717" s="19"/>
       <c r="G717" s="17"/>
     </row>
-    <row r="718" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B718" s="17"/>
       <c r="C718" s="17"/>
       <c r="D718" s="17"/>
@@ -12554,7 +12543,7 @@
       <c r="F718" s="19"/>
       <c r="G718" s="17"/>
     </row>
-    <row r="719" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B719" s="17"/>
       <c r="C719" s="17"/>
       <c r="D719" s="17"/>
@@ -12562,7 +12551,7 @@
       <c r="F719" s="19"/>
       <c r="G719" s="17"/>
     </row>
-    <row r="720" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B720" s="17"/>
       <c r="C720" s="17"/>
       <c r="D720" s="17"/>
@@ -12570,7 +12559,7 @@
       <c r="F720" s="19"/>
       <c r="G720" s="17"/>
     </row>
-    <row r="721" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B721" s="17"/>
       <c r="C721" s="17"/>
       <c r="D721" s="17"/>
@@ -12578,7 +12567,7 @@
       <c r="F721" s="19"/>
       <c r="G721" s="17"/>
     </row>
-    <row r="722" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B722" s="17"/>
       <c r="C722" s="17"/>
       <c r="D722" s="17"/>
@@ -12586,7 +12575,7 @@
       <c r="F722" s="19"/>
       <c r="G722" s="17"/>
     </row>
-    <row r="723" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B723" s="17"/>
       <c r="C723" s="17"/>
       <c r="D723" s="17"/>
@@ -12594,7 +12583,7 @@
       <c r="F723" s="19"/>
       <c r="G723" s="17"/>
     </row>
-    <row r="724" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B724" s="17"/>
       <c r="C724" s="17"/>
       <c r="D724" s="17"/>
@@ -12602,7 +12591,7 @@
       <c r="F724" s="19"/>
       <c r="G724" s="17"/>
     </row>
-    <row r="725" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B725" s="17"/>
       <c r="C725" s="17"/>
       <c r="D725" s="17"/>
@@ -12610,7 +12599,7 @@
       <c r="F725" s="19"/>
       <c r="G725" s="17"/>
     </row>
-    <row r="726" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B726" s="17"/>
       <c r="C726" s="17"/>
       <c r="D726" s="17"/>
@@ -12618,7 +12607,7 @@
       <c r="F726" s="19"/>
       <c r="G726" s="17"/>
     </row>
-    <row r="727" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B727" s="17"/>
       <c r="C727" s="17"/>
       <c r="D727" s="17"/>
@@ -12626,7 +12615,7 @@
       <c r="F727" s="19"/>
       <c r="G727" s="17"/>
     </row>
-    <row r="728" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B728" s="17"/>
       <c r="C728" s="17"/>
       <c r="D728" s="17"/>
@@ -12634,7 +12623,7 @@
       <c r="F728" s="19"/>
       <c r="G728" s="17"/>
     </row>
-    <row r="729" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B729" s="17"/>
       <c r="C729" s="17"/>
       <c r="D729" s="17"/>
@@ -12642,7 +12631,7 @@
       <c r="F729" s="19"/>
       <c r="G729" s="17"/>
     </row>
-    <row r="730" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B730" s="17"/>
       <c r="C730" s="17"/>
       <c r="D730" s="17"/>
@@ -12650,7 +12639,7 @@
       <c r="F730" s="19"/>
       <c r="G730" s="17"/>
     </row>
-    <row r="731" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B731" s="17"/>
       <c r="C731" s="17"/>
       <c r="D731" s="17"/>
@@ -12658,7 +12647,7 @@
       <c r="F731" s="19"/>
       <c r="G731" s="17"/>
     </row>
-    <row r="732" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B732" s="17"/>
       <c r="C732" s="17"/>
       <c r="D732" s="17"/>
@@ -12666,7 +12655,7 @@
       <c r="F732" s="19"/>
       <c r="G732" s="17"/>
     </row>
-    <row r="733" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B733" s="17"/>
       <c r="C733" s="17"/>
       <c r="D733" s="17"/>
@@ -12674,7 +12663,7 @@
       <c r="F733" s="19"/>
       <c r="G733" s="17"/>
     </row>
-    <row r="734" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B734" s="17"/>
       <c r="C734" s="17"/>
       <c r="D734" s="17"/>
@@ -12682,7 +12671,7 @@
       <c r="F734" s="19"/>
       <c r="G734" s="17"/>
     </row>
-    <row r="735" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B735" s="17"/>
       <c r="C735" s="17"/>
       <c r="D735" s="17"/>
@@ -12690,7 +12679,7 @@
       <c r="F735" s="19"/>
       <c r="G735" s="17"/>
     </row>
-    <row r="736" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B736" s="17"/>
       <c r="C736" s="17"/>
       <c r="D736" s="17"/>
@@ -12698,7 +12687,7 @@
       <c r="F736" s="19"/>
       <c r="G736" s="17"/>
     </row>
-    <row r="737" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B737" s="17"/>
       <c r="C737" s="17"/>
       <c r="D737" s="17"/>
@@ -12706,7 +12695,7 @@
       <c r="F737" s="19"/>
       <c r="G737" s="17"/>
     </row>
-    <row r="738" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B738" s="17"/>
       <c r="C738" s="17"/>
       <c r="D738" s="17"/>
@@ -12714,7 +12703,7 @@
       <c r="F738" s="19"/>
       <c r="G738" s="17"/>
     </row>
-    <row r="739" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B739" s="17"/>
       <c r="C739" s="17"/>
       <c r="D739" s="17"/>
@@ -12722,7 +12711,7 @@
       <c r="F739" s="19"/>
       <c r="G739" s="17"/>
     </row>
-    <row r="740" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B740" s="17"/>
       <c r="C740" s="17"/>
       <c r="D740" s="17"/>
@@ -12730,7 +12719,7 @@
       <c r="F740" s="19"/>
       <c r="G740" s="17"/>
     </row>
-    <row r="741" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B741" s="17"/>
       <c r="C741" s="17"/>
       <c r="D741" s="17"/>
@@ -12738,7 +12727,7 @@
       <c r="F741" s="19"/>
       <c r="G741" s="17"/>
     </row>
-    <row r="742" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B742" s="17"/>
       <c r="C742" s="17"/>
       <c r="D742" s="17"/>
@@ -12746,7 +12735,7 @@
       <c r="F742" s="19"/>
       <c r="G742" s="17"/>
     </row>
-    <row r="743" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B743" s="17"/>
       <c r="C743" s="17"/>
       <c r="D743" s="17"/>
@@ -12754,7 +12743,7 @@
       <c r="F743" s="19"/>
       <c r="G743" s="17"/>
     </row>
-    <row r="744" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B744" s="17"/>
       <c r="C744" s="17"/>
       <c r="D744" s="17"/>
@@ -12762,7 +12751,7 @@
       <c r="F744" s="19"/>
       <c r="G744" s="17"/>
     </row>
-    <row r="745" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B745" s="17"/>
       <c r="C745" s="17"/>
       <c r="D745" s="17"/>
@@ -12770,7 +12759,7 @@
       <c r="F745" s="19"/>
       <c r="G745" s="17"/>
     </row>
-    <row r="746" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B746" s="17"/>
       <c r="C746" s="17"/>
       <c r="D746" s="17"/>
@@ -12778,7 +12767,7 @@
       <c r="F746" s="19"/>
       <c r="G746" s="17"/>
     </row>
-    <row r="747" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B747" s="17"/>
       <c r="C747" s="17"/>
       <c r="D747" s="17"/>
@@ -12786,7 +12775,7 @@
       <c r="F747" s="19"/>
       <c r="G747" s="17"/>
     </row>
-    <row r="748" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B748" s="17"/>
       <c r="C748" s="17"/>
       <c r="D748" s="17"/>
@@ -12794,7 +12783,7 @@
       <c r="F748" s="19"/>
       <c r="G748" s="17"/>
     </row>
-    <row r="749" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B749" s="17"/>
       <c r="C749" s="17"/>
       <c r="D749" s="17"/>
@@ -12802,7 +12791,7 @@
       <c r="F749" s="19"/>
       <c r="G749" s="17"/>
     </row>
-    <row r="750" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B750" s="17"/>
       <c r="C750" s="17"/>
       <c r="D750" s="17"/>
@@ -12810,7 +12799,7 @@
       <c r="F750" s="19"/>
       <c r="G750" s="17"/>
     </row>
-    <row r="751" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B751" s="17"/>
       <c r="C751" s="17"/>
       <c r="D751" s="17"/>
@@ -12818,7 +12807,7 @@
       <c r="F751" s="19"/>
       <c r="G751" s="17"/>
     </row>
-    <row r="752" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B752" s="17"/>
       <c r="C752" s="17"/>
       <c r="D752" s="17"/>
@@ -12826,7 +12815,7 @@
       <c r="F752" s="19"/>
       <c r="G752" s="17"/>
     </row>
-    <row r="753" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B753" s="17"/>
       <c r="C753" s="17"/>
       <c r="D753" s="17"/>
@@ -12834,7 +12823,7 @@
       <c r="F753" s="19"/>
       <c r="G753" s="17"/>
     </row>
-    <row r="754" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B754" s="17"/>
       <c r="C754" s="17"/>
       <c r="D754" s="17"/>
@@ -12842,7 +12831,7 @@
       <c r="F754" s="19"/>
       <c r="G754" s="17"/>
     </row>
-    <row r="755" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B755" s="17"/>
       <c r="C755" s="17"/>
       <c r="D755" s="17"/>
@@ -12850,7 +12839,7 @@
       <c r="F755" s="19"/>
       <c r="G755" s="17"/>
     </row>
-    <row r="756" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B756" s="17"/>
       <c r="C756" s="17"/>
       <c r="D756" s="17"/>
@@ -12858,7 +12847,7 @@
       <c r="F756" s="19"/>
       <c r="G756" s="17"/>
     </row>
-    <row r="757" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B757" s="17"/>
       <c r="C757" s="17"/>
       <c r="D757" s="17"/>
@@ -12866,7 +12855,7 @@
       <c r="F757" s="19"/>
       <c r="G757" s="17"/>
     </row>
-    <row r="758" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B758" s="17"/>
       <c r="C758" s="17"/>
       <c r="D758" s="17"/>
@@ -12874,7 +12863,7 @@
       <c r="F758" s="19"/>
       <c r="G758" s="17"/>
     </row>
-    <row r="759" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B759" s="17"/>
       <c r="C759" s="17"/>
       <c r="D759" s="17"/>
@@ -12882,7 +12871,7 @@
       <c r="F759" s="19"/>
       <c r="G759" s="17"/>
     </row>
-    <row r="760" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B760" s="17"/>
       <c r="C760" s="17"/>
       <c r="D760" s="17"/>
@@ -12890,7 +12879,7 @@
       <c r="F760" s="19"/>
       <c r="G760" s="17"/>
     </row>
-    <row r="761" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B761" s="17"/>
       <c r="C761" s="17"/>
       <c r="D761" s="17"/>
@@ -12898,7 +12887,7 @@
       <c r="F761" s="19"/>
       <c r="G761" s="17"/>
     </row>
-    <row r="762" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B762" s="17"/>
       <c r="C762" s="17"/>
       <c r="D762" s="17"/>
@@ -12906,7 +12895,7 @@
       <c r="F762" s="19"/>
       <c r="G762" s="17"/>
     </row>
-    <row r="763" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B763" s="17"/>
       <c r="C763" s="17"/>
       <c r="D763" s="17"/>
@@ -12914,7 +12903,7 @@
       <c r="F763" s="19"/>
       <c r="G763" s="17"/>
     </row>
-    <row r="764" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B764" s="17"/>
       <c r="C764" s="17"/>
       <c r="D764" s="17"/>
@@ -12922,7 +12911,7 @@
       <c r="F764" s="19"/>
       <c r="G764" s="17"/>
     </row>
-    <row r="765" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B765" s="17"/>
       <c r="C765" s="17"/>
       <c r="D765" s="17"/>
@@ -12930,7 +12919,7 @@
       <c r="F765" s="19"/>
       <c r="G765" s="17"/>
     </row>
-    <row r="766" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B766" s="17"/>
       <c r="C766" s="17"/>
       <c r="D766" s="17"/>
@@ -12938,7 +12927,7 @@
       <c r="F766" s="19"/>
       <c r="G766" s="17"/>
     </row>
-    <row r="767" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B767" s="17"/>
       <c r="C767" s="17"/>
       <c r="D767" s="17"/>
@@ -12946,7 +12935,7 @@
       <c r="F767" s="19"/>
       <c r="G767" s="17"/>
     </row>
-    <row r="768" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B768" s="17"/>
       <c r="C768" s="17"/>
       <c r="D768" s="17"/>
@@ -12954,7 +12943,7 @@
       <c r="F768" s="19"/>
       <c r="G768" s="17"/>
     </row>
-    <row r="769" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B769" s="17"/>
       <c r="C769" s="17"/>
       <c r="D769" s="17"/>
@@ -12962,7 +12951,7 @@
       <c r="F769" s="19"/>
       <c r="G769" s="17"/>
     </row>
-    <row r="770" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B770" s="17"/>
       <c r="C770" s="17"/>
       <c r="D770" s="17"/>
@@ -12970,7 +12959,7 @@
       <c r="F770" s="19"/>
       <c r="G770" s="17"/>
     </row>
-    <row r="771" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B771" s="17"/>
       <c r="C771" s="17"/>
       <c r="D771" s="17"/>
@@ -12978,7 +12967,7 @@
       <c r="F771" s="19"/>
       <c r="G771" s="17"/>
     </row>
-    <row r="772" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B772" s="17"/>
       <c r="C772" s="17"/>
       <c r="D772" s="17"/>
@@ -12986,7 +12975,7 @@
       <c r="F772" s="19"/>
       <c r="G772" s="17"/>
     </row>
-    <row r="773" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B773" s="17"/>
       <c r="C773" s="17"/>
       <c r="D773" s="17"/>
@@ -12994,7 +12983,7 @@
       <c r="F773" s="19"/>
       <c r="G773" s="17"/>
     </row>
-    <row r="774" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B774" s="17"/>
       <c r="C774" s="17"/>
       <c r="D774" s="17"/>
@@ -13002,7 +12991,7 @@
       <c r="F774" s="19"/>
       <c r="G774" s="17"/>
     </row>
-    <row r="775" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B775" s="17"/>
       <c r="C775" s="17"/>
       <c r="D775" s="17"/>
@@ -13010,7 +12999,7 @@
       <c r="F775" s="19"/>
       <c r="G775" s="17"/>
     </row>
-    <row r="776" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B776" s="17"/>
       <c r="C776" s="17"/>
       <c r="D776" s="17"/>
@@ -13018,7 +13007,7 @@
       <c r="F776" s="19"/>
       <c r="G776" s="17"/>
     </row>
-    <row r="777" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B777" s="17"/>
       <c r="C777" s="17"/>
       <c r="D777" s="17"/>
@@ -13026,7 +13015,7 @@
       <c r="F777" s="19"/>
       <c r="G777" s="17"/>
     </row>
-    <row r="778" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B778" s="17"/>
       <c r="C778" s="17"/>
       <c r="D778" s="17"/>
@@ -13034,7 +13023,7 @@
       <c r="F778" s="19"/>
       <c r="G778" s="17"/>
     </row>
-    <row r="779" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B779" s="17"/>
       <c r="C779" s="17"/>
       <c r="D779" s="17"/>
@@ -13042,7 +13031,7 @@
       <c r="F779" s="19"/>
       <c r="G779" s="17"/>
     </row>
-    <row r="780" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B780" s="17"/>
       <c r="C780" s="17"/>
       <c r="D780" s="17"/>
@@ -13050,7 +13039,7 @@
       <c r="F780" s="19"/>
       <c r="G780" s="17"/>
     </row>
-    <row r="781" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B781" s="17"/>
       <c r="C781" s="17"/>
       <c r="D781" s="17"/>
@@ -13058,7 +13047,7 @@
       <c r="F781" s="19"/>
       <c r="G781" s="17"/>
     </row>
-    <row r="782" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B782" s="17"/>
       <c r="C782" s="17"/>
       <c r="D782" s="17"/>
@@ -13066,7 +13055,7 @@
       <c r="F782" s="19"/>
       <c r="G782" s="17"/>
     </row>
-    <row r="783" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B783" s="17"/>
       <c r="C783" s="17"/>
       <c r="D783" s="17"/>
@@ -13074,7 +13063,7 @@
       <c r="F783" s="19"/>
       <c r="G783" s="17"/>
     </row>
-    <row r="784" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B784" s="17"/>
       <c r="C784" s="17"/>
       <c r="D784" s="17"/>
@@ -13082,7 +13071,7 @@
       <c r="F784" s="19"/>
       <c r="G784" s="17"/>
     </row>
-    <row r="785" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B785" s="17"/>
       <c r="C785" s="17"/>
       <c r="D785" s="17"/>
@@ -13090,7 +13079,7 @@
       <c r="F785" s="19"/>
       <c r="G785" s="17"/>
     </row>
-    <row r="786" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B786" s="17"/>
       <c r="C786" s="17"/>
       <c r="D786" s="17"/>
@@ -13098,7 +13087,7 @@
       <c r="F786" s="19"/>
       <c r="G786" s="17"/>
     </row>
-    <row r="787" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B787" s="17"/>
       <c r="C787" s="17"/>
       <c r="D787" s="17"/>
@@ -13106,7 +13095,7 @@
       <c r="F787" s="19"/>
       <c r="G787" s="17"/>
     </row>
-    <row r="788" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B788" s="17"/>
       <c r="C788" s="17"/>
       <c r="D788" s="17"/>
@@ -13114,7 +13103,7 @@
       <c r="F788" s="19"/>
       <c r="G788" s="17"/>
     </row>
-    <row r="789" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B789" s="17"/>
       <c r="C789" s="17"/>
       <c r="D789" s="17"/>
@@ -13122,7 +13111,7 @@
       <c r="F789" s="19"/>
       <c r="G789" s="17"/>
     </row>
-    <row r="790" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B790" s="17"/>
       <c r="C790" s="17"/>
       <c r="D790" s="17"/>
@@ -13130,7 +13119,7 @@
       <c r="F790" s="19"/>
       <c r="G790" s="17"/>
     </row>
-    <row r="791" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B791" s="17"/>
       <c r="C791" s="17"/>
       <c r="D791" s="17"/>
@@ -13138,7 +13127,7 @@
       <c r="F791" s="19"/>
       <c r="G791" s="17"/>
     </row>
-    <row r="792" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B792" s="17"/>
       <c r="C792" s="17"/>
       <c r="D792" s="17"/>
@@ -13146,7 +13135,7 @@
       <c r="F792" s="19"/>
       <c r="G792" s="17"/>
     </row>
-    <row r="793" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B793" s="17"/>
       <c r="C793" s="17"/>
       <c r="D793" s="17"/>
@@ -13154,7 +13143,7 @@
       <c r="F793" s="19"/>
       <c r="G793" s="17"/>
     </row>
-    <row r="794" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B794" s="17"/>
       <c r="C794" s="17"/>
       <c r="D794" s="17"/>
@@ -13162,7 +13151,7 @@
       <c r="F794" s="19"/>
       <c r="G794" s="17"/>
     </row>
-    <row r="795" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B795" s="17"/>
       <c r="C795" s="17"/>
       <c r="D795" s="17"/>
@@ -13170,7 +13159,7 @@
       <c r="F795" s="19"/>
       <c r="G795" s="17"/>
     </row>
-    <row r="796" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B796" s="17"/>
       <c r="C796" s="17"/>
       <c r="D796" s="17"/>
@@ -13178,7 +13167,7 @@
       <c r="F796" s="19"/>
       <c r="G796" s="17"/>
     </row>
-    <row r="797" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B797" s="17"/>
       <c r="C797" s="17"/>
       <c r="D797" s="17"/>
@@ -13186,7 +13175,7 @@
       <c r="F797" s="19"/>
       <c r="G797" s="17"/>
     </row>
-    <row r="798" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B798" s="17"/>
       <c r="C798" s="17"/>
       <c r="D798" s="17"/>
@@ -13194,7 +13183,7 @@
       <c r="F798" s="19"/>
       <c r="G798" s="17"/>
     </row>
-    <row r="799" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B799" s="17"/>
       <c r="C799" s="17"/>
       <c r="D799" s="17"/>
@@ -13202,7 +13191,7 @@
       <c r="F799" s="19"/>
       <c r="G799" s="17"/>
     </row>
-    <row r="800" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B800" s="17"/>
       <c r="C800" s="17"/>
       <c r="D800" s="17"/>
@@ -13210,7 +13199,7 @@
       <c r="F800" s="19"/>
       <c r="G800" s="17"/>
     </row>
-    <row r="801" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B801" s="17"/>
       <c r="C801" s="17"/>
       <c r="D801" s="17"/>
@@ -13218,7 +13207,7 @@
       <c r="F801" s="19"/>
       <c r="G801" s="17"/>
     </row>
-    <row r="802" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B802" s="17"/>
       <c r="C802" s="17"/>
       <c r="D802" s="17"/>
@@ -13226,7 +13215,7 @@
       <c r="F802" s="19"/>
       <c r="G802" s="17"/>
     </row>
-    <row r="803" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B803" s="17"/>
       <c r="C803" s="17"/>
       <c r="D803" s="17"/>
@@ -13234,7 +13223,7 @@
       <c r="F803" s="19"/>
       <c r="G803" s="17"/>
     </row>
-    <row r="804" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B804" s="17"/>
       <c r="C804" s="17"/>
       <c r="D804" s="17"/>
@@ -13242,7 +13231,7 @@
       <c r="F804" s="19"/>
       <c r="G804" s="17"/>
     </row>
-    <row r="805" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B805" s="17"/>
       <c r="C805" s="17"/>
       <c r="D805" s="17"/>
@@ -13250,7 +13239,7 @@
       <c r="F805" s="19"/>
       <c r="G805" s="17"/>
     </row>
-    <row r="806" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B806" s="17"/>
       <c r="C806" s="17"/>
       <c r="D806" s="17"/>
@@ -13258,7 +13247,7 @@
       <c r="F806" s="19"/>
       <c r="G806" s="17"/>
     </row>
-    <row r="807" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B807" s="17"/>
       <c r="C807" s="17"/>
       <c r="D807" s="17"/>
@@ -13266,7 +13255,7 @@
       <c r="F807" s="19"/>
       <c r="G807" s="17"/>
     </row>
-    <row r="808" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B808" s="17"/>
       <c r="C808" s="17"/>
       <c r="D808" s="17"/>
@@ -13274,7 +13263,7 @@
       <c r="F808" s="19"/>
       <c r="G808" s="17"/>
     </row>
-    <row r="809" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B809" s="17"/>
       <c r="C809" s="17"/>
       <c r="D809" s="17"/>
@@ -13282,7 +13271,7 @@
       <c r="F809" s="19"/>
       <c r="G809" s="17"/>
     </row>
-    <row r="810" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B810" s="17"/>
       <c r="C810" s="17"/>
       <c r="D810" s="17"/>
@@ -13290,7 +13279,7 @@
       <c r="F810" s="19"/>
       <c r="G810" s="17"/>
     </row>
-    <row r="811" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B811" s="17"/>
       <c r="C811" s="17"/>
       <c r="D811" s="17"/>
@@ -13298,7 +13287,7 @@
       <c r="F811" s="19"/>
       <c r="G811" s="17"/>
     </row>
-    <row r="812" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B812" s="17"/>
       <c r="C812" s="17"/>
       <c r="D812" s="17"/>
@@ -13306,7 +13295,7 @@
       <c r="F812" s="19"/>
       <c r="G812" s="17"/>
     </row>
-    <row r="813" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B813" s="17"/>
       <c r="C813" s="17"/>
       <c r="D813" s="17"/>
@@ -13314,7 +13303,7 @@
       <c r="F813" s="19"/>
       <c r="G813" s="17"/>
     </row>
-    <row r="814" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B814" s="17"/>
       <c r="C814" s="17"/>
       <c r="D814" s="17"/>
@@ -13322,7 +13311,7 @@
       <c r="F814" s="19"/>
       <c r="G814" s="17"/>
     </row>
-    <row r="815" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B815" s="17"/>
       <c r="C815" s="17"/>
       <c r="D815" s="17"/>
@@ -13330,7 +13319,7 @@
       <c r="F815" s="19"/>
       <c r="G815" s="17"/>
     </row>
-    <row r="816" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B816" s="17"/>
       <c r="C816" s="17"/>
       <c r="D816" s="17"/>
@@ -13338,7 +13327,7 @@
       <c r="F816" s="19"/>
       <c r="G816" s="17"/>
     </row>
-    <row r="817" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B817" s="17"/>
       <c r="C817" s="17"/>
       <c r="D817" s="17"/>
@@ -13346,7 +13335,7 @@
       <c r="F817" s="19"/>
       <c r="G817" s="17"/>
     </row>
-    <row r="818" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B818" s="17"/>
       <c r="C818" s="17"/>
       <c r="D818" s="17"/>
@@ -13354,7 +13343,7 @@
       <c r="F818" s="19"/>
       <c r="G818" s="17"/>
     </row>
-    <row r="819" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B819" s="17"/>
       <c r="C819" s="17"/>
       <c r="D819" s="17"/>
@@ -13362,7 +13351,7 @@
       <c r="F819" s="19"/>
       <c r="G819" s="17"/>
     </row>
-    <row r="820" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B820" s="17"/>
       <c r="C820" s="17"/>
       <c r="D820" s="17"/>
@@ -13370,7 +13359,7 @@
       <c r="F820" s="19"/>
       <c r="G820" s="17"/>
     </row>
-    <row r="821" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B821" s="17"/>
       <c r="C821" s="17"/>
       <c r="D821" s="17"/>
@@ -13378,7 +13367,7 @@
       <c r="F821" s="19"/>
       <c r="G821" s="17"/>
     </row>
-    <row r="822" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B822" s="17"/>
       <c r="C822" s="17"/>
       <c r="D822" s="17"/>
@@ -13386,7 +13375,7 @@
       <c r="F822" s="19"/>
       <c r="G822" s="17"/>
     </row>
-    <row r="823" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B823" s="17"/>
       <c r="C823" s="17"/>
       <c r="D823" s="17"/>
@@ -13394,7 +13383,7 @@
       <c r="F823" s="19"/>
       <c r="G823" s="17"/>
     </row>
-    <row r="824" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B824" s="17"/>
       <c r="C824" s="17"/>
       <c r="D824" s="17"/>
@@ -13402,7 +13391,7 @@
       <c r="F824" s="19"/>
       <c r="G824" s="17"/>
     </row>
-    <row r="825" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B825" s="17"/>
       <c r="C825" s="17"/>
       <c r="D825" s="17"/>
@@ -13410,7 +13399,7 @@
       <c r="F825" s="19"/>
       <c r="G825" s="17"/>
     </row>
-    <row r="826" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B826" s="17"/>
       <c r="C826" s="17"/>
       <c r="D826" s="17"/>
@@ -13418,7 +13407,7 @@
       <c r="F826" s="19"/>
       <c r="G826" s="17"/>
     </row>
-    <row r="827" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B827" s="17"/>
       <c r="C827" s="17"/>
       <c r="D827" s="17"/>
@@ -13426,7 +13415,7 @@
       <c r="F827" s="19"/>
       <c r="G827" s="17"/>
     </row>
-    <row r="828" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B828" s="17"/>
       <c r="C828" s="17"/>
       <c r="D828" s="17"/>
@@ -13434,7 +13423,7 @@
       <c r="F828" s="19"/>
       <c r="G828" s="17"/>
     </row>
-    <row r="829" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B829" s="17"/>
       <c r="C829" s="17"/>
       <c r="D829" s="17"/>
@@ -13442,7 +13431,7 @@
       <c r="F829" s="19"/>
       <c r="G829" s="17"/>
     </row>
-    <row r="830" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B830" s="17"/>
       <c r="C830" s="17"/>
       <c r="D830" s="17"/>
@@ -13450,7 +13439,7 @@
       <c r="F830" s="19"/>
       <c r="G830" s="17"/>
     </row>
-    <row r="831" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B831" s="17"/>
       <c r="C831" s="17"/>
       <c r="D831" s="17"/>
@@ -13458,7 +13447,7 @@
       <c r="F831" s="19"/>
       <c r="G831" s="17"/>
     </row>
-    <row r="832" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B832" s="17"/>
       <c r="C832" s="17"/>
       <c r="D832" s="17"/>
@@ -13466,7 +13455,7 @@
       <c r="F832" s="19"/>
       <c r="G832" s="17"/>
     </row>
-    <row r="833" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B833" s="17"/>
       <c r="C833" s="17"/>
       <c r="D833" s="17"/>
@@ -13474,7 +13463,7 @@
       <c r="F833" s="19"/>
       <c r="G833" s="17"/>
     </row>
-    <row r="834" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B834" s="17"/>
       <c r="C834" s="17"/>
       <c r="D834" s="17"/>
@@ -13482,7 +13471,7 @@
       <c r="F834" s="19"/>
       <c r="G834" s="17"/>
     </row>
-    <row r="835" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B835" s="17"/>
       <c r="C835" s="17"/>
       <c r="D835" s="17"/>
@@ -13490,7 +13479,7 @@
       <c r="F835" s="19"/>
       <c r="G835" s="17"/>
     </row>
-    <row r="836" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B836" s="17"/>
       <c r="C836" s="17"/>
       <c r="D836" s="17"/>
@@ -13498,7 +13487,7 @@
       <c r="F836" s="19"/>
       <c r="G836" s="17"/>
     </row>
-    <row r="837" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B837" s="17"/>
       <c r="C837" s="17"/>
       <c r="D837" s="17"/>
@@ -13506,7 +13495,7 @@
       <c r="F837" s="19"/>
       <c r="G837" s="17"/>
     </row>
-    <row r="838" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B838" s="17"/>
       <c r="C838" s="17"/>
       <c r="D838" s="17"/>
@@ -13514,7 +13503,7 @@
       <c r="F838" s="19"/>
       <c r="G838" s="17"/>
     </row>
-    <row r="839" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B839" s="17"/>
       <c r="C839" s="17"/>
       <c r="D839" s="17"/>
@@ -13522,7 +13511,7 @@
       <c r="F839" s="19"/>
       <c r="G839" s="17"/>
     </row>
-    <row r="840" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B840" s="17"/>
       <c r="C840" s="17"/>
       <c r="D840" s="17"/>
@@ -13530,7 +13519,7 @@
       <c r="F840" s="19"/>
       <c r="G840" s="17"/>
     </row>
-    <row r="841" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B841" s="17"/>
       <c r="C841" s="17"/>
       <c r="D841" s="17"/>
@@ -13538,7 +13527,7 @@
       <c r="F841" s="19"/>
       <c r="G841" s="17"/>
     </row>
-    <row r="842" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B842" s="17"/>
       <c r="C842" s="17"/>
       <c r="D842" s="17"/>
@@ -13546,7 +13535,7 @@
       <c r="F842" s="19"/>
       <c r="G842" s="17"/>
     </row>
-    <row r="843" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B843" s="17"/>
       <c r="C843" s="17"/>
       <c r="D843" s="17"/>
@@ -13554,7 +13543,7 @@
       <c r="F843" s="19"/>
       <c r="G843" s="17"/>
     </row>
-    <row r="844" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B844" s="17"/>
       <c r="C844" s="17"/>
       <c r="D844" s="17"/>
@@ -13562,7 +13551,7 @@
       <c r="F844" s="19"/>
       <c r="G844" s="17"/>
     </row>
-    <row r="845" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B845" s="17"/>
       <c r="C845" s="17"/>
       <c r="D845" s="17"/>
@@ -13570,7 +13559,7 @@
       <c r="F845" s="19"/>
       <c r="G845" s="17"/>
     </row>
-    <row r="846" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B846" s="17"/>
       <c r="C846" s="17"/>
       <c r="D846" s="17"/>
@@ -13578,7 +13567,7 @@
       <c r="F846" s="19"/>
       <c r="G846" s="17"/>
     </row>
-    <row r="847" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B847" s="17"/>
       <c r="C847" s="17"/>
       <c r="D847" s="17"/>
@@ -13586,7 +13575,7 @@
       <c r="F847" s="19"/>
       <c r="G847" s="17"/>
     </row>
-    <row r="848" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B848" s="17"/>
       <c r="C848" s="17"/>
       <c r="D848" s="17"/>
@@ -13594,7 +13583,7 @@
       <c r="F848" s="19"/>
       <c r="G848" s="17"/>
     </row>
-    <row r="849" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B849" s="17"/>
       <c r="C849" s="17"/>
       <c r="D849" s="17"/>
@@ -13602,7 +13591,7 @@
       <c r="F849" s="19"/>
       <c r="G849" s="17"/>
     </row>
-    <row r="850" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B850" s="17"/>
       <c r="C850" s="17"/>
       <c r="D850" s="17"/>
@@ -13610,7 +13599,7 @@
       <c r="F850" s="19"/>
       <c r="G850" s="17"/>
     </row>
-    <row r="851" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B851" s="17"/>
       <c r="C851" s="17"/>
       <c r="D851" s="17"/>
@@ -13618,7 +13607,7 @@
       <c r="F851" s="19"/>
       <c r="G851" s="17"/>
     </row>
-    <row r="852" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B852" s="17"/>
       <c r="C852" s="17"/>
       <c r="D852" s="17"/>
@@ -13626,7 +13615,7 @@
       <c r="F852" s="19"/>
       <c r="G852" s="17"/>
     </row>
-    <row r="853" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B853" s="17"/>
       <c r="C853" s="17"/>
       <c r="D853" s="17"/>
@@ -13634,7 +13623,7 @@
       <c r="F853" s="19"/>
       <c r="G853" s="17"/>
     </row>
-    <row r="854" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B854" s="17"/>
       <c r="C854" s="17"/>
       <c r="D854" s="17"/>
@@ -13642,7 +13631,7 @@
       <c r="F854" s="19"/>
       <c r="G854" s="17"/>
     </row>
-    <row r="855" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B855" s="17"/>
       <c r="C855" s="17"/>
       <c r="D855" s="17"/>
@@ -13650,7 +13639,7 @@
       <c r="F855" s="19"/>
       <c r="G855" s="17"/>
     </row>
-    <row r="856" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B856" s="17"/>
       <c r="C856" s="17"/>
       <c r="D856" s="17"/>
@@ -13658,7 +13647,7 @@
       <c r="F856" s="19"/>
       <c r="G856" s="17"/>
     </row>
-    <row r="857" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B857" s="17"/>
       <c r="C857" s="17"/>
       <c r="D857" s="17"/>
@@ -13666,7 +13655,7 @@
       <c r="F857" s="19"/>
       <c r="G857" s="17"/>
     </row>
-    <row r="858" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B858" s="17"/>
       <c r="C858" s="17"/>
       <c r="D858" s="17"/>
@@ -13674,7 +13663,7 @@
       <c r="F858" s="19"/>
       <c r="G858" s="17"/>
     </row>
-    <row r="859" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B859" s="17"/>
       <c r="C859" s="17"/>
       <c r="D859" s="17"/>
@@ -13682,7 +13671,7 @@
       <c r="F859" s="19"/>
       <c r="G859" s="17"/>
     </row>
-    <row r="860" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B860" s="17"/>
       <c r="C860" s="17"/>
       <c r="D860" s="17"/>
@@ -13690,7 +13679,7 @@
       <c r="F860" s="19"/>
       <c r="G860" s="17"/>
     </row>
-    <row r="861" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B861" s="17"/>
       <c r="C861" s="17"/>
       <c r="D861" s="17"/>
@@ -13698,7 +13687,7 @@
       <c r="F861" s="19"/>
       <c r="G861" s="17"/>
     </row>
-    <row r="862" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B862" s="17"/>
       <c r="C862" s="17"/>
       <c r="D862" s="17"/>
@@ -13706,7 +13695,7 @@
       <c r="F862" s="19"/>
       <c r="G862" s="17"/>
     </row>
-    <row r="863" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B863" s="17"/>
       <c r="C863" s="17"/>
       <c r="D863" s="17"/>
@@ -13714,7 +13703,7 @@
       <c r="F863" s="19"/>
       <c r="G863" s="17"/>
     </row>
-    <row r="864" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B864" s="17"/>
       <c r="C864" s="17"/>
       <c r="D864" s="17"/>
@@ -13722,7 +13711,7 @@
       <c r="F864" s="19"/>
       <c r="G864" s="17"/>
     </row>
-    <row r="865" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B865" s="17"/>
       <c r="C865" s="17"/>
       <c r="D865" s="17"/>
@@ -13730,7 +13719,7 @@
       <c r="F865" s="19"/>
       <c r="G865" s="17"/>
     </row>
-    <row r="866" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B866" s="17"/>
       <c r="C866" s="17"/>
       <c r="D866" s="17"/>
@@ -13738,7 +13727,7 @@
       <c r="F866" s="19"/>
       <c r="G866" s="17"/>
     </row>
-    <row r="867" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B867" s="17"/>
       <c r="C867" s="17"/>
       <c r="D867" s="17"/>
@@ -13746,7 +13735,7 @@
       <c r="F867" s="19"/>
       <c r="G867" s="17"/>
     </row>
-    <row r="868" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B868" s="17"/>
       <c r="C868" s="17"/>
       <c r="D868" s="17"/>
@@ -13754,7 +13743,7 @@
       <c r="F868" s="19"/>
       <c r="G868" s="17"/>
     </row>
-    <row r="869" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B869" s="17"/>
       <c r="C869" s="17"/>
       <c r="D869" s="17"/>
@@ -13762,7 +13751,7 @@
       <c r="F869" s="19"/>
       <c r="G869" s="17"/>
     </row>
-    <row r="870" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B870" s="17"/>
       <c r="C870" s="17"/>
       <c r="D870" s="17"/>
@@ -13770,7 +13759,7 @@
       <c r="F870" s="19"/>
       <c r="G870" s="17"/>
     </row>
-    <row r="871" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B871" s="17"/>
       <c r="C871" s="17"/>
       <c r="D871" s="17"/>
@@ -13778,7 +13767,7 @@
       <c r="F871" s="19"/>
       <c r="G871" s="17"/>
     </row>
-    <row r="872" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B872" s="17"/>
       <c r="C872" s="17"/>
       <c r="D872" s="17"/>
@@ -13786,7 +13775,7 @@
       <c r="F872" s="19"/>
       <c r="G872" s="17"/>
     </row>
-    <row r="873" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B873" s="17"/>
       <c r="C873" s="17"/>
       <c r="D873" s="17"/>
@@ -13794,7 +13783,7 @@
       <c r="F873" s="19"/>
       <c r="G873" s="17"/>
     </row>
-    <row r="874" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B874" s="17"/>
       <c r="C874" s="17"/>
       <c r="D874" s="17"/>
@@ -13802,7 +13791,7 @@
       <c r="F874" s="19"/>
       <c r="G874" s="17"/>
     </row>
-    <row r="875" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B875" s="17"/>
       <c r="C875" s="17"/>
       <c r="D875" s="17"/>
@@ -13810,7 +13799,7 @@
       <c r="F875" s="19"/>
       <c r="G875" s="17"/>
     </row>
-    <row r="876" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B876" s="17"/>
       <c r="C876" s="17"/>
       <c r="D876" s="17"/>
@@ -13818,7 +13807,7 @@
       <c r="F876" s="19"/>
       <c r="G876" s="17"/>
     </row>
-    <row r="877" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B877" s="17"/>
       <c r="C877" s="17"/>
       <c r="D877" s="17"/>
@@ -13826,7 +13815,7 @@
       <c r="F877" s="19"/>
       <c r="G877" s="17"/>
     </row>
-    <row r="878" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B878" s="17"/>
       <c r="C878" s="17"/>
       <c r="D878" s="17"/>
@@ -13834,7 +13823,7 @@
       <c r="F878" s="19"/>
       <c r="G878" s="17"/>
     </row>
-    <row r="879" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B879" s="17"/>
       <c r="C879" s="17"/>
       <c r="D879" s="17"/>
@@ -13842,7 +13831,7 @@
       <c r="F879" s="19"/>
       <c r="G879" s="17"/>
     </row>
-    <row r="880" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B880" s="17"/>
       <c r="C880" s="17"/>
       <c r="D880" s="17"/>
@@ -13850,7 +13839,7 @@
       <c r="F880" s="19"/>
       <c r="G880" s="17"/>
     </row>
-    <row r="881" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B881" s="17"/>
       <c r="C881" s="17"/>
       <c r="D881" s="17"/>
@@ -13858,7 +13847,7 @@
       <c r="F881" s="19"/>
       <c r="G881" s="17"/>
     </row>
-    <row r="882" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B882" s="17"/>
       <c r="C882" s="17"/>
       <c r="D882" s="17"/>
@@ -13866,7 +13855,7 @@
       <c r="F882" s="19"/>
       <c r="G882" s="17"/>
     </row>
-    <row r="883" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B883" s="17"/>
       <c r="C883" s="17"/>
       <c r="D883" s="17"/>
@@ -13874,7 +13863,7 @@
       <c r="F883" s="19"/>
       <c r="G883" s="17"/>
     </row>
-    <row r="884" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B884" s="17"/>
       <c r="C884" s="17"/>
       <c r="D884" s="17"/>
@@ -13882,7 +13871,7 @@
       <c r="F884" s="19"/>
       <c r="G884" s="17"/>
     </row>
-    <row r="885" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B885" s="17"/>
       <c r="C885" s="17"/>
       <c r="D885" s="17"/>
@@ -13890,7 +13879,7 @@
       <c r="F885" s="19"/>
       <c r="G885" s="17"/>
     </row>
-    <row r="886" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B886" s="17"/>
       <c r="C886" s="17"/>
       <c r="D886" s="17"/>
@@ -13898,7 +13887,7 @@
       <c r="F886" s="19"/>
       <c r="G886" s="17"/>
     </row>
-    <row r="887" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B887" s="17"/>
       <c r="C887" s="17"/>
       <c r="D887" s="17"/>
@@ -13906,7 +13895,7 @@
       <c r="F887" s="19"/>
       <c r="G887" s="17"/>
     </row>
-    <row r="888" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B888" s="17"/>
       <c r="C888" s="17"/>
       <c r="D888" s="17"/>
@@ -13914,7 +13903,7 @@
       <c r="F888" s="19"/>
       <c r="G888" s="17"/>
     </row>
-    <row r="889" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B889" s="17"/>
       <c r="C889" s="17"/>
       <c r="D889" s="17"/>
@@ -13922,7 +13911,7 @@
       <c r="F889" s="19"/>
       <c r="G889" s="17"/>
     </row>
-    <row r="890" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B890" s="17"/>
       <c r="C890" s="17"/>
       <c r="D890" s="17"/>
@@ -13930,7 +13919,7 @@
       <c r="F890" s="19"/>
       <c r="G890" s="17"/>
     </row>
-    <row r="891" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B891" s="17"/>
       <c r="C891" s="17"/>
       <c r="D891" s="17"/>
@@ -13938,7 +13927,7 @@
       <c r="F891" s="19"/>
       <c r="G891" s="17"/>
     </row>
-    <row r="892" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B892" s="17"/>
       <c r="C892" s="17"/>
       <c r="D892" s="17"/>
@@ -13946,7 +13935,7 @@
       <c r="F892" s="19"/>
       <c r="G892" s="17"/>
     </row>
-    <row r="893" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B893" s="17"/>
       <c r="C893" s="17"/>
       <c r="D893" s="17"/>
@@ -13954,7 +13943,7 @@
       <c r="F893" s="19"/>
       <c r="G893" s="17"/>
     </row>
-    <row r="894" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B894" s="17"/>
       <c r="C894" s="17"/>
       <c r="D894" s="17"/>
@@ -13962,7 +13951,7 @@
       <c r="F894" s="19"/>
       <c r="G894" s="17"/>
     </row>
-    <row r="895" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B895" s="17"/>
       <c r="C895" s="17"/>
       <c r="D895" s="17"/>
@@ -13970,7 +13959,7 @@
       <c r="F895" s="19"/>
       <c r="G895" s="17"/>
     </row>
-    <row r="896" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B896" s="17"/>
       <c r="C896" s="17"/>
       <c r="D896" s="17"/>
@@ -13978,7 +13967,7 @@
       <c r="F896" s="19"/>
       <c r="G896" s="17"/>
     </row>
-    <row r="897" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B897" s="17"/>
       <c r="C897" s="17"/>
       <c r="D897" s="17"/>
@@ -13986,7 +13975,7 @@
       <c r="F897" s="19"/>
       <c r="G897" s="17"/>
     </row>
-    <row r="898" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B898" s="17"/>
       <c r="C898" s="17"/>
       <c r="D898" s="17"/>
@@ -13994,7 +13983,7 @@
       <c r="F898" s="19"/>
       <c r="G898" s="17"/>
     </row>
-    <row r="899" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B899" s="17"/>
       <c r="C899" s="17"/>
       <c r="D899" s="17"/>
@@ -14002,7 +13991,7 @@
       <c r="F899" s="19"/>
       <c r="G899" s="17"/>
     </row>
-    <row r="900" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B900" s="17"/>
       <c r="C900" s="17"/>
       <c r="D900" s="17"/>
@@ -14010,7 +13999,7 @@
       <c r="F900" s="19"/>
       <c r="G900" s="17"/>
     </row>
-    <row r="901" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B901" s="17"/>
       <c r="C901" s="17"/>
       <c r="D901" s="17"/>
@@ -14018,7 +14007,7 @@
       <c r="F901" s="19"/>
       <c r="G901" s="17"/>
     </row>
-    <row r="902" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B902" s="17"/>
       <c r="C902" s="17"/>
       <c r="D902" s="17"/>
@@ -14026,7 +14015,7 @@
       <c r="F902" s="19"/>
       <c r="G902" s="17"/>
     </row>
-    <row r="903" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B903" s="17"/>
       <c r="C903" s="17"/>
       <c r="D903" s="17"/>
@@ -14034,7 +14023,7 @@
       <c r="F903" s="19"/>
       <c r="G903" s="17"/>
     </row>
-    <row r="904" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B904" s="17"/>
       <c r="C904" s="17"/>
       <c r="D904" s="17"/>
@@ -14042,7 +14031,7 @@
       <c r="F904" s="19"/>
       <c r="G904" s="17"/>
     </row>
-    <row r="905" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B905" s="17"/>
       <c r="C905" s="17"/>
       <c r="D905" s="17"/>
@@ -14050,7 +14039,7 @@
       <c r="F905" s="19"/>
       <c r="G905" s="17"/>
     </row>
-    <row r="906" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B906" s="17"/>
       <c r="C906" s="17"/>
       <c r="D906" s="17"/>
@@ -14058,7 +14047,7 @@
       <c r="F906" s="19"/>
       <c r="G906" s="17"/>
     </row>
-    <row r="907" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B907" s="17"/>
       <c r="C907" s="17"/>
       <c r="D907" s="17"/>
@@ -14066,7 +14055,7 @@
       <c r="F907" s="19"/>
       <c r="G907" s="17"/>
     </row>
-    <row r="908" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B908" s="17"/>
       <c r="C908" s="17"/>
       <c r="D908" s="17"/>
@@ -14074,7 +14063,7 @@
       <c r="F908" s="19"/>
       <c r="G908" s="17"/>
     </row>
-    <row r="909" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B909" s="17"/>
       <c r="C909" s="17"/>
       <c r="D909" s="17"/>
@@ -14082,7 +14071,7 @@
       <c r="F909" s="19"/>
       <c r="G909" s="17"/>
     </row>
-    <row r="910" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B910" s="17"/>
       <c r="C910" s="17"/>
       <c r="D910" s="17"/>
@@ -14090,7 +14079,7 @@
       <c r="F910" s="19"/>
       <c r="G910" s="17"/>
     </row>
-    <row r="911" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B911" s="17"/>
       <c r="C911" s="17"/>
       <c r="D911" s="17"/>
@@ -14098,7 +14087,7 @@
       <c r="F911" s="19"/>
       <c r="G911" s="17"/>
     </row>
-    <row r="912" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B912" s="17"/>
       <c r="C912" s="17"/>
       <c r="D912" s="17"/>
@@ -14106,7 +14095,7 @@
       <c r="F912" s="19"/>
       <c r="G912" s="17"/>
     </row>
-    <row r="913" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B913" s="17"/>
       <c r="C913" s="17"/>
       <c r="D913" s="17"/>
@@ -14114,7 +14103,7 @@
       <c r="F913" s="19"/>
       <c r="G913" s="17"/>
     </row>
-    <row r="914" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B914" s="17"/>
       <c r="C914" s="17"/>
       <c r="D914" s="17"/>
@@ -14122,7 +14111,7 @@
       <c r="F914" s="19"/>
       <c r="G914" s="17"/>
     </row>
-    <row r="915" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B915" s="17"/>
       <c r="C915" s="17"/>
       <c r="D915" s="17"/>
@@ -14130,7 +14119,7 @@
       <c r="F915" s="19"/>
       <c r="G915" s="17"/>
     </row>
-    <row r="916" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B916" s="17"/>
       <c r="C916" s="17"/>
       <c r="D916" s="17"/>
@@ -14138,7 +14127,7 @@
       <c r="F916" s="19"/>
       <c r="G916" s="17"/>
     </row>
-    <row r="917" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B917" s="17"/>
       <c r="C917" s="17"/>
       <c r="D917" s="17"/>
@@ -14146,7 +14135,7 @@
       <c r="F917" s="19"/>
       <c r="G917" s="17"/>
     </row>
-    <row r="918" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B918" s="17"/>
       <c r="C918" s="17"/>
       <c r="D918" s="17"/>
@@ -14154,7 +14143,7 @@
       <c r="F918" s="19"/>
       <c r="G918" s="17"/>
     </row>
-    <row r="919" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B919" s="17"/>
       <c r="C919" s="17"/>
       <c r="D919" s="17"/>
@@ -14162,7 +14151,7 @@
       <c r="F919" s="19"/>
       <c r="G919" s="17"/>
     </row>
-    <row r="920" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B920" s="17"/>
       <c r="C920" s="17"/>
       <c r="D920" s="17"/>
@@ -14170,7 +14159,7 @@
       <c r="F920" s="19"/>
       <c r="G920" s="17"/>
     </row>
-    <row r="921" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B921" s="17"/>
       <c r="C921" s="17"/>
       <c r="D921" s="17"/>
@@ -14178,7 +14167,7 @@
       <c r="F921" s="19"/>
       <c r="G921" s="17"/>
     </row>
-    <row r="922" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B922" s="17"/>
       <c r="C922" s="17"/>
       <c r="D922" s="17"/>
@@ -14186,7 +14175,7 @@
       <c r="F922" s="19"/>
       <c r="G922" s="17"/>
     </row>
-    <row r="923" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B923" s="17"/>
       <c r="C923" s="17"/>
       <c r="D923" s="17"/>
@@ -14194,7 +14183,7 @@
       <c r="F923" s="19"/>
       <c r="G923" s="17"/>
     </row>
-    <row r="924" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B924" s="17"/>
       <c r="C924" s="17"/>
       <c r="D924" s="17"/>
@@ -14202,7 +14191,7 @@
       <c r="F924" s="19"/>
       <c r="G924" s="17"/>
     </row>
-    <row r="925" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B925" s="17"/>
       <c r="C925" s="17"/>
       <c r="D925" s="17"/>
@@ -14210,7 +14199,7 @@
       <c r="F925" s="19"/>
       <c r="G925" s="17"/>
     </row>
-    <row r="926" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B926" s="17"/>
       <c r="C926" s="17"/>
       <c r="D926" s="17"/>
@@ -14218,7 +14207,7 @@
       <c r="F926" s="19"/>
       <c r="G926" s="17"/>
     </row>
-    <row r="927" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B927" s="17"/>
       <c r="C927" s="17"/>
       <c r="D927" s="17"/>
@@ -14226,7 +14215,7 @@
       <c r="F927" s="19"/>
       <c r="G927" s="17"/>
     </row>
-    <row r="928" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B928" s="17"/>
       <c r="C928" s="17"/>
       <c r="D928" s="17"/>
@@ -14234,7 +14223,7 @@
       <c r="F928" s="19"/>
       <c r="G928" s="17"/>
     </row>
-    <row r="929" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B929" s="17"/>
       <c r="C929" s="17"/>
       <c r="D929" s="17"/>
@@ -14242,7 +14231,7 @@
       <c r="F929" s="19"/>
       <c r="G929" s="17"/>
     </row>
-    <row r="930" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B930" s="17"/>
       <c r="C930" s="17"/>
       <c r="D930" s="17"/>
@@ -14250,7 +14239,7 @@
       <c r="F930" s="19"/>
       <c r="G930" s="17"/>
     </row>
-    <row r="931" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B931" s="17"/>
       <c r="C931" s="17"/>
       <c r="D931" s="17"/>
@@ -14258,7 +14247,7 @@
       <c r="F931" s="19"/>
       <c r="G931" s="17"/>
     </row>
-    <row r="932" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B932" s="17"/>
       <c r="C932" s="17"/>
       <c r="D932" s="17"/>
@@ -14266,7 +14255,7 @@
       <c r="F932" s="19"/>
       <c r="G932" s="17"/>
     </row>
-    <row r="933" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B933" s="17"/>
       <c r="C933" s="17"/>
       <c r="D933" s="17"/>
@@ -14274,7 +14263,7 @@
       <c r="F933" s="19"/>
       <c r="G933" s="17"/>
     </row>
-    <row r="934" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B934" s="17"/>
       <c r="C934" s="17"/>
       <c r="D934" s="17"/>
@@ -14282,7 +14271,7 @@
       <c r="F934" s="19"/>
       <c r="G934" s="17"/>
     </row>
-    <row r="935" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B935" s="17"/>
       <c r="C935" s="17"/>
       <c r="D935" s="17"/>
@@ -14290,7 +14279,7 @@
       <c r="F935" s="19"/>
       <c r="G935" s="17"/>
     </row>
-    <row r="936" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B936" s="17"/>
       <c r="C936" s="17"/>
       <c r="D936" s="17"/>
@@ -14298,7 +14287,7 @@
       <c r="F936" s="19"/>
       <c r="G936" s="17"/>
     </row>
-    <row r="937" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B937" s="17"/>
       <c r="C937" s="17"/>
       <c r="D937" s="17"/>
@@ -14306,7 +14295,7 @@
       <c r="F937" s="19"/>
       <c r="G937" s="17"/>
     </row>
-    <row r="938" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B938" s="17"/>
       <c r="C938" s="17"/>
       <c r="D938" s="17"/>
@@ -14314,7 +14303,7 @@
       <c r="F938" s="19"/>
       <c r="G938" s="17"/>
     </row>
-    <row r="939" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B939" s="17"/>
       <c r="C939" s="17"/>
       <c r="D939" s="17"/>
@@ -14322,7 +14311,7 @@
       <c r="F939" s="19"/>
       <c r="G939" s="17"/>
     </row>
-    <row r="940" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B940" s="17"/>
       <c r="C940" s="17"/>
       <c r="D940" s="17"/>
@@ -14330,7 +14319,7 @@
       <c r="F940" s="19"/>
       <c r="G940" s="17"/>
     </row>
-    <row r="941" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B941" s="17"/>
       <c r="C941" s="17"/>
       <c r="D941" s="17"/>
@@ -14338,7 +14327,7 @@
       <c r="F941" s="19"/>
       <c r="G941" s="17"/>
     </row>
-    <row r="942" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B942" s="17"/>
       <c r="C942" s="17"/>
       <c r="D942" s="17"/>
@@ -14346,7 +14335,7 @@
       <c r="F942" s="19"/>
       <c r="G942" s="17"/>
     </row>
-    <row r="943" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B943" s="17"/>
       <c r="C943" s="17"/>
       <c r="D943" s="17"/>
@@ -14354,7 +14343,7 @@
       <c r="F943" s="19"/>
       <c r="G943" s="17"/>
     </row>
-    <row r="944" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B944" s="17"/>
       <c r="C944" s="17"/>
       <c r="D944" s="17"/>
@@ -14362,7 +14351,7 @@
       <c r="F944" s="19"/>
       <c r="G944" s="17"/>
     </row>
-    <row r="945" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B945" s="17"/>
       <c r="C945" s="17"/>
       <c r="D945" s="17"/>
@@ -14370,7 +14359,7 @@
       <c r="F945" s="19"/>
       <c r="G945" s="17"/>
     </row>
-    <row r="946" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B946" s="17"/>
       <c r="C946" s="17"/>
       <c r="D946" s="17"/>
@@ -14378,7 +14367,7 @@
       <c r="F946" s="19"/>
       <c r="G946" s="17"/>
     </row>
-    <row r="947" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B947" s="17"/>
       <c r="C947" s="17"/>
       <c r="D947" s="17"/>
@@ -14386,7 +14375,7 @@
       <c r="F947" s="19"/>
       <c r="G947" s="17"/>
     </row>
-    <row r="948" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B948" s="17"/>
       <c r="C948" s="17"/>
       <c r="D948" s="17"/>
@@ -14394,7 +14383,7 @@
       <c r="F948" s="19"/>
       <c r="G948" s="17"/>
     </row>
-    <row r="949" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B949" s="17"/>
       <c r="C949" s="17"/>
       <c r="D949" s="17"/>
@@ -14402,7 +14391,7 @@
       <c r="F949" s="19"/>
       <c r="G949" s="17"/>
     </row>
-    <row r="950" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B950" s="17"/>
       <c r="C950" s="17"/>
       <c r="D950" s="17"/>
@@ -14410,7 +14399,7 @@
       <c r="F950" s="19"/>
       <c r="G950" s="17"/>
     </row>
-    <row r="951" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B951" s="17"/>
       <c r="C951" s="17"/>
       <c r="D951" s="17"/>
@@ -14418,7 +14407,7 @@
       <c r="F951" s="19"/>
       <c r="G951" s="17"/>
     </row>
-    <row r="952" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B952" s="17"/>
       <c r="C952" s="17"/>
       <c r="D952" s="17"/>
@@ -14426,7 +14415,7 @@
       <c r="F952" s="19"/>
       <c r="G952" s="17"/>
     </row>
-    <row r="953" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B953" s="17"/>
       <c r="C953" s="17"/>
       <c r="D953" s="17"/>
@@ -14434,7 +14423,7 @@
       <c r="F953" s="19"/>
       <c r="G953" s="17"/>
     </row>
-    <row r="954" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B954" s="17"/>
       <c r="C954" s="17"/>
       <c r="D954" s="17"/>
@@ -14442,7 +14431,7 @@
       <c r="F954" s="19"/>
       <c r="G954" s="17"/>
     </row>
-    <row r="955" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B955" s="17"/>
       <c r="C955" s="17"/>
       <c r="D955" s="17"/>
@@ -14450,7 +14439,7 @@
       <c r="F955" s="19"/>
       <c r="G955" s="17"/>
     </row>
-    <row r="956" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B956" s="17"/>
       <c r="C956" s="17"/>
       <c r="D956" s="17"/>
@@ -14458,7 +14447,7 @@
       <c r="F956" s="19"/>
       <c r="G956" s="17"/>
     </row>
-    <row r="957" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B957" s="17"/>
       <c r="C957" s="17"/>
       <c r="D957" s="17"/>
@@ -14466,7 +14455,7 @@
       <c r="F957" s="19"/>
       <c r="G957" s="17"/>
     </row>
-    <row r="958" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B958" s="17"/>
       <c r="C958" s="17"/>
       <c r="D958" s="17"/>
@@ -14474,7 +14463,7 @@
       <c r="F958" s="19"/>
       <c r="G958" s="17"/>
     </row>
-    <row r="959" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B959" s="17"/>
       <c r="C959" s="17"/>
       <c r="D959" s="17"/>
@@ -14482,7 +14471,7 @@
       <c r="F959" s="19"/>
       <c r="G959" s="17"/>
     </row>
-    <row r="960" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B960" s="17"/>
       <c r="C960" s="17"/>
       <c r="D960" s="17"/>
@@ -14490,7 +14479,7 @@
       <c r="F960" s="19"/>
       <c r="G960" s="17"/>
     </row>
-    <row r="961" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B961" s="17"/>
       <c r="C961" s="17"/>
       <c r="D961" s="17"/>
@@ -14498,7 +14487,7 @@
       <c r="F961" s="19"/>
       <c r="G961" s="17"/>
     </row>
-    <row r="962" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B962" s="17"/>
       <c r="C962" s="17"/>
       <c r="D962" s="17"/>
@@ -14506,7 +14495,7 @@
       <c r="F962" s="19"/>
       <c r="G962" s="17"/>
     </row>
-    <row r="963" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B963" s="17"/>
       <c r="C963" s="17"/>
       <c r="D963" s="17"/>
@@ -14514,7 +14503,7 @@
       <c r="F963" s="19"/>
       <c r="G963" s="17"/>
     </row>
-    <row r="964" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B964" s="17"/>
       <c r="C964" s="17"/>
       <c r="D964" s="17"/>
@@ -14522,7 +14511,7 @@
       <c r="F964" s="19"/>
       <c r="G964" s="17"/>
     </row>
-    <row r="965" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B965" s="17"/>
       <c r="C965" s="17"/>
       <c r="D965" s="17"/>
@@ -14530,7 +14519,7 @@
       <c r="F965" s="19"/>
       <c r="G965" s="17"/>
     </row>
-    <row r="966" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B966" s="17"/>
       <c r="C966" s="17"/>
       <c r="D966" s="17"/>
@@ -14538,7 +14527,7 @@
       <c r="F966" s="19"/>
       <c r="G966" s="17"/>
     </row>
-    <row r="967" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B967" s="17"/>
       <c r="C967" s="17"/>
       <c r="D967" s="17"/>
@@ -14546,7 +14535,7 @@
       <c r="F967" s="19"/>
       <c r="G967" s="17"/>
     </row>
-    <row r="968" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B968" s="17"/>
       <c r="C968" s="17"/>
       <c r="D968" s="17"/>
@@ -14554,7 +14543,7 @@
       <c r="F968" s="19"/>
       <c r="G968" s="17"/>
     </row>
-    <row r="969" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B969" s="17"/>
       <c r="C969" s="17"/>
       <c r="D969" s="17"/>
@@ -14562,7 +14551,7 @@
       <c r="F969" s="19"/>
       <c r="G969" s="17"/>
     </row>
-    <row r="970" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B970" s="17"/>
       <c r="C970" s="17"/>
       <c r="D970" s="17"/>
@@ -14570,7 +14559,7 @@
       <c r="F970" s="19"/>
       <c r="G970" s="17"/>
     </row>
-    <row r="971" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B971" s="17"/>
       <c r="C971" s="17"/>
       <c r="D971" s="17"/>
@@ -14578,7 +14567,7 @@
       <c r="F971" s="19"/>
       <c r="G971" s="17"/>
     </row>
-    <row r="972" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B972" s="17"/>
       <c r="C972" s="17"/>
       <c r="D972" s="17"/>
@@ -14586,7 +14575,7 @@
       <c r="F972" s="19"/>
       <c r="G972" s="17"/>
     </row>
-    <row r="973" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B973" s="17"/>
       <c r="C973" s="17"/>
       <c r="D973" s="17"/>
@@ -14594,7 +14583,7 @@
       <c r="F973" s="19"/>
       <c r="G973" s="17"/>
     </row>
-    <row r="974" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B974" s="17"/>
       <c r="C974" s="17"/>
       <c r="D974" s="17"/>
@@ -14602,7 +14591,7 @@
       <c r="F974" s="19"/>
       <c r="G974" s="17"/>
     </row>
-    <row r="975" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B975" s="17"/>
       <c r="C975" s="17"/>
       <c r="D975" s="17"/>
@@ -14610,7 +14599,7 @@
       <c r="F975" s="19"/>
       <c r="G975" s="17"/>
     </row>
-    <row r="976" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B976" s="17"/>
       <c r="C976" s="17"/>
       <c r="D976" s="17"/>
@@ -14618,7 +14607,7 @@
       <c r="F976" s="19"/>
       <c r="G976" s="17"/>
     </row>
-    <row r="977" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B977" s="17"/>
       <c r="C977" s="17"/>
       <c r="D977" s="17"/>
@@ -14626,7 +14615,7 @@
       <c r="F977" s="19"/>
       <c r="G977" s="17"/>
     </row>
-    <row r="978" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B978" s="17"/>
       <c r="C978" s="17"/>
       <c r="D978" s="17"/>
@@ -14634,7 +14623,7 @@
       <c r="F978" s="19"/>
       <c r="G978" s="17"/>
     </row>
-    <row r="979" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B979" s="17"/>
       <c r="C979" s="17"/>
       <c r="D979" s="17"/>
@@ -14642,7 +14631,7 @@
       <c r="F979" s="19"/>
       <c r="G979" s="17"/>
     </row>
-    <row r="980" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B980" s="17"/>
       <c r="C980" s="17"/>
       <c r="D980" s="17"/>
@@ -14650,7 +14639,7 @@
       <c r="F980" s="19"/>
       <c r="G980" s="17"/>
     </row>
-    <row r="981" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B981" s="17"/>
       <c r="C981" s="17"/>
       <c r="D981" s="17"/>
@@ -14658,7 +14647,7 @@
       <c r="F981" s="19"/>
       <c r="G981" s="17"/>
     </row>
-    <row r="982" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B982" s="17"/>
       <c r="C982" s="17"/>
       <c r="D982" s="17"/>
@@ -14666,7 +14655,7 @@
       <c r="F982" s="19"/>
       <c r="G982" s="17"/>
     </row>
-    <row r="983" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B983" s="17"/>
       <c r="C983" s="17"/>
       <c r="D983" s="17"/>
@@ -14674,7 +14663,7 @@
       <c r="F983" s="19"/>
       <c r="G983" s="17"/>
     </row>
-    <row r="984" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B984" s="17"/>
       <c r="C984" s="17"/>
       <c r="D984" s="17"/>
@@ -14682,7 +14671,7 @@
       <c r="F984" s="19"/>
       <c r="G984" s="17"/>
     </row>
-    <row r="985" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B985" s="17"/>
       <c r="C985" s="17"/>
       <c r="D985" s="17"/>
@@ -14690,7 +14679,7 @@
       <c r="F985" s="19"/>
       <c r="G985" s="17"/>
     </row>
-    <row r="986" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B986" s="17"/>
       <c r="C986" s="17"/>
       <c r="D986" s="17"/>
@@ -14698,7 +14687,7 @@
       <c r="F986" s="19"/>
       <c r="G986" s="17"/>
     </row>
-    <row r="987" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B987" s="17"/>
       <c r="C987" s="17"/>
       <c r="D987" s="17"/>
@@ -14706,7 +14695,7 @@
       <c r="F987" s="19"/>
       <c r="G987" s="17"/>
     </row>
-    <row r="988" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B988" s="17"/>
       <c r="C988" s="17"/>
       <c r="D988" s="17"/>
@@ -14714,7 +14703,7 @@
       <c r="F988" s="19"/>
       <c r="G988" s="17"/>
     </row>
-    <row r="989" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B989" s="17"/>
       <c r="C989" s="17"/>
       <c r="D989" s="17"/>
@@ -14722,7 +14711,7 @@
       <c r="F989" s="19"/>
       <c r="G989" s="17"/>
     </row>
-    <row r="990" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B990" s="17"/>
       <c r="C990" s="17"/>
       <c r="D990" s="17"/>
@@ -14730,7 +14719,7 @@
       <c r="F990" s="19"/>
       <c r="G990" s="17"/>
     </row>
-    <row r="991" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B991" s="17"/>
       <c r="C991" s="17"/>
       <c r="D991" s="17"/>
@@ -14738,7 +14727,7 @@
       <c r="F991" s="19"/>
       <c r="G991" s="17"/>
     </row>
-    <row r="992" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B992" s="17"/>
       <c r="C992" s="17"/>
       <c r="D992" s="17"/>
@@ -14746,7 +14735,7 @@
       <c r="F992" s="19"/>
       <c r="G992" s="17"/>
     </row>
-    <row r="993" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B993" s="17"/>
       <c r="C993" s="17"/>
       <c r="D993" s="17"/>
@@ -14754,7 +14743,7 @@
       <c r="F993" s="19"/>
       <c r="G993" s="17"/>
     </row>
-    <row r="994" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B994" s="17"/>
       <c r="C994" s="17"/>
       <c r="D994" s="17"/>
@@ -14762,7 +14751,7 @@
       <c r="F994" s="19"/>
       <c r="G994" s="17"/>
     </row>
-    <row r="995" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B995" s="17"/>
       <c r="C995" s="17"/>
       <c r="D995" s="17"/>
@@ -14770,7 +14759,7 @@
       <c r="F995" s="19"/>
       <c r="G995" s="17"/>
     </row>
-    <row r="996" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B996" s="17"/>
       <c r="C996" s="17"/>
       <c r="D996" s="17"/>
@@ -14778,7 +14767,7 @@
       <c r="F996" s="19"/>
       <c r="G996" s="17"/>
     </row>
-    <row r="997" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B997" s="17"/>
       <c r="C997" s="17"/>
       <c r="D997" s="17"/>
@@ -14786,7 +14775,7 @@
       <c r="F997" s="19"/>
       <c r="G997" s="17"/>
     </row>
-    <row r="998" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B998" s="17"/>
       <c r="C998" s="17"/>
       <c r="D998" s="17"/>
@@ -14794,7 +14783,7 @@
       <c r="F998" s="19"/>
       <c r="G998" s="17"/>
     </row>
-    <row r="999" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B999" s="17"/>
       <c r="C999" s="17"/>
       <c r="D999" s="17"/>
@@ -14802,14 +14791,7 @@
       <c r="F999" s="19"/>
       <c r="G999" s="17"/>
     </row>
-    <row r="1000" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1000" s="17"/>
-      <c r="C1000" s="17"/>
-      <c r="D1000" s="17"/>
-      <c r="E1000" s="18"/>
-      <c r="F1000" s="19"/>
-      <c r="G1000" s="17"/>
-    </row>
+    <row r="1000" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:K146" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
@@ -14940,21 +14922,19 @@
     <hyperlink ref="G129" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
     <hyperlink ref="G130" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
     <hyperlink ref="G131" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="G132" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="G133" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="G134" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="G135" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="G136" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="G137" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="G138" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="J139" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="G140" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="G141" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="G142" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="G143" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="G144" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="G145" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="G146" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="G133" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="G134" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="G135" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="G136" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="G137" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="G138" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="J139" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="G140" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="G141" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="G142" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="G143" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="G144" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="G145" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
